--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1710,13 +1710,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.62019984954</v>
+        <v>46146.7868665162</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70543086805</v>
+        <v>46175.872097534724</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70544517361</v>
+        <v>46175.872111840275</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1763,13 +1763,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.620326226854</v>
+        <v>46146.78699289352</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70540511574</v>
+        <v>46175.8720717824</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70543134259</v>
+        <v>46175.87209800926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1826,13 +1826,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.62032965278</v>
+        <v>46146.786996319446</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70540572917</v>
+        <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70543135417</v>
+        <v>46175.87209802083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1889,13 +1889,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.620332997685</v>
+        <v>46146.78699966436</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.705406099536</v>
+        <v>46175.8720727662</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70543190972</v>
+        <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1952,13 +1952,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.62033583333</v>
+        <v>46146.7870025</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.705406469904</v>
+        <v>46175.872073136576</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70543217592</v>
+        <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2015,13 +2015,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.62033996527</v>
+        <v>46146.787006631945</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.705407002315</v>
+        <v>46175.87207366899</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70543275463</v>
+        <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2078,11 +2078,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.620205439816</v>
+        <v>46146.78687210648</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46146.654912303246</v>
+        <v>46146.8215789699</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2125,11 +2125,11 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.62034349537</v>
+        <v>46146.787010162036</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.70543185185</v>
+        <v>46175.87209851852</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2188,11 +2188,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.62034891204</v>
+        <v>46146.7870155787</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46175.70543159722</v>
+        <v>46175.87209826389</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2251,11 +2251,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.620354733794</v>
+        <v>46146.787021400465</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.70543159722</v>
+        <v>46175.87209826389</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2314,11 +2314,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.62036493055</v>
+        <v>46146.787031597225</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46156.0150424537</v>
+        <v>46156.18170912037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2377,11 +2377,11 @@
         <v>68</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.62020984954</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46146.66828484954</v>
+        <v>46146.834951516204</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2424,11 +2424,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.620374895836</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.69216849537</v>
+        <v>46169.85883516204</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2487,11 +2487,11 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.62038076389</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.692179363425</v>
+        <v>46169.858846030096</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2550,11 +2550,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.62038653935</v>
+        <v>46146.78705320602</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.69219260417</v>
+        <v>46169.85885927083</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2613,11 +2613,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.620392384255</v>
+        <v>46146.78705905093</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.00363233796</v>
+        <v>46178.17029900463</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2676,11 +2676,11 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.620402858796</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.00363422454</v>
+        <v>46178.1703008912</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2739,11 +2739,11 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.62040673611</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.00363568287</v>
+        <v>46178.170302349536</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2802,11 +2802,11 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.62041070602</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46178.00363732639</v>
+        <v>46178.17030399306</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2865,11 +2865,11 @@
         <v>96</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.62021439815</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46146.66933215278</v>
+        <v>46146.83599881944</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -2912,11 +2912,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.6204152662</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.69203420139</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -2975,11 +2975,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.620420127314</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.6922908912</v>
+        <v>46169.858957557866</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3034,11 +3034,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.62042537037</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.69230549769</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3093,11 +3093,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.62043092593</v>
+        <v>46146.78709759259</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46175.031093495374</v>
+        <v>46175.19776016204</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3156,11 +3156,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.62043646991</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.69234486111</v>
+        <v>46169.85901152778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3215,11 +3215,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.62044230324</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46174.004191134256</v>
+        <v>46174.17085780093</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3274,11 +3274,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.62044760417</v>
+        <v>46146.78711427083</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46183.02971696759</v>
+        <v>46183.19638363426</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3337,11 +3337,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.62045268518</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.69239640047</v>
+        <v>46169.859063067124</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3396,11 +3396,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.620457997684</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.69243152778</v>
+        <v>46169.85909819444</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3455,11 +3455,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.62046320602</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.69245552083</v>
+        <v>46169.859122187496</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3514,11 +3514,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.62052135417</v>
+        <v>46146.78718802083</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.035626701385</v>
+        <v>46182.20229336806</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3577,11 +3577,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.620526597224</v>
+        <v>46146.78719326389</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46182.00217861111</v>
+        <v>46182.168845277774</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3636,11 +3636,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.62053138889</v>
+        <v>46146.78719805555</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.6925337037</v>
+        <v>46169.85920037037</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3695,11 +3695,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.62054903935</v>
+        <v>46146.78721570602</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.03562672454</v>
+        <v>46182.20229339121</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -3758,11 +3758,11 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.6205521875</v>
+        <v>46146.787218854166</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.002176724534</v>
+        <v>46182.168843391206</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>89</v>
@@ -3811,11 +3811,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.62055623843</v>
+        <v>46146.78722290509</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69258931713</v>
+        <v>46169.8592559838</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3864,11 +3864,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.620560069445</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.6921353588</v>
+        <v>46169.85880202547</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>153</v>
@@ -3927,11 +3927,11 @@
         <v>157</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.62056321759</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46185.00290997685</v>
+        <v>46185.169576643515</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>95</v>
@@ -3980,11 +3980,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.6205671412</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69264173611</v>
+        <v>46169.85930840278</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4033,11 +4033,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.75478928241</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.69266547453</v>
+        <v>46169.859332141205</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4084,11 +4084,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.62057075232</v>
+        <v>46146.78723741898</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.035626956014</v>
+        <v>46182.202293622686</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4147,11 +4147,11 @@
         <v>169</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.62057396991</v>
+        <v>46146.78724063658</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46182.00217998843</v>
+        <v>46182.16884665509</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>92</v>
@@ -4200,11 +4200,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.62057800926</v>
+        <v>46146.78724467593</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.69273061343</v>
+        <v>46169.85939728009</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4253,11 +4253,11 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.620219097225</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46146.66787917824</v>
+        <v>46146.834545844904</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4300,11 +4300,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.62058282408</v>
+        <v>46146.78724949074</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46163.0263762963</v>
+        <v>46163.193042962965</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4363,11 +4363,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.62058797454</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46176.03509844907</v>
+        <v>46176.20176511574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4426,11 +4426,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.62059395833</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46177.03618011574</v>
+        <v>46177.202846782406</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>85</v>
@@ -4487,11 +4487,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.620612175924</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.77304238426</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4548,11 +4548,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.620615949076</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.77290814815</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4599,11 +4599,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.62061986111</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.77290880787</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>194</v>
@@ -4650,11 +4650,11 @@
         <v>197</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.62067509259</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46146.74787008102</v>
+        <v>46146.91453674769</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>198</v>
@@ -4697,11 +4697,11 @@
         <v>200</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.62067858796</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46184.013349699075</v>
+        <v>46184.18001636574</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4760,11 +4760,11 @@
         <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.62069221065</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46185.02079229167</v>
+        <v>46185.18745895833</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4821,11 +4821,11 @@
         <v>209</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.620683981484</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46184.01334978009</v>
+        <v>46184.18001644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>210</v>
@@ -4884,11 +4884,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.630636851856</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46185.02079232639</v>
+        <v>46185.18745899305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4947,11 +4947,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.62068782408</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46184.01335008102</v>
+        <v>46184.18001674769</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5010,11 +5010,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.63084329861</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46185.02079234953</v>
+        <v>46185.187459016204</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5073,11 +5073,11 @@
         <v>219</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.62069773149</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46146.75272751157</v>
+        <v>46146.91939417824</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>220</v>
@@ -5120,11 +5120,11 @@
         <v>222</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.62070028935</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.41057712963</v>
+        <v>46161.577243796295</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -5183,11 +5183,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.62771714121</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46146.77484982639</v>
+        <v>46146.941516493054</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>228</v>
@@ -5236,11 +5236,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.627734525464</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46146.77484672454</v>
+        <v>46146.941513391204</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>228</v>
@@ -5289,11 +5289,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.620705127316</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.774744594906</v>
+        <v>46146.94141126158</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>235</v>
@@ -5352,11 +5352,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.620708946764</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.77494079861</v>
+        <v>46146.941607465276</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5405,11 +5405,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.6207152662</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46146.774937407405</v>
+        <v>46146.941604074076</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>233</v>
@@ -5458,11 +5458,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.62073795139</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46146.77473961806</v>
+        <v>46146.94140628472</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>242</v>
@@ -5519,11 +5519,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.62074189815</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46146.77503974537</v>
+        <v>46146.941706412035</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>228</v>
@@ -5570,11 +5570,11 @@
         <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.62074706018</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.77503626158</v>
+        <v>46146.94170292824</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>228</v>
@@ -5621,11 +5621,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.62076790509</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46146.754552962964</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>198</v>
@@ -5668,11 +5668,11 @@
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.62077079861</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46176.03509914352</v>
+        <v>46176.20176581018</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5729,11 +5729,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.62077674769</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46157.01592533565</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>253</v>
@@ -5790,11 +5790,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.620782303246</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46184.01335005787</v>
+        <v>46184.18001672454</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5851,11 +5851,11 @@
         <v>257</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.62079372685</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46146.77516402778</v>
+        <v>46146.94183069444</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>258</v>
@@ -5912,11 +5912,11 @@
         <v>260</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.6208378588</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.7732647338</v>
+        <v>46146.93993140046</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>261</v>
@@ -5959,11 +5959,11 @@
         <v>263</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.62084224537</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.77532376157</v>
+        <v>46146.94199042824</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>264</v>
@@ -6022,11 +6022,11 @@
         <v>266</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.62085349537</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.77539079861</v>
+        <v>46146.942057465276</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>194</v>
@@ -6075,11 +6075,11 @@
         <v>268</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.62085773148</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46146.77538378473</v>
+        <v>46146.942050451384</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>194</v>
@@ -6128,11 +6128,11 @@
         <v>269</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.620914652776</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46146.77532060185</v>
+        <v>46146.94198726852</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>270</v>
@@ -6189,11 +6189,11 @@
         <v>271</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.62091990741</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46146.77546072917</v>
+        <v>46146.94212739583</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>194</v>
@@ -6240,11 +6240,11 @@
         <v>274</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.62092627315</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.775457881944</v>
+        <v>46146.942124548616</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>194</v>
@@ -6291,11 +6291,11 @@
         <v>276</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.6209508912</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46146.77531712963</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>277</v>
@@ -6354,11 +6354,11 @@
         <v>278</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.620960416665</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46146.77554761574</v>
+        <v>46146.942214282404</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>194</v>
@@ -6405,11 +6405,11 @@
         <v>280</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.62096664352</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.775545219905</v>
+        <v>46146.94221188658</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>194</v>
@@ -6456,11 +6456,11 @@
         <v>281</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.62103199074</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.77531423611</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>282</v>
@@ -6517,11 +6517,11 @@
         <v>283</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.62103688657</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.77562837963</v>
+        <v>46146.9422950463</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>194</v>
@@ -6568,11 +6568,11 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.62104225694</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.7756253125</v>
+        <v>46146.94229197917</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>194</v>
@@ -6619,11 +6619,11 @@
         <v>288</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.62106385417</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.77531146991</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>289</v>
@@ -6680,11 +6680,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.62106844907</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.7757059375</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>194</v>
@@ -6731,11 +6731,11 @@
         <v>292</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.621073692135</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.77570342593</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>194</v>
@@ -6782,11 +6782,11 @@
         <v>293</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.6210928125</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.77530659722</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>294</v>
@@ -6843,11 +6843,11 @@
         <v>296</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.62109759259</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.77578200231</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>194</v>
@@ -6894,11 +6894,11 @@
         <v>298</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.62110192129</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.775778923606</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>194</v>
@@ -6945,11 +6945,11 @@
         <v>299</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.62111905093</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.77389681713</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>300</v>
@@ -6992,11 +6992,11 @@
         <v>302</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.621122453704</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.77631427083</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>303</v>
@@ -7053,11 +7053,11 @@
         <v>307</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.62112762731</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.77597652777</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>194</v>
@@ -7104,11 +7104,11 @@
         <v>309</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.621131747685</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.77597726852</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>194</v>
@@ -7155,11 +7155,11 @@
         <v>311</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.6211480787</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.77622869213</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>312</v>
@@ -7216,11 +7216,11 @@
         <v>313</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.62115233796</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.77619097222</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>194</v>
@@ -7267,11 +7267,11 @@
         <v>315</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.62115648148</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.77618863426</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>194</v>
@@ -7318,11 +7318,11 @@
         <v>317</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.62122486111</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.776493067126</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>318</v>
@@ -7379,11 +7379,11 @@
         <v>319</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.62123096065</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.77676126157</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>194</v>
@@ -7430,11 +7430,11 @@
         <v>321</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.62123871528</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.77679804398</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>194</v>
@@ -7481,11 +7481,11 @@
         <v>323</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.621261504624</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.77660861111</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>324</v>
@@ -7542,11 +7542,11 @@
         <v>326</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.62126774306</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.77665572916</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>194</v>
@@ -7593,11 +7593,11 @@
         <v>327</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.62127246527</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.77665320602</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>194</v>
@@ -7644,11 +7644,11 @@
         <v>328</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.62129130787</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.77389685185</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>329</v>
@@ -7691,11 +7691,11 @@
         <v>331</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.62129487269</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46146.77686291667</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>332</v>
@@ -7754,11 +7754,11 @@
         <v>335</v>
       </c>
       <c r="B110" s="5">
-        <v>46146.6213005787</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46146.77691881944</v>
+        <v>46146.94358548611</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.20229336806</v>
+        <v>46189.168644363424</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.85920037037</v>
+        <v>46189.16864960648</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.20229339121</v>
+        <v>46189.1686389699</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.8592559838</v>
+        <v>46189.16864146991</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.202293622686</v>
+        <v>46189.16864567129</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.85939728009</v>
+        <v>46189.168642951394</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46183.19638363426</v>
+        <v>46190.168740520836</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.85909819444</v>
+        <v>46190.16874317129</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46161.577243796295</v>
+        <v>46190.16989362269</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -5168,8 +5168,8 @@
       <c r="R62" s="5">
         <v>46197</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>107</v>
+      <c r="S62" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46189.168644363424</v>
+        <v>46190.18189784722</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3562,8 +3562,8 @@
       <c r="R34" s="5">
         <v>46189</v>
       </c>
-      <c r="S34" s="12" t="s">
-        <v>123</v>
+      <c r="S34" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46189.1686389699</v>
+        <v>46190.18189791667</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>145</v>
@@ -3743,8 +3743,8 @@
       <c r="R37" s="9">
         <v>46189</v>
       </c>
-      <c r="S37" s="12" t="s">
-        <v>123</v>
+      <c r="S37" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46189.16864567129</v>
+        <v>46190.1818981713</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>167</v>
@@ -4132,8 +4132,8 @@
       <c r="R44" s="5">
         <v>46189</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>123</v>
+      <c r="S44" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -441,250 +441,250 @@
     <t>Generación OC motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
   </si>
   <si>
+    <t>1214511142420771</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511155826380</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214511155826398</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511240963370</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240963385</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511245068713</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002704</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>1214511199002729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214511142484065</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142484075</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973505</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084879</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214511240973520</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973530</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199027682</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084764</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199027697</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199035045</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214511240985139</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901576</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901586</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901596</t>
+  </si>
+  <si>
+    <t>1214511155796713</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511155796723</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511142420771</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511155826380</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214511155826398</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511240963370</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240963385</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511245068713</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002704</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>1214511199002729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214511142484065</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142484075</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973505</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084879</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214511240973520</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973530</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199027682</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084764</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199027697</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199035045</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214511240985139</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901576</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901586</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901596</t>
-  </si>
-  <si>
-    <t>1214511155796713</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511155796723</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214511245146577</t>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46190.168740520836</v>
+        <v>46191.18668917824</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3322,8 +3322,8 @@
       <c r="R30" s="5">
         <v>46190</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>123</v>
+      <c r="S30" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78711935185</v>
@@ -3344,7 +3344,7 @@
         <v>46169.859063067124</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3377,7 +3377,7 @@
         <v>72</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712466435</v>
@@ -3403,7 +3403,7 @@
         <v>46190.16874317129</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3433,10 +3433,10 @@
         <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78712987268</v>
@@ -3462,7 +3462,7 @@
         <v>46169.859122187496</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3492,10 +3492,10 @@
         <v>121</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78718802083</v>
@@ -3521,16 +3521,16 @@
         <v>46190.18189784722</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3551,7 +3551,7 @@
         <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>97</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719326389</v>
@@ -3584,16 +3584,16 @@
         <v>46182.168845277774</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>136</v>
       </c>
       <c r="I35" s="9">
         <v>46181</v>
@@ -3611,13 +3611,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78719805555</v>
@@ -3643,16 +3643,16 @@
         <v>46189.16864960648</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="I36" s="5">
         <v>46183</v>
@@ -3670,13 +3670,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46146.78721570602</v>
@@ -3702,16 +3702,16 @@
         <v>46190.18189791667</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>136</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3732,7 +3732,7 @@
         <v>97</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46146.787218854166</v>
@@ -3771,10 +3771,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="I38" s="5">
         <v>46181</v>
@@ -3792,13 +3792,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722290509</v>
@@ -3818,16 +3818,16 @@
         <v>46189.16864146991</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>136</v>
       </c>
       <c r="I39" s="9">
         <v>46183</v>
@@ -3845,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46146.78722673611</v>
@@ -3871,16 +3871,16 @@
         <v>46169.85880202547</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3901,7 +3901,7 @@
         <v>97</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787229884256</v>
@@ -3940,10 +3940,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I41" s="9">
         <v>46181</v>
@@ -3961,13 +3961,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>94</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46146.787233807874</v>
@@ -3987,16 +3987,16 @@
         <v>46169.85930840278</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46188</v>
@@ -4014,13 +4014,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46146.92145594908</v>
@@ -4040,16 +4040,16 @@
         <v>46169.859332141205</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4065,10 +4065,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78723741898</v>
@@ -4091,16 +4091,16 @@
         <v>46190.1818981713</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4121,7 +4121,7 @@
         <v>97</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724063658</v>
@@ -4160,10 +4160,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>136</v>
       </c>
       <c r="I45" s="9">
         <v>46181</v>
@@ -4181,13 +4181,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>91</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78724467593</v>
@@ -4207,16 +4207,16 @@
         <v>46189.168642951394</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="I46" s="5">
         <v>46183</v>
@@ -4234,13 +4234,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>92</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78688576389</v>
@@ -4260,7 +4260,7 @@
         <v>46146.834545844904</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4284,7 +4284,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46146.78724949074</v>
@@ -4307,16 +4307,16 @@
         <v>46163.193042962965</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46156</v>
@@ -4334,13 +4334,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46156</v>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46146.7872546412</v>
@@ -4370,16 +4370,16 @@
         <v>46176.20176511574</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="I49" s="9">
         <v>46169</v>
@@ -4397,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="P49" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="P49" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46169</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46146.787260625</v>
@@ -4439,10 +4439,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4458,13 +4458,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46176</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78727884259</v>
@@ -4494,16 +4494,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4519,10 +4519,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46146.78728261574</v>
@@ -4555,16 +4555,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4580,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787286527775</v>
@@ -4606,16 +4606,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4631,13 +4631,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="P53" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787341759264</v>
@@ -4657,7 +4657,7 @@
         <v>46146.91453674769</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4681,7 +4681,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4694,26 +4694,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787345254634</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46184.18001636574</v>
+        <v>46191.16860351852</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I55" s="9">
         <v>46190</v>
@@ -4731,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="9">
         <v>46190</v>
@@ -4746,7 +4746,7 @@
         <v>46191</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4773,10 +4773,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4792,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>207</v>
@@ -4807,7 +4807,7 @@
         <v>46192</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46184.18001644676</v>
+        <v>46191.16860615741</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>210</v>
@@ -4834,10 +4834,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I57" s="9">
         <v>46190</v>
@@ -4855,10 +4855,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>211</v>
@@ -4870,7 +4870,7 @@
         <v>46191</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4897,10 +4897,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I58" s="5">
         <v>46192</v>
@@ -4918,7 +4918,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>210</v>
@@ -4933,7 +4933,7 @@
         <v>46192</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46184.18001674769</v>
+        <v>46191.16860751157</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -4960,10 +4960,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I59" s="9">
         <v>46190</v>
@@ -4981,10 +4981,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>217</v>
@@ -4996,7 +4996,7 @@
         <v>46191</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
@@ -5023,10 +5023,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I60" s="5">
         <v>46192</v>
@@ -5044,7 +5044,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>216</v>
@@ -5059,7 +5059,7 @@
         <v>46192</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5169,7 +5169,7 @@
         <v>46197</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>46146.92121962963</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5681,10 +5681,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5700,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>118</v>
@@ -5742,10 +5742,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5761,7 +5761,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>109</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46184.18001672454</v>
+        <v>46191.16860884259</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5803,10 +5803,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5822,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>251</v>
@@ -5837,7 +5837,7 @@
         <v>46191</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5864,10 +5864,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -5883,10 +5883,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>259</v>
@@ -6029,7 +6029,7 @@
         <v>46146.942057465276</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6082,7 +6082,7 @@
         <v>46146.942050451384</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6163,7 +6163,7 @@
         <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>261</v>
@@ -6196,7 +6196,7 @@
         <v>46146.94212739583</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6247,7 +6247,7 @@
         <v>46146.942124548616</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6328,7 +6328,7 @@
         <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>261</v>
@@ -6361,7 +6361,7 @@
         <v>46146.942214282404</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6412,7 +6412,7 @@
         <v>46146.94221188658</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6491,7 +6491,7 @@
         <v>261</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>261</v>
@@ -6524,7 +6524,7 @@
         <v>46146.9422950463</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6575,7 +6575,7 @@
         <v>46146.94229197917</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6654,7 +6654,7 @@
         <v>261</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>261</v>
@@ -6687,7 +6687,7 @@
         <v>46146.94237260417</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6715,7 +6715,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6738,7 +6738,7 @@
         <v>46146.94237009259</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6766,7 +6766,7 @@
         <v>289</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>291</v>
@@ -6817,7 +6817,7 @@
         <v>261</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>295</v>
@@ -6850,7 +6850,7 @@
         <v>46146.94244866898</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6878,7 +6878,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>297</v>
@@ -6901,7 +6901,7 @@
         <v>46146.94244559028</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6929,7 +6929,7 @@
         <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>297</v>
@@ -7060,7 +7060,7 @@
         <v>46146.942643194445</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7088,7 +7088,7 @@
         <v>303</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>308</v>
@@ -7111,7 +7111,7 @@
         <v>46146.94264393518</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7139,7 +7139,7 @@
         <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>310</v>
@@ -7190,7 +7190,7 @@
         <v>300</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>300</v>
@@ -7223,7 +7223,7 @@
         <v>46146.94285763889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7251,7 +7251,7 @@
         <v>312</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>314</v>
@@ -7274,7 +7274,7 @@
         <v>46146.94285530093</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7302,7 +7302,7 @@
         <v>312</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>316</v>
@@ -7353,7 +7353,7 @@
         <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>300</v>
@@ -7386,7 +7386,7 @@
         <v>46146.94342792824</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7414,7 +7414,7 @@
         <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>320</v>
@@ -7437,7 +7437,7 @@
         <v>46146.94346471065</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7465,7 +7465,7 @@
         <v>318</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>322</v>
@@ -7516,7 +7516,7 @@
         <v>300</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>325</v>
@@ -7549,7 +7549,7 @@
         <v>46146.94332239583</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7577,7 +7577,7 @@
         <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>324</v>
@@ -7600,7 +7600,7 @@
         <v>46146.943319872684</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7628,7 +7628,7 @@
         <v>324</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>324</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46146.834951516204</v>
+        <v>46191.784095717594</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2552,9 +2552,11 @@
       <c r="B18" s="5">
         <v>46146.78705320602</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46191.784087754626</v>
+      </c>
       <c r="D18" s="5">
-        <v>46169.85885927083</v>
+        <v>46191.78471304398</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2602,10 +2604,10 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3097,7 +3099,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46175.19776016204</v>
+        <v>46191.78582608796</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3160,7 +3162,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.85901152778</v>
+        <v>46191.78409722222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3217,9 +3219,11 @@
       <c r="B29" s="9">
         <v>46146.787108969904</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46191.78550167824</v>
+      </c>
       <c r="D29" s="9">
-        <v>46174.17085780093</v>
+        <v>46191.78550341435</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -5672,7 +5676,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46176.20176581018</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5720,8 +5724,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>67</v>
+      <c r="U72" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -684,19 +684,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1214511245146577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511245146577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
   </si>
   <si>
     <t>1214511155961778</t>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46191.16860351852</v>
+        <v>46192.17325630787</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4749,8 +4749,8 @@
       <c r="R55" s="9">
         <v>46191</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>204</v>
+      <c r="S55" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4761,17 +4761,17 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46146.787358877315</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46185.18745895833</v>
+        <v>46192.171127546295</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4799,10 +4799,10 @@
         <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46192</v>
@@ -4811,7 +4811,7 @@
         <v>46192</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46191.16860615741</v>
+        <v>46192.17324446759</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>210</v>
@@ -4873,8 +4873,8 @@
       <c r="R57" s="9">
         <v>46191</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>204</v>
+      <c r="S57" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46185.18745899305</v>
+        <v>46192.170792986115</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4937,7 +4937,7 @@
         <v>46192</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46191.16860751157</v>
+        <v>46192.17323068287</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -4999,8 +4999,8 @@
       <c r="R59" s="9">
         <v>46191</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>204</v>
+      <c r="S59" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46185.187459016204</v>
+        <v>46192.17099846065</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5063,7 +5063,7 @@
         <v>46192</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>46197</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.16860884259</v>
+        <v>46192.17326015046</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5840,8 +5840,8 @@
       <c r="R74" s="5">
         <v>46191</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>204</v>
+      <c r="S74" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46191.78582608796</v>
+        <v>46192.79812496528</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -696,61 +696,61 @@
     <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
   </si>
   <si>
+    <t>1214511155961778</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214508463084772</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155961793</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084773</t>
+  </si>
+  <si>
+    <t>1214511241037947</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214511241037957</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511155961778</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214508463084772</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155961793</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084773</t>
-  </si>
-  <si>
-    <t>1214511241037947</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214511241037957</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4232 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.171127546295</v>
+        <v>46193.182386307875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>205</v>
@@ -4810,8 +4810,8 @@
       <c r="R56" s="5">
         <v>46192</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>208</v>
+      <c r="S56" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="9">
         <v>46146.78735064815</v>
@@ -4832,7 +4832,7 @@
         <v>46192.17324446759</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4865,7 +4865,7 @@
         <v>149</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="9">
         <v>46190</v>
@@ -4885,17 +4885,17 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46146.79730351851</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.170792986115</v>
+        <v>46193.18238616898</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4925,10 +4925,10 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46192</v>
@@ -4936,8 +4936,8 @@
       <c r="R58" s="5">
         <v>46192</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>208</v>
+      <c r="S58" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46146.78735449074</v>
@@ -4958,7 +4958,7 @@
         <v>46192.17323068287</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4991,7 +4991,7 @@
         <v>171</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="9">
         <v>46190</v>
@@ -5011,17 +5011,17 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46146.79750996528</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46192.17099846065</v>
+        <v>46193.182386203705</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5051,10 +5051,10 @@
         <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46192</v>
@@ -5062,8 +5062,8 @@
       <c r="R60" s="5">
         <v>46192</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>208</v>
+      <c r="S60" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46146.787364398144</v>
@@ -5084,7 +5084,7 @@
         <v>46146.91939417824</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5108,7 +5108,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46146.78736695602</v>
@@ -5131,16 +5131,16 @@
         <v>46190.16989362269</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5158,13 +5158,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46195</v>
@@ -5173,7 +5173,7 @@
         <v>46197</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5221,7 +5221,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>229</v>
@@ -5253,10 +5253,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46195</v>
@@ -5274,7 +5274,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>232</v>
@@ -5306,10 +5306,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5327,13 +5327,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>236</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46198</v>
@@ -5369,10 +5369,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5422,10 +5422,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I67" s="9">
         <v>46198</v>
@@ -5475,10 +5475,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5494,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46205</v>
@@ -5536,10 +5536,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5587,10 +5587,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -7335,10 +7335,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7396,10 +7396,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7447,10 +7447,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7498,10 +7498,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7559,10 +7559,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7610,10 +7610,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46146.83599881944</v>
+        <v>46195.92635412037</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3097,9 +3097,11 @@
       <c r="B27" s="9">
         <v>46146.78709759259</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46195.92634351852</v>
+      </c>
       <c r="D27" s="9">
-        <v>46192.79812496528</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3147,10 +3149,10 @@
         <v>33</v>
       </c>
       <c r="T27" s="10">
-        <v>0</v>
-      </c>
-      <c r="U27" s="11" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3160,9 +3162,11 @@
       <c r="B28" s="5">
         <v>46146.78710313658</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46195.92632717593</v>
+      </c>
       <c r="D28" s="5">
-        <v>46191.78409722222</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3223,7 +3227,7 @@
         <v>46191.78550167824</v>
       </c>
       <c r="D29" s="9">
-        <v>46191.78550341435</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="334">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -213,7 +213,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor</t>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
     <t>1214511240917238</t>
@@ -231,7 +231,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>propuesta motor OT 4309,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
+    <t>propuesta motor OT 4309,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -252,7 +252,7 @@
 </t>
   </si>
   <si>
-    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
+    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1214511155782245</t>
@@ -261,39 +261,30 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Planos preliminar,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1214511240918578</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214508463084760</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,propuesta Corte Laser OT 4309,propuesta motor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198865760</t>
+  </si>
+  <si>
+    <t>propuesta motor OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309,Propuesta compras:</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1214508463084760</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,propuesta Corte Laser OT 4309,propuesta motor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198865760</t>
-  </si>
-  <si>
-    <t>propuesta motor OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309,Propuesta compras:</t>
-  </si>
-  <si>
     <t>1214511142378696</t>
   </si>
   <si>
@@ -1081,9 +1072,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2082,7 +2070,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46146.8215789699</v>
+        <v>46196.86770065972</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2129,7 +2117,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.87209851852</v>
+        <v>46196.86770065972</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2192,7 +2180,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46175.87209826389</v>
+        <v>46196.867700752315</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2255,7 +2243,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.87209826389</v>
+        <v>46196.86770050926</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2314,30 +2302,24 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.787031597225</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46156.18170912037</v>
+        <v>46191.784095717594</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46147</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46155</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2345,90 +2327,96 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46147</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46155</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.7868765162</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46191.784095717594</v>
+        <v>46169.85883516204</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46149</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46150</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="10" t="s">
+      <c r="Q15" s="9">
+        <v>46149</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46150</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="N15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="10" t="s">
+      <c r="U15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.7870415625</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.85883516204</v>
+        <v>46169.858846030096</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2458,10 +2446,10 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>73</v>
@@ -2479,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="U16" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2487,11 +2475,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.78704743055</v>
-      </c>
-      <c r="C17" s="10"/>
+        <v>46146.78705320602</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46191.784087754626</v>
+      </c>
       <c r="D17" s="9">
-        <v>46169.858846030096</v>
+        <v>46191.78471304398</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2500,10 +2490,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="I17" s="9">
         <v>46149</v>
@@ -2521,13 +2511,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2539,42 +2529,40 @@
         <v>33</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.78705320602</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46191.784087754626</v>
-      </c>
+        <v>46146.78705905093</v>
+      </c>
+      <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46191.78471304398</v>
+        <v>46178.17029900463</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I18" s="5">
-        <v>46149</v>
+        <v>46177</v>
       </c>
       <c r="J18" s="5">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
@@ -2586,52 +2574,52 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="R18" s="5">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="S18" s="11" t="s">
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>1</v>
-      </c>
-      <c r="U18" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.78705905093</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.17029900463</v>
+        <v>46178.1703008912</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I19" s="9">
         <v>46177</v>
@@ -2649,16 +2637,16 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>86</v>
       </c>
       <c r="Q19" s="9">
-        <v>46146</v>
+        <v>46177</v>
       </c>
       <c r="R19" s="9">
         <v>46147</v>
@@ -2670,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2678,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.78706952547</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.1703008912</v>
+        <v>46178.170302349536</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>88</v>
@@ -2691,10 +2679,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I20" s="5">
         <v>46177</v>
@@ -2712,10 +2700,10 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>89</v>
@@ -2733,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2741,11 +2729,11 @@
         <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.78707340278</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.170302349536</v>
+        <v>46178.17030399306</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2754,10 +2742,10 @@
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I21" s="9">
         <v>46177</v>
@@ -2775,10 +2763,10 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>92</v>
@@ -2796,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2804,30 +2792,24 @@
         <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.78707737269</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46178.17030399306</v>
+        <v>46195.92635412037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="5">
-        <v>46177</v>
-      </c>
-      <c r="J22" s="5">
-        <v>46178</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2835,56 +2817,52 @@
         <v>26</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>46177</v>
-      </c>
-      <c r="R22" s="5">
-        <v>46147</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.786881064814</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46195.92635412037</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46153</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46156</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
       </c>
@@ -2892,51 +2870,61 @@
         <v>26</v>
       </c>
       <c r="M23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46153</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46156</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="N23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
+      <c r="U23" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.78708193287</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.858700868055</v>
+        <v>46169.858957557866</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
       </c>
       <c r="J24" s="5">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -2951,84 +2939,80 @@
         <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P24" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="P24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46153</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46156</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>33</v>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.78708679398</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.858957557866</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H25" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46155</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46156</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="9">
-        <v>46153</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46154</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3036,11 +3020,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.78709203703</v>
-      </c>
-      <c r="C26" s="6"/>
+        <v>46146.78709759259</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46195.92634351852</v>
+      </c>
       <c r="D26" s="5">
-        <v>46169.85897216435</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3049,16 +3035,16 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="J26" s="5">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -3070,24 +3056,28 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46153</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46174</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3095,13 +3085,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.78709759259</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.92634351852</v>
+        <v>46195.92632717593</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.92635861111</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3110,16 +3100,16 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
       </c>
       <c r="J27" s="9">
-        <v>46174</v>
+        <v>46154</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3131,28 +3121,24 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="P27" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46153</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46174</v>
-      </c>
-      <c r="S27" s="11" t="s">
-        <v>33</v>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T27" s="10">
-        <v>1</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3160,13 +3146,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.78710313658</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.92632717593</v>
+        <v>46191.78550167824</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.92632960648</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3175,16 +3161,16 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="J28" s="5">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3196,10 +3182,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>116</v>
@@ -3207,13 +3193,13 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3221,13 +3207,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.787108969904</v>
-      </c>
-      <c r="C29" s="9">
-        <v>46191.78550167824</v>
-      </c>
+        <v>46146.78711427083</v>
+      </c>
+      <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46195.9263380787</v>
+        <v>46191.18668917824</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3236,16 +3220,16 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I29" s="9">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="J29" s="9">
-        <v>46174</v>
+        <v>46190</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3257,24 +3241,28 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46153</v>
+      </c>
+      <c r="R29" s="9">
+        <v>46190</v>
+      </c>
+      <c r="S29" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3282,11 +3270,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.78711427083</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46191.18668917824</v>
+        <v>46169.859063067124</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3295,16 +3283,16 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
       </c>
       <c r="J30" s="5">
-        <v>46190</v>
+        <v>46161</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3316,28 +3304,24 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="P30" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>46153</v>
-      </c>
-      <c r="R30" s="5">
-        <v>46190</v>
-      </c>
-      <c r="S30" s="11" t="s">
-        <v>33</v>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3345,11 +3329,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.78711935185</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.859063067124</v>
+        <v>46190.16874317129</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3358,16 +3342,16 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I31" s="9">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="J31" s="9">
-        <v>46161</v>
+        <v>46190</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>26</v>
@@ -3379,10 +3363,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>125</v>
@@ -3390,13 +3374,13 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3404,11 +3388,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.78712466435</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46190.16874317129</v>
+        <v>46169.859122187496</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3417,16 +3401,16 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="J32" s="5">
-        <v>46190</v>
+        <v>46169</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3438,10 +3422,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>128</v>
@@ -3449,13 +3433,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3463,11 +3447,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.78712987268</v>
+        <v>46146.78718802083</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.859122187496</v>
+        <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3476,16 +3460,16 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I33" s="9">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J33" s="9">
-        <v>46169</v>
+        <v>46189</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3497,54 +3481,58 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>46150</v>
+      </c>
+      <c r="R33" s="9">
+        <v>46189</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.78718802083</v>
+        <v>46146.78719326389</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.18189784722</v>
+        <v>46182.168845277774</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
       </c>
       <c r="J34" s="5">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3556,28 +3544,24 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="P34" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46150</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S34" s="11" t="s">
-        <v>33</v>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3585,11 +3569,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.78719326389</v>
+        <v>46146.78719805555</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46182.168845277774</v>
+        <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3598,31 +3582,31 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46183</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46189</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O35" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46181</v>
-      </c>
-      <c r="J35" s="9">
-        <v>46182</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>139</v>
@@ -3630,13 +3614,13 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3644,11 +3628,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.78719805555</v>
+        <v>46146.78721570602</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46189.16864960648</v>
+        <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3657,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="J36" s="5">
         <v>46189</v>
@@ -3678,24 +3662,28 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="7" t="s">
-        <v>107</v>
+        <v>26</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46150</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46189</v>
+      </c>
+      <c r="S36" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3703,29 +3691,29 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.78721570602</v>
+        <v>46146.787218854166</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.18189791667</v>
+        <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
       </c>
       <c r="J37" s="9">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3737,58 +3725,48 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>46150</v>
-      </c>
-      <c r="R37" s="9">
-        <v>46189</v>
-      </c>
-      <c r="S37" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.787218854166</v>
+        <v>46146.78722290509</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.168843391206</v>
+        <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="J38" s="5">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3800,10 +3778,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>147</v>
@@ -3819,11 +3797,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.78722290509</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46189.16864146991</v>
+        <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3832,16 +3810,16 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="I39" s="9">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="J39" s="9">
-        <v>46189</v>
+        <v>46216</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3853,48 +3831,58 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>46181</v>
+      </c>
+      <c r="R39" s="9">
+        <v>46217</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T39" s="10">
+        <v>0</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.78722673611</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.85880202547</v>
+        <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
       </c>
       <c r="J40" s="5">
-        <v>46216</v>
+        <v>46185</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3906,58 +3894,48 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46181</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46217</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.787229884256</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46185.169576643515</v>
+        <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="J41" s="9">
-        <v>46185</v>
+        <v>46216</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -3969,10 +3947,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>157</v>
@@ -3988,11 +3966,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.787233807874</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.85930840278</v>
+        <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4001,16 +3979,14 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="I42" s="5">
-        <v>46188</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="I42" s="6"/>
       <c r="J42" s="5">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -4022,13 +3998,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4038,83 +4014,95 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.92145594908</v>
+        <v>46146.78723741898</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.859332141205</v>
+        <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="H43" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46181</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="9">
-        <v>46217</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>159</v>
-      </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9">
+        <v>46181</v>
+      </c>
+      <c r="R43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="S43" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T43" s="10">
+        <v>0</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.78723741898</v>
+        <v>46146.78724063658</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46190.1818981713</v>
+        <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
       </c>
       <c r="J44" s="5">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4126,58 +4114,48 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46181</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S44" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.78724063658</v>
+        <v>46146.78724467593</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46182.16884665509</v>
+        <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I45" s="9">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="J45" s="9">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4189,10 +4167,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>169</v>
@@ -4208,30 +4186,24 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.78724467593</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46189.168642951394</v>
+        <v>46146.834545844904</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46183</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46189</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -4239,16 +4211,16 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4261,24 +4233,30 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.78688576389</v>
+        <v>46146.78724949074</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46146.834545844904</v>
+        <v>46163.193042962965</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+        <v>175</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46156</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46162</v>
+      </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4286,51 +4264,61 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>46156</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46162</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="N47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
+      <c r="U47" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.78724949074</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46163.193042962965</v>
+        <v>46176.20176511574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="J48" s="5">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>26</v>
@@ -4342,19 +4330,19 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="R48" s="5">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="S48" s="11" t="s">
         <v>33</v>
@@ -4363,61 +4351,59 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.7872546412</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46176.20176511574</v>
+        <v>46177.202846782406</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I49" s="10"/>
+      <c r="J49" s="9">
+        <v>46176</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="O49" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="I49" s="9">
-        <v>46169</v>
-      </c>
-      <c r="J49" s="9">
-        <v>46175</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="O49" s="10" t="s">
+      <c r="P49" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="P49" s="10" t="s">
-        <v>184</v>
-      </c>
       <c r="Q49" s="9">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="R49" s="9">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="S49" s="11" t="s">
         <v>33</v>
@@ -4426,35 +4412,35 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.787260625</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46177.202846782406</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
-        <v>46176</v>
+        <v>46232</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4466,52 +4452,52 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="5">
-        <v>46176</v>
+        <v>46232</v>
       </c>
       <c r="R50" s="5">
-        <v>46176</v>
-      </c>
-      <c r="S50" s="11" t="s">
-        <v>33</v>
+        <v>46232</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.78727884259</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.93970905093</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4527,52 +4513,42 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="P51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>46232</v>
-      </c>
-      <c r="R51" s="9">
-        <v>46232</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>67</v>
-      </c>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.78728261574</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939574814816</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4588,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4604,31 +4580,27 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.787286527775</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.939575474535</v>
+        <v>46146.91453674769</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>190</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H53" s="10"/>
       <c r="I53" s="10"/>
-      <c r="J53" s="9">
-        <v>46232</v>
-      </c>
+      <c r="J53" s="10"/>
       <c r="K53" s="10" t="s">
         <v>26</v>
       </c>
@@ -4636,16 +4608,16 @@
         <v>26</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4658,24 +4630,30 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.787341759264</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46146.91453674769</v>
+        <v>46192.17325630787</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+        <v>198</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46190</v>
+      </c>
+      <c r="J54" s="5">
+        <v>46191</v>
+      </c>
       <c r="K54" s="6" t="s">
         <v>26</v>
       </c>
@@ -4683,51 +4661,59 @@
         <v>26</v>
       </c>
       <c r="M54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>46190</v>
+      </c>
+      <c r="R54" s="5">
+        <v>46191</v>
+      </c>
+      <c r="S54" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="N54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
+      <c r="U54" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.787345254634</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46192.17325630787</v>
+        <v>46193.182386307875</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="I55" s="9">
-        <v>46190</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="I55" s="10"/>
       <c r="J55" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="K55" s="10" t="s">
         <v>26</v>
@@ -4739,19 +4725,19 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="R55" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="S55" s="11" t="s">
         <v>33</v>
@@ -4760,35 +4746,37 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.787358877315</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46193.182386307875</v>
+        <v>46192.17324446759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="I56" s="6"/>
+        <v>199</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46190</v>
+      </c>
       <c r="J56" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
@@ -4800,19 +4788,19 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>207</v>
       </c>
       <c r="Q56" s="5">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="R56" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="S56" s="11" t="s">
         <v>33</v>
@@ -4821,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4829,11 +4817,11 @@
         <v>208</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.78735064815</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46192.17324446759</v>
+        <v>46193.18238616898</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>209</v>
@@ -4842,16 +4830,16 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="I57" s="9">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="J57" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="K57" s="10" t="s">
         <v>26</v>
@@ -4863,19 +4851,19 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>210</v>
       </c>
       <c r="Q57" s="9">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="R57" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="S57" s="11" t="s">
         <v>33</v>
@@ -4884,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4892,11 +4880,11 @@
         <v>211</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.79730351851</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.18238616898</v>
+        <v>46192.17323068287</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>212</v>
@@ -4905,16 +4893,16 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="J58" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
@@ -4926,19 +4914,19 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>213</v>
       </c>
       <c r="Q58" s="5">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="R58" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="S58" s="11" t="s">
         <v>33</v>
@@ -4947,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4955,29 +4943,29 @@
         <v>214</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.78735449074</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46192.17323068287</v>
+        <v>46193.182386203705</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="I59" s="9">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="J59" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -4989,19 +4977,19 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="9">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="R59" s="9">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="S59" s="11" t="s">
         <v>33</v>
@@ -5010,38 +4998,32 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.79750996528</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46193.182386203705</v>
+        <v>46146.91939417824</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46192</v>
-      </c>
-      <c r="J60" s="5">
-        <v>46192</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
       <c r="K60" s="6" t="s">
         <v>26</v>
       </c>
@@ -5049,56 +5031,52 @@
         <v>26</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q60" s="5">
-        <v>46192</v>
-      </c>
-      <c r="R60" s="5">
-        <v>46192</v>
-      </c>
-      <c r="S60" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.787364398144</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46146.91939417824</v>
+        <v>46190.16989362269</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>219</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I61" s="9">
+        <v>46195</v>
+      </c>
+      <c r="J61" s="9">
+        <v>46197</v>
+      </c>
       <c r="K61" s="10" t="s">
         <v>26</v>
       </c>
@@ -5106,45 +5084,55 @@
         <v>26</v>
       </c>
       <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>46195</v>
+      </c>
+      <c r="R61" s="9">
+        <v>46197</v>
+      </c>
+      <c r="S61" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="N61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+      <c r="U61" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.78736695602</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46190.16989362269</v>
+        <v>46146.941516493054</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5165,49 +5153,39 @@
         <v>219</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>46195</v>
-      </c>
-      <c r="R62" s="5">
-        <v>46197</v>
-      </c>
-      <c r="S62" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.79438380787</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46146.941516493054</v>
+        <v>46146.941513391204</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5225,7 +5203,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>229</v>
@@ -5244,29 +5222,29 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.79440119213</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46146.941513391204</v>
+        <v>46146.94141126158</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="J64" s="5">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5278,42 +5256,52 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+        <v>216</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46198</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46204</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>234</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.78737179398</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.94141126158</v>
+        <v>46146.941607465276</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5331,52 +5319,42 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="P65" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46198</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46204</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>67</v>
-      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.78737561342</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.941607465276</v>
+        <v>46146.941604074076</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5394,13 +5372,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="O66" s="6" t="s">
-        <v>238</v>
-      </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5410,32 +5388,30 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.78738193287</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46146.941604074076</v>
+        <v>46146.94140628472</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="I67" s="9">
-        <v>46198</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="I67" s="10"/>
       <c r="J67" s="9">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
@@ -5447,42 +5423,52 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+        <v>216</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46205</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46205</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T67" s="10">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.78740461805</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46146.94140628472</v>
+        <v>46146.941706412035</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5498,52 +5484,42 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>46205</v>
-      </c>
-      <c r="R68" s="5">
-        <v>46205</v>
-      </c>
-      <c r="S68" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.787408564815</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46146.941706412035</v>
+        <v>46146.94170292824</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5559,13 +5535,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5575,31 +5551,27 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.78741372685</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.94170292824</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>224</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="6"/>
-      <c r="J70" s="5">
-        <v>46205</v>
-      </c>
+      <c r="J70" s="6"/>
       <c r="K70" s="6" t="s">
         <v>26</v>
       </c>
@@ -5607,16 +5579,16 @@
         <v>26</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>242</v>
+        <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5626,27 +5598,31 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.78743457176</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46146.92121962963</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="10"/>
+        <v>198</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>199</v>
+      </c>
       <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
+      <c r="J71" s="9">
+        <v>46175</v>
+      </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
       </c>
@@ -5654,33 +5630,43 @@
         <v>26</v>
       </c>
       <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>46175</v>
+      </c>
+      <c r="R71" s="9">
+        <v>46175</v>
+      </c>
+      <c r="S71" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="N71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="10"/>
-      <c r="T71" s="10"/>
-      <c r="U71" s="10"/>
+      <c r="U71" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.787437465275</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46191.78551768519</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5689,14 +5675,14 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
-        <v>46175</v>
+        <v>46156</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5708,19 +5694,19 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>251</v>
       </c>
       <c r="Q72" s="5">
-        <v>46175</v>
+        <v>46156</v>
       </c>
       <c r="R72" s="5">
-        <v>46175</v>
+        <v>46156</v>
       </c>
       <c r="S72" s="11" t="s">
         <v>33</v>
@@ -5728,8 +5714,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>56</v>
+      <c r="U72" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5737,11 +5723,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.78744341435</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46157.18259200231</v>
+        <v>46192.17326015046</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>253</v>
@@ -5750,14 +5736,14 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
-        <v>46156</v>
+        <v>46191</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5769,19 +5755,19 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="9">
-        <v>46156</v>
+        <v>46191</v>
       </c>
       <c r="R73" s="9">
-        <v>46156</v>
+        <v>46191</v>
       </c>
       <c r="S73" s="11" t="s">
         <v>33</v>
@@ -5790,35 +5776,35 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.7874489699</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46192.17326015046</v>
+        <v>46146.94183069444</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
-        <v>46191</v>
+        <v>46218</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5830,28 +5816,28 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q74" s="5">
-        <v>46191</v>
+        <v>46218</v>
       </c>
       <c r="R74" s="5">
-        <v>46191</v>
-      </c>
-      <c r="S74" s="11" t="s">
-        <v>33</v>
+        <v>46218</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5859,28 +5845,24 @@
         <v>257</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.78746039352</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46146.94183069444</v>
+        <v>46146.93993140046</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>258</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>202</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="10"/>
       <c r="I75" s="10"/>
-      <c r="J75" s="9">
-        <v>46218</v>
-      </c>
+      <c r="J75" s="10"/>
       <c r="K75" s="10" t="s">
         <v>26</v>
       </c>
@@ -5888,56 +5870,52 @@
         <v>26</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>46218</v>
-      </c>
-      <c r="R75" s="9">
-        <v>46218</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>260</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.78750452546</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.93993140046</v>
+        <v>46146.94199042824</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>261</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I76" s="5">
+        <v>46219</v>
+      </c>
+      <c r="J76" s="5">
+        <v>46225</v>
+      </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
       </c>
@@ -5945,45 +5923,55 @@
         <v>26</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>26</v>
+        <v>258</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>262</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+        <v>258</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46219</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46225</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>263</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.787508912035</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.94199042824</v>
+        <v>46146.942057465276</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I77" s="9">
         <v>46219</v>
@@ -6004,49 +5992,39 @@
         <v>261</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46219</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46225</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.78752016203</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.942057465276</v>
+        <v>46146.942050451384</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I78" s="5">
         <v>46219</v>
@@ -6064,10 +6042,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="O78" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6080,32 +6058,30 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.78752439815</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46146.942050451384</v>
+        <v>46146.94198726852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I79" s="9">
-        <v>46219</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I79" s="10"/>
       <c r="J79" s="9">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -6117,42 +6093,52 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+        <v>258</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>46226</v>
+      </c>
+      <c r="R79" s="9">
+        <v>46226</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T79" s="10">
+        <v>0</v>
+      </c>
+      <c r="U79" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.78758131944</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46146.94198726852</v>
+        <v>46146.94212739583</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6168,52 +6154,42 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>269</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46226</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46226</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>271</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.78758657408</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46146.94212739583</v>
+        <v>46146.942124548616</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6229,13 +6205,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6245,30 +6221,32 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.787592939814</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.942124548616</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>193</v>
+        <v>274</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I82" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46227</v>
+      </c>
       <c r="J82" s="5">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6280,46 +6258,54 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>272</v>
+        <v>188</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+        <v>258</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>46227</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46227</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T82" s="6">
+        <v>0</v>
+      </c>
+      <c r="U82" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.78761755787</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46146.94198379629</v>
+        <v>46146.942214282404</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I83" s="9">
-        <v>46227</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I83" s="10"/>
       <c r="J83" s="9">
         <v>46227</v>
       </c>
@@ -6333,52 +6319,42 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q83" s="9">
-        <v>46227</v>
-      </c>
-      <c r="R83" s="9">
-        <v>46227</v>
-      </c>
-      <c r="S83" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.78762708334</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46146.942214282404</v>
+        <v>46146.94221188658</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6394,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6410,30 +6386,30 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.78763331019</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.94221188658</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>193</v>
+        <v>279</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
@@ -6445,42 +6421,52 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>279</v>
+        <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
-      <c r="T85" s="10"/>
-      <c r="U85" s="10"/>
+        <v>258</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>46230</v>
+      </c>
+      <c r="R85" s="9">
+        <v>46230</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T85" s="10">
+        <v>0</v>
+      </c>
+      <c r="U85" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.78769865741</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.941980902775</v>
+        <v>46146.9422950463</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6496,52 +6482,42 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q86" s="5">
-        <v>46230</v>
-      </c>
-      <c r="R86" s="5">
-        <v>46230</v>
-      </c>
-      <c r="S86" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>283</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.787703553244</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.9422950463</v>
+        <v>46146.94229197917</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6557,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>284</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6573,30 +6549,30 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.78770892361</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94229197917</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>193</v>
+        <v>286</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6608,42 +6584,52 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>287</v>
+        <v>188</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>258</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46231</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46231</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0</v>
+      </c>
+      <c r="U88" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.78773052084</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94197813657</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6659,52 +6645,42 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46231</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46231</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.78773511574</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237260417</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6720,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6736,30 +6712,30 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.78774035879</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94237009259</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -6771,46 +6747,56 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+        <v>292</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>46233</v>
+      </c>
+      <c r="R91" s="9">
+        <v>46233</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T91" s="10">
+        <v>0</v>
+      </c>
+      <c r="U91" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>293</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.787759479164</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94197326389</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -6822,52 +6808,42 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>46233</v>
-      </c>
-      <c r="R92" s="5">
-        <v>46233</v>
-      </c>
-      <c r="S92" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.78776425926</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244866898</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6883,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="O93" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6899,31 +6875,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.787768587965</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.94244559028</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="6"/>
-      <c r="J94" s="5">
-        <v>46232</v>
-      </c>
+      <c r="J94" s="6"/>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -6931,16 +6903,16 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>294</v>
+        <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>193</v>
+        <v>298</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>26</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6953,24 +6925,28 @@
         <v>299</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.78778571759</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9405634838</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>300</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>301</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>302</v>
+      </c>
       <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
+      <c r="J95" s="9">
+        <v>46234</v>
+      </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
       </c>
@@ -6978,45 +6954,55 @@
         <v>26</v>
       </c>
       <c r="M95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="O95" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q95" s="9">
+        <v>46234</v>
+      </c>
+      <c r="R95" s="9">
+        <v>46234</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T95" s="10">
         <v>0</v>
       </c>
-      <c r="N95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O95" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="P95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q95" s="10"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="10"/>
-      <c r="T95" s="10"/>
-      <c r="U95" s="10"/>
+      <c r="U95" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.78778912037</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.9429809375</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7035,49 +7021,39 @@
         <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>306</v>
+        <v>190</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46234</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46234</v>
-      </c>
-      <c r="S96" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.78779429398</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.942643194445</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7093,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7109,30 +7085,30 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.787798414356</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94264393518</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>304</v>
+        <v>76</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>305</v>
+        <v>76</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7144,42 +7120,52 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
+        <v>297</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>46237</v>
+      </c>
+      <c r="R98" s="5">
+        <v>46237</v>
+      </c>
+      <c r="S98" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T98" s="6">
+        <v>0</v>
+      </c>
+      <c r="U98" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.787814745374</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94289535879</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>312</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7195,52 +7181,42 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46237</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46237</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.78781900463</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285763889</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7256,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7272,30 +7248,30 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.787823148145</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.94285530093</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
@@ -7307,42 +7283,52 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
+        <v>297</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>46238</v>
+      </c>
+      <c r="R101" s="9">
+        <v>46238</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T101" s="10">
+        <v>0</v>
+      </c>
+      <c r="U101" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.787891527776</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.9431597338</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>318</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7358,52 +7344,42 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q102" s="5">
-        <v>46238</v>
-      </c>
-      <c r="R102" s="5">
-        <v>46238</v>
-      </c>
-      <c r="S102" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T102" s="6">
-        <v>0</v>
-      </c>
-      <c r="U102" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.78789762731</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94342792824</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7419,13 +7395,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7435,30 +7411,30 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.78790538195</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94346471065</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7470,42 +7446,52 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
+      <c r="Q104" s="5">
+        <v>46239</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46239</v>
+      </c>
+      <c r="S104" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0</v>
+      </c>
+      <c r="U104" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>323</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.787928171296</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94327527778</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7521,52 +7507,42 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46239</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46239</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="11" t="s">
-        <v>67</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.787934409724</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.94332239583</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7582,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7598,31 +7574,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.787939131944</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.943319872684</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>193</v>
+        <v>326</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>224</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="10"/>
       <c r="I107" s="10"/>
-      <c r="J107" s="9">
-        <v>46239</v>
-      </c>
+      <c r="J107" s="10"/>
       <c r="K107" s="10" t="s">
         <v>26</v>
       </c>
@@ -7630,16 +7602,16 @@
         <v>26</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7652,24 +7624,30 @@
         <v>328</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.787957974535</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94056351852</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>329</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
+        <v>330</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I108" s="5">
+        <v>46240</v>
+      </c>
+      <c r="J108" s="5">
+        <v>46248</v>
+      </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
       </c>
@@ -7677,45 +7655,55 @@
         <v>26</v>
       </c>
       <c r="M108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>46240</v>
+      </c>
+      <c r="R108" s="5">
+        <v>46248</v>
+      </c>
+      <c r="S108" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="N108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
+      <c r="U108" s="11" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.78796153935</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46146.94352958333</v>
+        <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>333</v>
+        <v>52</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="I109" s="9">
         <v>46240</v>
@@ -7733,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7748,76 +7736,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B110" s="5">
-        <v>46146.78796724537</v>
-      </c>
-      <c r="C110" s="6"/>
-      <c r="D110" s="5">
-        <v>46146.94358548611</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I110" s="5">
-        <v>46240</v>
-      </c>
-      <c r="J110" s="5">
-        <v>46248</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N110" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>46240</v>
-      </c>
-      <c r="R110" s="5">
-        <v>46248</v>
-      </c>
-      <c r="S110" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -738,7 +738,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>Media</t>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46190.16989362269</v>
+        <v>46197.16872233796</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>219</v>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46146.941516493054</v>
+        <v>46197.168706122684</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46146.941513391204</v>
+        <v>46197.16870811343</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>225</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46146.94141126158</v>
+        <v>46197.17484288194</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5270,8 +5270,8 @@
       <c r="R64" s="5">
         <v>46204</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>104</v>
+      <c r="S64" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46146.93993140046</v>
+        <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>258</v>
@@ -6063,9 +6063,11 @@
       <c r="B79" s="9">
         <v>46146.78758131944</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46197.58901480324</v>
+      </c>
       <c r="D79" s="9">
-        <v>46146.94198726852</v>
+        <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>267</v>
@@ -6111,10 +6113,10 @@
         <v>104</v>
       </c>
       <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="U79" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6124,9 +6126,11 @@
       <c r="B80" s="5">
         <v>46146.78758657408</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46197.58893424769</v>
+      </c>
       <c r="D80" s="5">
-        <v>46146.94212739583</v>
+        <v>46197.58893591435</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>190</v>
@@ -6175,9 +6179,11 @@
       <c r="B81" s="9">
         <v>46146.787592939814</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9">
+        <v>46197.58900142361</v>
+      </c>
       <c r="D81" s="9">
-        <v>46146.942124548616</v>
+        <v>46197.58900278935</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>190</v>
@@ -6291,7 +6297,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46146.942214282404</v>
+        <v>46197.588939629626</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>190</v>
@@ -6342,7 +6348,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46146.94221188658</v>
+        <v>46197.5890109375</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>190</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="335">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -234,94 +234,119 @@
     <t>propuesta motor OT 4309,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
+    <t>1214511240917258</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+        Calaje entre -5° y -6
+        Consumo estimado en fabrica 60 a 65Kw
+</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1214511155782245</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para el pedido 50001543, se tienen 2 ventiladores ZVN 1-9-75/2 para Zitrón Colombia (EMG):
+Alcance CHILE: TOBERA + REJILLA + VENTILADOR
+Alcance COLOMBIA:  VDF + FAR 90/100 + TIPO A 900 mm
+    Plano para fabricación:
+        Ventilador ZVN 1-9-75/2 con motor ZITRON - 350011
+        Alcance: Tobera, Rejilla, Ventilador.
+        Planos: CH1480
+    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+        Calaje entre -5° y -6
+        Consumo estimado en fabrica 60 a 65Kw
+    Datos eléctricos motor 75KW:
+        75 kW, 460 V, 60 Hz, IE3, IP-55
+        Considerar duplicado de placas benjamin.bustos@zitron.com
+    Tratamiento superficial estándar Zitrón:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214508463084760</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,propuesta Corte Laser OT 4309,propuesta motor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198865760</t>
+  </si>
+  <si>
+    <t>propuesta motor OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309,Propuesta compras:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214511240917258</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1214511155782245</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214508463084760</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4309,propuesta nucleo rodete OT 4309,propuesta Corte Laser OT 4309,propuesta motor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198865760</t>
-  </si>
-  <si>
-    <t>propuesta motor OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309,Propuesta compras:</t>
+    <t>1214511142378696</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4309</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142378716</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4309</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>1214511155793305</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4309</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214511142378696</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4309</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142378716</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4309</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>1214511155793305</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4309</t>
   </si>
   <si>
     <t>1214511198886127</t>
@@ -2068,9 +2093,11 @@
       <c r="B10" s="5">
         <v>46146.78687210648</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46197.64946785879</v>
+      </c>
       <c r="D10" s="5">
-        <v>46196.86770065972</v>
+        <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2105,8 +2132,12 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -2115,9 +2146,11 @@
       <c r="B11" s="9">
         <v>46146.787010162036</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46197.64821641204</v>
+      </c>
       <c r="D11" s="9">
-        <v>46196.86770065972</v>
+        <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2165,25 +2198,27 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="5">
         <v>46146.7870155787</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.648967245375</v>
+      </c>
       <c r="D12" s="5">
-        <v>46196.867700752315</v>
+        <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2204,7 +2239,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2216,7 +2251,7 @@
         <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46147</v>
@@ -2228,25 +2263,27 @@
         <v>33</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="9">
         <v>46146.787021400465</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46197.64945164352</v>
+      </c>
       <c r="D13" s="9">
-        <v>46196.86770050926</v>
+        <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2267,7 +2304,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2291,10 +2328,10 @@
         <v>33</v>
       </c>
       <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2353,7 +2390,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46169.85883516204</v>
+        <v>46197.64823577546</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2403,7 +2440,7 @@
       <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="U15" s="12" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2416,7 +2453,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.858846030096</v>
+        <v>46197.64899046296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2449,7 +2486,7 @@
         <v>65</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>73</v>
@@ -2466,7 +2503,7 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="U16" s="12" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2481,7 +2518,7 @@
         <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46191.78471304398</v>
+        <v>46197.64899056713</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2514,7 +2551,7 @@
         <v>65</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>77</v>
@@ -2531,8 +2568,8 @@
       <c r="T17" s="10">
         <v>1</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>27</v>
+      <c r="U17" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2595,12 +2632,12 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
@@ -2610,7 +2647,7 @@
         <v>46178.1703008912</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2643,7 +2680,7 @@
         <v>82</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2658,12 +2695,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
@@ -2673,7 +2710,7 @@
         <v>46178.170302349536</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2706,7 +2743,7 @@
         <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2721,12 +2758,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
@@ -2736,7 +2773,7 @@
         <v>46178.17030399306</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2769,7 +2806,7 @@
         <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2784,12 +2821,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2799,7 +2836,7 @@
         <v>46195.92635412037</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2823,7 +2860,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2836,7 +2873,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2846,16 +2883,16 @@
         <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2873,13 +2910,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2894,12 +2931,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2909,16 +2946,16 @@
         <v>46169.858957557866</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2936,29 +2973,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -2968,16 +3005,16 @@
         <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -2995,29 +3032,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3029,16 +3066,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3056,13 +3093,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3082,7 +3119,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3094,16 +3131,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3121,29 +3158,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3155,16 +3192,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3182,29 +3219,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3214,16 +3251,16 @@
         <v>46191.18668917824</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3241,13 +3278,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3262,12 +3299,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3277,16 +3314,16 @@
         <v>46169.859063067124</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3304,29 +3341,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3336,16 +3373,16 @@
         <v>46190.16874317129</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3363,29 +3400,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3395,16 +3432,16 @@
         <v>46169.859122187496</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3422,29 +3459,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3454,16 +3491,16 @@
         <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3481,13 +3518,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3502,12 +3539,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3517,16 +3554,16 @@
         <v>46182.168845277774</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3544,29 +3581,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3576,16 +3613,16 @@
         <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3603,29 +3640,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3635,16 +3672,16 @@
         <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3662,10 +3699,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3683,12 +3720,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3698,16 +3735,16 @@
         <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3725,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3741,7 +3778,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3751,16 +3788,16 @@
         <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3778,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3794,7 +3831,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3804,16 +3841,16 @@
         <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3831,10 +3868,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3846,18 +3883,18 @@
         <v>46217</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3867,16 +3904,16 @@
         <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3894,13 +3931,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3910,7 +3947,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -3920,16 +3957,16 @@
         <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -3947,13 +3984,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3963,7 +4000,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -3973,16 +4010,16 @@
         <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3998,10 +4035,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4014,7 +4051,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4024,16 +4061,16 @@
         <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4051,10 +4088,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4072,12 +4109,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4087,16 +4124,16 @@
         <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4114,13 +4151,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4130,7 +4167,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4140,16 +4177,16 @@
         <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4167,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4183,7 +4220,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4193,7 +4230,7 @@
         <v>46146.834545844904</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4217,7 +4254,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4230,26 +4267,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46163.193042962965</v>
+        <v>46197.64947251158</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4267,13 +4304,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4287,13 +4324,13 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="11" t="s">
+      <c r="U47" s="12" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4303,16 +4340,16 @@
         <v>46176.20176511574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4330,13 +4367,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4351,12 +4388,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4372,10 +4409,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4391,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4412,12 +4449,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4427,16 +4464,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4452,10 +4489,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4467,18 +4504,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4488,16 +4525,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4513,13 +4550,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4529,7 +4566,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4539,16 +4576,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4564,13 +4601,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4580,7 +4617,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4590,7 +4627,7 @@
         <v>46146.91453674769</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4614,7 +4651,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4627,7 +4664,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4637,16 +4674,16 @@
         <v>46192.17325630787</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4664,13 +4701,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4685,12 +4722,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4700,16 +4737,16 @@
         <v>46193.182386307875</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4725,13 +4762,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4746,12 +4783,12 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4761,16 +4798,16 @@
         <v>46192.17324446759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4788,13 +4825,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4809,12 +4846,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4824,16 +4861,16 @@
         <v>46193.18238616898</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4851,13 +4888,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4872,12 +4909,12 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -4887,16 +4924,16 @@
         <v>46192.17323068287</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -4914,13 +4951,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4935,12 +4972,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -4950,16 +4987,16 @@
         <v>46193.182386203705</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -4977,13 +5014,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -4998,12 +5035,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5013,7 +5050,7 @@
         <v>46146.91939417824</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5037,7 +5074,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5050,7 +5087,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5060,16 +5097,16 @@
         <v>46197.16872233796</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5087,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5102,18 +5139,18 @@
         <v>46197</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5123,16 +5160,16 @@
         <v>46197.168706122684</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5150,13 +5187,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5166,7 +5203,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5176,16 +5213,16 @@
         <v>46197.16870811343</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5203,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5219,7 +5256,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5229,16 +5266,16 @@
         <v>46197.17484288194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5256,13 +5293,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5271,18 +5308,18 @@
         <v>46204</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5292,16 +5329,16 @@
         <v>46146.941607465276</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5319,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5335,7 +5372,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5345,16 +5382,16 @@
         <v>46146.941604074076</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5372,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5388,7 +5425,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5398,16 +5435,16 @@
         <v>46146.94140628472</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5423,13 +5460,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5438,18 +5475,18 @@
         <v>46205</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5459,16 +5496,16 @@
         <v>46146.941706412035</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5484,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5500,7 +5537,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5510,16 +5547,16 @@
         <v>46146.94170292824</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5535,13 +5572,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5551,7 +5588,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5561,7 +5598,7 @@
         <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5585,7 +5622,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5598,7 +5635,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5608,16 +5645,16 @@
         <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5633,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5654,12 +5691,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5669,16 +5706,16 @@
         <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5694,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5715,12 +5752,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5730,16 +5767,16 @@
         <v>46192.17326015046</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5755,13 +5792,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5776,12 +5813,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5791,16 +5828,16 @@
         <v>46146.94183069444</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5816,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5831,18 +5868,18 @@
         <v>46218</v>
       </c>
       <c r="S74" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -5852,7 +5889,7 @@
         <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -5876,7 +5913,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5889,7 +5926,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -5899,7 +5936,7 @@
         <v>46146.94199042824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5926,13 +5963,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -5941,18 +5978,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -5962,7 +5999,7 @@
         <v>46146.942057465276</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5989,10 +6026,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6005,7 +6042,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6015,7 +6052,7 @@
         <v>46146.942050451384</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6042,10 +6079,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6058,7 +6095,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6070,7 +6107,7 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6095,13 +6132,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6110,7 +6147,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6121,7 +6158,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6133,7 +6170,7 @@
         <v>46197.58893591435</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6158,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6174,7 +6211,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6186,7 +6223,7 @@
         <v>46197.58900278935</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6211,13 +6248,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6227,7 +6264,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6237,7 +6274,7 @@
         <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6264,13 +6301,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6279,18 +6316,18 @@
         <v>46227</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6300,7 +6337,7 @@
         <v>46197.588939629626</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6325,13 +6362,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6341,7 +6378,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6351,7 +6388,7 @@
         <v>46197.5890109375</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6376,13 +6413,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6392,7 +6429,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6402,7 +6439,7 @@
         <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6427,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6442,18 +6479,18 @@
         <v>46230</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6463,7 +6500,7 @@
         <v>46146.9422950463</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6488,13 +6525,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6504,7 +6541,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6514,7 +6551,7 @@
         <v>46146.94229197917</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6539,13 +6576,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6555,7 +6592,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6565,7 +6602,7 @@
         <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6590,13 +6627,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6605,18 +6642,18 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6626,7 +6663,7 @@
         <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6651,13 +6688,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6667,7 +6704,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6677,7 +6714,7 @@
         <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6702,13 +6739,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6718,7 +6755,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6728,7 +6765,7 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6753,13 +6790,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6768,18 +6805,18 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6789,7 +6826,7 @@
         <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6814,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6830,7 +6867,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -6840,7 +6877,7 @@
         <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6865,13 +6902,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6881,7 +6918,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -6891,7 +6928,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -6915,7 +6952,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -6928,7 +6965,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -6938,16 +6975,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6963,13 +7000,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -6978,18 +7015,18 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -6999,16 +7036,16 @@
         <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7024,13 +7061,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7040,7 +7077,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7050,16 +7087,16 @@
         <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7075,13 +7112,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7091,7 +7128,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7101,7 +7138,7 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7126,13 +7163,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7141,18 +7178,18 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7162,7 +7199,7 @@
         <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7187,13 +7224,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7203,7 +7240,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7213,7 +7250,7 @@
         <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7238,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7254,7 +7291,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7264,16 +7301,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7289,13 +7326,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7304,18 +7341,18 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7325,16 +7362,16 @@
         <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7350,13 +7387,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7366,7 +7403,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7376,16 +7413,16 @@
         <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7401,13 +7438,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7417,7 +7454,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7427,16 +7464,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7452,13 +7489,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7467,18 +7504,18 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7488,16 +7525,16 @@
         <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7513,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7529,7 +7566,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7539,16 +7576,16 @@
         <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7564,13 +7601,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7580,7 +7617,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7590,7 +7627,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7614,7 +7651,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7627,7 +7664,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7637,16 +7674,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7664,13 +7701,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7679,18 +7716,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7700,7 +7737,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7727,13 +7764,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7742,13 +7779,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1723,13 +1723,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.7868665162</v>
+        <v>46146.62019984954</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.872097534724</v>
+        <v>46175.70543086805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.872111840275</v>
+        <v>46175.70544517361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1776,13 +1776,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.78699289352</v>
+        <v>46146.620326226854</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.8720717824</v>
+        <v>46175.70540511574</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87209800926</v>
+        <v>46175.70543134259</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1839,13 +1839,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.786996319446</v>
+        <v>46146.62032965278</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87207239583</v>
+        <v>46175.70540572917</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87209802083</v>
+        <v>46175.70543135417</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1902,13 +1902,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.78699966436</v>
+        <v>46146.620332997685</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8720727662</v>
+        <v>46175.705406099536</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.872098576394</v>
+        <v>46175.70543190972</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1965,13 +1965,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.7870025</v>
+        <v>46146.62033583333</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872073136576</v>
+        <v>46175.705406469904</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87209884259</v>
+        <v>46175.70543217592</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2028,13 +2028,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.787006631945</v>
+        <v>46146.62033996527</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87207366899</v>
+        <v>46175.705407002315</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87209942129</v>
+        <v>46175.70543275463</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2091,13 +2091,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.78687210648</v>
+        <v>46146.620205439816</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.64946785879</v>
+        <v>46197.482801192135</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.6494803588</v>
+        <v>46197.48281369213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2144,13 +2144,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.787010162036</v>
+        <v>46146.62034349537</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.64821641204</v>
+        <v>46197.48154974537</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.64823298611</v>
+        <v>46197.481566319446</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2209,13 +2209,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.7870155787</v>
+        <v>46146.62034891204</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.648967245375</v>
+        <v>46197.482300578704</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.64898236111</v>
+        <v>46197.48231569445</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2274,13 +2274,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.787021400465</v>
+        <v>46146.620354733794</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.64945164352</v>
+        <v>46197.48278497685</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.6494675463</v>
+        <v>46197.48280087963</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2339,11 +2339,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.7868765162</v>
+        <v>46146.62020984954</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.784095717594</v>
+        <v>46191.61742905092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2386,11 +2386,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.7870415625</v>
+        <v>46146.620374895836</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.64823577546</v>
+        <v>46197.4815691088</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2449,11 +2449,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.78704743055</v>
+        <v>46146.62038076389</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.64899046296</v>
+        <v>46197.4823237963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2512,13 +2512,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.78705320602</v>
+        <v>46146.62038653935</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.784087754626</v>
+        <v>46191.61742108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.64899056713</v>
+        <v>46197.48232390046</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2577,11 +2577,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.78705905093</v>
+        <v>46146.620392384255</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.17029900463</v>
+        <v>46178.00363233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2640,11 +2640,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.78706952547</v>
+        <v>46146.620402858796</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.1703008912</v>
+        <v>46178.00363422454</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2703,11 +2703,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.78707340278</v>
+        <v>46146.62040673611</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.170302349536</v>
+        <v>46178.00363568287</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2766,11 +2766,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.78707737269</v>
+        <v>46146.62041070602</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.17030399306</v>
+        <v>46178.00363732639</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2829,11 +2829,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.786881064814</v>
+        <v>46146.62021439815</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.92635412037</v>
+        <v>46195.759687453705</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2876,11 +2876,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.78708193287</v>
+        <v>46146.6204152662</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.858700868055</v>
+        <v>46169.69203420139</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2939,11 +2939,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.78708679398</v>
+        <v>46146.620420127314</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.858957557866</v>
+        <v>46169.6922908912</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2998,11 +2998,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.78709203703</v>
+        <v>46146.62042537037</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.85897216435</v>
+        <v>46169.69230549769</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3057,13 +3057,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.78709759259</v>
+        <v>46146.62043092593</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.92634351852</v>
+        <v>46195.759676851856</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.92635861111</v>
+        <v>46195.75969194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3122,13 +3122,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.78710313658</v>
+        <v>46146.62043646991</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.92632717593</v>
+        <v>46195.759660509255</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.92632960648</v>
+        <v>46195.75966293982</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3183,13 +3183,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.787108969904</v>
+        <v>46146.62044230324</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.78550167824</v>
+        <v>46191.61883501157</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.9263380787</v>
+        <v>46195.75967141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3244,11 +3244,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.78711427083</v>
+        <v>46146.62044760417</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.18668917824</v>
+        <v>46191.02002251157</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3307,11 +3307,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.78711935185</v>
+        <v>46146.62045268518</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.859063067124</v>
+        <v>46169.69239640047</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3366,11 +3366,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.78712466435</v>
+        <v>46146.620457997684</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.16874317129</v>
+        <v>46190.00207650463</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3425,11 +3425,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.78712987268</v>
+        <v>46146.62046320602</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.859122187496</v>
+        <v>46169.69245552083</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3484,11 +3484,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.78718802083</v>
+        <v>46146.62052135417</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.18189784722</v>
+        <v>46190.01523118056</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3547,11 +3547,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.78719326389</v>
+        <v>46146.620526597224</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.168845277774</v>
+        <v>46182.00217861111</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3606,11 +3606,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.78719805555</v>
+        <v>46146.62053138889</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.16864960648</v>
+        <v>46189.001982939815</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3665,11 +3665,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.78721570602</v>
+        <v>46146.62054903935</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.18189791667</v>
+        <v>46190.01523125</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3728,11 +3728,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.787218854166</v>
+        <v>46146.6205521875</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.168843391206</v>
+        <v>46182.002176724534</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3781,11 +3781,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.78722290509</v>
+        <v>46146.62055623843</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.16864146991</v>
+        <v>46189.001974803235</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3834,11 +3834,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.78722673611</v>
+        <v>46146.620560069445</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.85880202547</v>
+        <v>46169.6921353588</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3897,11 +3897,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.787229884256</v>
+        <v>46146.62056321759</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.169576643515</v>
+        <v>46185.00290997685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3950,11 +3950,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.787233807874</v>
+        <v>46146.6205671412</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.85930840278</v>
+        <v>46169.69264173611</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4003,11 +4003,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.92145594908</v>
+        <v>46146.75478928241</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859332141205</v>
+        <v>46169.69266547453</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4054,11 +4054,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.78723741898</v>
+        <v>46146.62057075232</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.1818981713</v>
+        <v>46190.01523150463</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4117,11 +4117,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.78724063658</v>
+        <v>46146.62057396991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.16884665509</v>
+        <v>46182.00217998843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4170,11 +4170,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.78724467593</v>
+        <v>46146.62057800926</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.168642951394</v>
+        <v>46189.00197628472</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4223,11 +4223,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.78688576389</v>
+        <v>46146.620219097225</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46146.834545844904</v>
+        <v>46146.66787917824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4270,11 +4270,11 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.78724949074</v>
+        <v>46146.62058282408</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46197.64947251158</v>
+        <v>46197.482805844906</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4333,11 +4333,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.7872546412</v>
+        <v>46146.62058797454</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46176.20176511574</v>
+        <v>46176.03509844907</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4396,11 +4396,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.787260625</v>
+        <v>46146.62059395833</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46177.202846782406</v>
+        <v>46177.03618011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4457,11 +4457,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.78727884259</v>
+        <v>46146.620612175924</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.93970905093</v>
+        <v>46146.77304238426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4518,11 +4518,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.78728261574</v>
+        <v>46146.620615949076</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.939574814816</v>
+        <v>46146.77290814815</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4569,11 +4569,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.787286527775</v>
+        <v>46146.62061986111</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939575474535</v>
+        <v>46146.77290880787</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4620,11 +4620,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.787341759264</v>
+        <v>46146.62067509259</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.91453674769</v>
+        <v>46146.74787008102</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -4667,11 +4667,11 @@
         <v>197</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.787345254634</v>
+        <v>46146.62067858796</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46192.17325630787</v>
+        <v>46192.006589641205</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>198</v>
@@ -4730,11 +4730,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.787358877315</v>
+        <v>46146.62069221065</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46193.182386307875</v>
+        <v>46193.015719641204</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>203</v>
@@ -4791,11 +4791,11 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.78735064815</v>
+        <v>46146.620683981484</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.17324446759</v>
+        <v>46192.00657780093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4854,11 +4854,11 @@
         <v>209</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.79730351851</v>
+        <v>46146.630636851856</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46193.18238616898</v>
+        <v>46193.01571950231</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>210</v>
@@ -4917,11 +4917,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.78735449074</v>
+        <v>46146.62068782408</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.17323068287</v>
+        <v>46192.00656401621</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4980,11 +4980,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.79750996528</v>
+        <v>46146.63084329861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46193.182386203705</v>
+        <v>46193.01571953704</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>214</v>
@@ -5043,11 +5043,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.787364398144</v>
+        <v>46146.62069773149</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46146.91939417824</v>
+        <v>46146.75272751157</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5090,11 +5090,11 @@
         <v>219</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.78736695602</v>
+        <v>46146.62070028935</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46197.16872233796</v>
+        <v>46197.0020556713</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>220</v>
@@ -5153,11 +5153,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.79438380787</v>
+        <v>46146.62771714121</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46197.168706122684</v>
+        <v>46197.00203945602</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5206,11 +5206,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.79440119213</v>
+        <v>46146.627734525464</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46197.16870811343</v>
+        <v>46197.00204144676</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>226</v>
@@ -5259,11 +5259,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.78737179398</v>
+        <v>46146.620705127316</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.17484288194</v>
+        <v>46197.00817621528</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5322,11 +5322,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.78737561342</v>
+        <v>46146.620708946764</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.941607465276</v>
+        <v>46146.77494079861</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>226</v>
@@ -5375,11 +5375,11 @@
         <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.78738193287</v>
+        <v>46146.6207152662</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.941604074076</v>
+        <v>46146.774937407405</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5428,11 +5428,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.78740461805</v>
+        <v>46146.62073795139</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46146.94140628472</v>
+        <v>46146.77473961806</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>240</v>
@@ -5489,11 +5489,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.787408564815</v>
+        <v>46146.62074189815</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46146.941706412035</v>
+        <v>46146.77503974537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -5540,11 +5540,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.78741372685</v>
+        <v>46146.62074706018</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46146.94170292824</v>
+        <v>46146.77503626158</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>226</v>
@@ -5591,11 +5591,11 @@
         <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.78743457176</v>
+        <v>46146.62076790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.92121962963</v>
+        <v>46146.754552962964</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5638,11 +5638,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.787437465275</v>
+        <v>46146.62077079861</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.78551768519</v>
+        <v>46191.61885101852</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>248</v>
@@ -5699,11 +5699,11 @@
         <v>250</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.78744341435</v>
+        <v>46146.62077674769</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.18259200231</v>
+        <v>46157.01592533565</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5760,11 +5760,11 @@
         <v>253</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.7874489699</v>
+        <v>46146.620782303246</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.17326015046</v>
+        <v>46192.00659348379</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>254</v>
@@ -5821,11 +5821,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.78746039352</v>
+        <v>46146.62079372685</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.94183069444</v>
+        <v>46146.77516402778</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5882,11 +5882,11 @@
         <v>258</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.78750452546</v>
+        <v>46146.6208378588</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.58902260417</v>
+        <v>46197.422355937495</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>259</v>
@@ -5929,11 +5929,11 @@
         <v>261</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.787508912035</v>
+        <v>46146.62084224537</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.94199042824</v>
+        <v>46146.77532376157</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>262</v>
@@ -5992,11 +5992,11 @@
         <v>264</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.78752016203</v>
+        <v>46146.62085349537</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.942057465276</v>
+        <v>46146.77539079861</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>191</v>
@@ -6045,11 +6045,11 @@
         <v>266</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.78752439815</v>
+        <v>46146.62085773148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.942050451384</v>
+        <v>46146.77538378473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>191</v>
@@ -6098,13 +6098,13 @@
         <v>267</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.78758131944</v>
+        <v>46146.620914652776</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.58901480324</v>
+        <v>46197.42234813658</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.5890270949</v>
+        <v>46197.422360428245</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>268</v>
@@ -6161,13 +6161,13 @@
         <v>269</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.78758657408</v>
+        <v>46146.62091990741</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.58893424769</v>
+        <v>46197.422267581016</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.58893591435</v>
+        <v>46197.42226924769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>191</v>
@@ -6214,13 +6214,13 @@
         <v>272</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.787592939814</v>
+        <v>46146.62092627315</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.58900142361</v>
+        <v>46197.42233475695</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.58900278935</v>
+        <v>46197.42233612269</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>191</v>
@@ -6267,11 +6267,11 @@
         <v>274</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.78761755787</v>
+        <v>46146.6209508912</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.94198379629</v>
+        <v>46146.77531712963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>275</v>
@@ -6330,11 +6330,11 @@
         <v>276</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.78762708334</v>
+        <v>46146.620960416665</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.588939629626</v>
+        <v>46197.42227296296</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>191</v>
@@ -6381,11 +6381,11 @@
         <v>278</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.78763331019</v>
+        <v>46146.62096664352</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.5890109375</v>
+        <v>46197.42234427083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>191</v>
@@ -6432,11 +6432,11 @@
         <v>279</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.78769865741</v>
+        <v>46146.62103199074</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.941980902775</v>
+        <v>46146.77531423611</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>280</v>
@@ -6493,11 +6493,11 @@
         <v>281</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.787703553244</v>
+        <v>46146.62103688657</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.9422950463</v>
+        <v>46146.77562837963</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6544,11 +6544,11 @@
         <v>284</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.78770892361</v>
+        <v>46146.62104225694</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.94229197917</v>
+        <v>46146.7756253125</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>191</v>
@@ -6595,11 +6595,11 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.78773052084</v>
+        <v>46146.62106385417</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94197813657</v>
+        <v>46146.77531146991</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>287</v>
@@ -6656,11 +6656,11 @@
         <v>288</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.78773511574</v>
+        <v>46146.62106844907</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94237260417</v>
+        <v>46146.7757059375</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>191</v>
@@ -6707,11 +6707,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.78774035879</v>
+        <v>46146.621073692135</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237009259</v>
+        <v>46146.77570342593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>191</v>
@@ -6758,11 +6758,11 @@
         <v>291</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.787759479164</v>
+        <v>46146.6210928125</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94197326389</v>
+        <v>46146.77530659722</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>292</v>
@@ -6819,11 +6819,11 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.78776425926</v>
+        <v>46146.62109759259</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94244866898</v>
+        <v>46146.77578200231</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -6870,11 +6870,11 @@
         <v>296</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.787768587965</v>
+        <v>46146.62110192129</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244559028</v>
+        <v>46146.775778923606</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -6921,11 +6921,11 @@
         <v>297</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.78778571759</v>
+        <v>46146.62111905093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.9405634838</v>
+        <v>46146.77389681713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>298</v>
@@ -6968,11 +6968,11 @@
         <v>300</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.78778912037</v>
+        <v>46146.621122453704</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9429809375</v>
+        <v>46146.77631427083</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>301</v>
@@ -7029,11 +7029,11 @@
         <v>305</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.78779429398</v>
+        <v>46146.62112762731</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.942643194445</v>
+        <v>46146.77597652777</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7080,11 +7080,11 @@
         <v>307</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.787798414356</v>
+        <v>46146.621131747685</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.94264393518</v>
+        <v>46146.77597726852</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7131,11 +7131,11 @@
         <v>309</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.787814745374</v>
+        <v>46146.6211480787</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94289535879</v>
+        <v>46146.77622869213</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>310</v>
@@ -7192,11 +7192,11 @@
         <v>311</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.78781900463</v>
+        <v>46146.62115233796</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94285763889</v>
+        <v>46146.77619097222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>191</v>
@@ -7243,11 +7243,11 @@
         <v>313</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.787823148145</v>
+        <v>46146.62115648148</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285530093</v>
+        <v>46146.77618863426</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7294,11 +7294,11 @@
         <v>315</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.787891527776</v>
+        <v>46146.62122486111</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.9431597338</v>
+        <v>46146.776493067126</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>316</v>
@@ -7355,11 +7355,11 @@
         <v>317</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.78789762731</v>
+        <v>46146.62123096065</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.94342792824</v>
+        <v>46146.77676126157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7406,11 +7406,11 @@
         <v>319</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.78790538195</v>
+        <v>46146.62123871528</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94346471065</v>
+        <v>46146.77679804398</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7457,11 +7457,11 @@
         <v>321</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.787928171296</v>
+        <v>46146.621261504624</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94327527778</v>
+        <v>46146.77660861111</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>322</v>
@@ -7518,11 +7518,11 @@
         <v>324</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.787934409724</v>
+        <v>46146.62126774306</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94332239583</v>
+        <v>46146.77665572916</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7569,11 +7569,11 @@
         <v>325</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.787939131944</v>
+        <v>46146.62127246527</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.943319872684</v>
+        <v>46146.77665320602</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7620,11 +7620,11 @@
         <v>326</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.787957974535</v>
+        <v>46146.62129130787</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.94056351852</v>
+        <v>46146.77389685185</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>327</v>
@@ -7667,11 +7667,11 @@
         <v>329</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.78796153935</v>
+        <v>46146.62129487269</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94352958333</v>
+        <v>46146.77686291667</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>330</v>
@@ -7730,11 +7730,11 @@
         <v>333</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.78796724537</v>
+        <v>46146.6213005787</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.86770128472</v>
+        <v>46196.701034618054</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>334</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -622,28 +622,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199035045</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214511240985139</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199035045</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214511240985139</t>
   </si>
   <si>
     <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
@@ -1723,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.62019984954</v>
+        <v>46146.7868665162</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70543086805</v>
+        <v>46175.872097534724</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70544517361</v>
+        <v>46175.872111840275</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1776,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.620326226854</v>
+        <v>46146.78699289352</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70540511574</v>
+        <v>46175.8720717824</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70543134259</v>
+        <v>46175.87209800926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1839,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.62032965278</v>
+        <v>46146.786996319446</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70540572917</v>
+        <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70543135417</v>
+        <v>46175.87209802083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1902,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.620332997685</v>
+        <v>46146.78699966436</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.705406099536</v>
+        <v>46175.8720727662</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70543190972</v>
+        <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1965,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.62033583333</v>
+        <v>46146.7870025</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.705406469904</v>
+        <v>46175.872073136576</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70543217592</v>
+        <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2028,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.62033996527</v>
+        <v>46146.787006631945</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.705407002315</v>
+        <v>46175.87207366899</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70543275463</v>
+        <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2091,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.620205439816</v>
+        <v>46146.78687210648</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.482801192135</v>
+        <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.48281369213</v>
+        <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2144,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.62034349537</v>
+        <v>46146.787010162036</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.48154974537</v>
+        <v>46197.64821641204</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.481566319446</v>
+        <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2209,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.62034891204</v>
+        <v>46146.7870155787</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.482300578704</v>
+        <v>46197.648967245375</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.48231569445</v>
+        <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2274,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.620354733794</v>
+        <v>46146.787021400465</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.48278497685</v>
+        <v>46197.64945164352</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.48280087963</v>
+        <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2339,11 +2345,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.62020984954</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.61742905092</v>
+        <v>46191.784095717594</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2386,11 +2392,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.620374895836</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.4815691088</v>
+        <v>46197.64823577546</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2449,11 +2455,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.62038076389</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.4823237963</v>
+        <v>46197.64899046296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2512,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.62038653935</v>
+        <v>46146.78705320602</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.61742108796</v>
+        <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.48232390046</v>
+        <v>46197.64899056713</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2577,11 +2583,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.620392384255</v>
+        <v>46146.78705905093</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.00363233796</v>
+        <v>46178.17029900463</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2640,11 +2646,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.620402858796</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.00363422454</v>
+        <v>46178.1703008912</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2703,11 +2709,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.62040673611</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.00363568287</v>
+        <v>46178.170302349536</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2766,11 +2772,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.62041070602</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.00363732639</v>
+        <v>46178.17030399306</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2829,11 +2835,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.62021439815</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.759687453705</v>
+        <v>46195.92635412037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2876,11 +2882,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.6204152662</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.69203420139</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2939,11 +2945,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.620420127314</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.6922908912</v>
+        <v>46169.858957557866</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2998,11 +3004,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.62042537037</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.69230549769</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3057,13 +3063,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.62043092593</v>
+        <v>46146.78709759259</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.759676851856</v>
+        <v>46195.92634351852</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.75969194445</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3122,13 +3128,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.62043646991</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.759660509255</v>
+        <v>46195.92632717593</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.75966293982</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3183,13 +3189,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.62044230324</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.61883501157</v>
+        <v>46191.78550167824</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.75967141204</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3244,11 +3250,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.62044760417</v>
+        <v>46146.78711427083</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.02002251157</v>
+        <v>46191.18668917824</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3307,11 +3313,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.62045268518</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.69239640047</v>
+        <v>46169.859063067124</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3366,11 +3372,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.620457997684</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.00207650463</v>
+        <v>46190.16874317129</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3425,11 +3431,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.62046320602</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.69245552083</v>
+        <v>46197.71192840278</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3484,11 +3490,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.62052135417</v>
+        <v>46146.78718802083</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.01523118056</v>
+        <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3547,11 +3553,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.620526597224</v>
+        <v>46146.78719326389</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.00217861111</v>
+        <v>46182.168845277774</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3606,11 +3612,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.62053138889</v>
+        <v>46146.78719805555</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.001982939815</v>
+        <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3665,11 +3671,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.62054903935</v>
+        <v>46146.78721570602</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.01523125</v>
+        <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3728,11 +3734,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.6205521875</v>
+        <v>46146.787218854166</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.002176724534</v>
+        <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3781,11 +3787,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.62055623843</v>
+        <v>46146.78722290509</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.001974803235</v>
+        <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3834,11 +3840,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.620560069445</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.6921353588</v>
+        <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3897,11 +3903,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.62056321759</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.00290997685</v>
+        <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3950,11 +3956,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.6205671412</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69264173611</v>
+        <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4003,11 +4009,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.75478928241</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69266547453</v>
+        <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4054,11 +4060,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.62057075232</v>
+        <v>46146.78723741898</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.01523150463</v>
+        <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4117,11 +4123,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.62057396991</v>
+        <v>46146.78724063658</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.00217998843</v>
+        <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4170,11 +4176,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.62057800926</v>
+        <v>46146.78724467593</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.00197628472</v>
+        <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4223,11 +4229,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.620219097225</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46146.66787917824</v>
+        <v>46197.71096577546</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4270,11 +4276,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.62058282408</v>
-      </c>
-      <c r="C47" s="10"/>
+        <v>46146.78724949074</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46197.710958564814</v>
+      </c>
       <c r="D47" s="9">
-        <v>46197.482805844906</v>
+        <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4322,10 +4330,10 @@
         <v>33</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4333,11 +4341,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.62058797454</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46176.03509844907</v>
+        <v>46197.7115691088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4396,11 +4404,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.62059395833</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46177.03618011574</v>
+        <v>46197.71167261574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4409,10 +4417,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4434,7 +4442,7 @@
         <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4454,26 +4462,26 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.620612175924</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.77304238426</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4492,7 +4500,7 @@
         <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4515,26 +4523,26 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.620615949076</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.77290814815</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4550,13 +4558,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4566,26 +4574,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.62061986111</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.77290880787</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4601,13 +4609,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4617,17 +4625,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.62067509259</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.74787008102</v>
+        <v>46146.91453674769</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4651,7 +4659,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4664,26 +4672,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.62067858796</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46192.006589641205</v>
+        <v>46192.17325630787</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4701,13 +4709,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4727,17 +4735,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.62069221065</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46193.015719641204</v>
+        <v>46193.182386307875</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4762,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4788,26 +4796,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.620683981484</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.00657780093</v>
+        <v>46192.17324446759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4825,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4851,17 +4859,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.630636851856</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46193.01571950231</v>
+        <v>46193.18238616898</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4888,13 +4896,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4914,26 +4922,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.62068782408</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.00656401621</v>
+        <v>46192.17323068287</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -4951,13 +4959,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -4977,17 +4985,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.63084329861</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46193.01571953704</v>
+        <v>46193.182386203705</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5014,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5040,17 +5048,17 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.62069773149</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46146.75272751157</v>
+        <v>46146.91939417824</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5074,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5087,26 +5095,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.62070028935</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46197.0020556713</v>
+        <v>46197.16872233796</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5124,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5139,7 +5147,7 @@
         <v>46197</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5150,26 +5158,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.62771714121</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46197.00203945602</v>
+        <v>46197.168706122684</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5187,13 +5195,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5203,26 +5211,26 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.627734525464</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46197.00204144676</v>
+        <v>46197.16870811343</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5240,13 +5248,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5256,26 +5264,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.620705127316</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.00817621528</v>
+        <v>46197.17484288194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5293,13 +5301,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5308,7 +5316,7 @@
         <v>46204</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5319,26 +5327,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.620708946764</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.77494079861</v>
+        <v>46146.941607465276</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5356,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5372,26 +5380,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.6207152662</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.774937407405</v>
+        <v>46146.941604074076</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5409,13 +5417,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5425,26 +5433,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.62073795139</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46146.77473961806</v>
+        <v>46146.94140628472</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5460,13 +5468,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5486,26 +5494,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.62074189815</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46146.77503974537</v>
+        <v>46146.941706412035</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5521,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5537,26 +5545,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.62074706018</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46146.77503626158</v>
+        <v>46146.94170292824</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5572,13 +5580,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5588,17 +5596,17 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.62076790509</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.754552962964</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5622,7 +5630,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5635,26 +5643,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.62077079861</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.61885101852</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5670,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>116</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5696,26 +5704,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.62077674769</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.01592533565</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5731,13 +5739,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5757,26 +5765,26 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.620782303246</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.00659348379</v>
+        <v>46192.17326015046</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5792,13 +5800,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>125</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5818,26 +5826,26 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.62079372685</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.77516402778</v>
+        <v>46146.94183069444</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5853,13 +5861,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>157</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5879,17 +5887,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.6208378588</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.422355937495</v>
+        <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -5913,7 +5921,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5926,17 +5934,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.62084224537</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.77532376157</v>
+        <v>46146.94199042824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5963,13 +5971,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -5989,17 +5997,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.62085349537</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.77539079861</v>
+        <v>46146.942057465276</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6026,10 +6034,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6042,17 +6050,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.62085773148</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.77538378473</v>
+        <v>46146.942050451384</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6079,10 +6087,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6095,19 +6103,19 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.620914652776</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.42234813658</v>
+        <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.422360428245</v>
+        <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6132,13 +6140,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6158,19 +6166,19 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.62091990741</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.422267581016</v>
+        <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42226924769</v>
+        <v>46197.58893591435</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6195,13 +6203,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6211,19 +6219,19 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.62092627315</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42233475695</v>
+        <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.42233612269</v>
+        <v>46197.58900278935</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6248,13 +6256,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6264,17 +6272,17 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.6209508912</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.77531712963</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6301,13 +6309,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6327,17 +6335,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.620960416665</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.42227296296</v>
+        <v>46197.588939629626</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6362,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6378,17 +6386,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.62096664352</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.42234427083</v>
+        <v>46197.5890109375</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6413,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6429,17 +6437,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.62103199074</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.77531423611</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6464,13 +6472,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6490,17 +6498,17 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.62103688657</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.77562837963</v>
+        <v>46146.9422950463</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6525,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6541,17 +6549,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.62104225694</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.7756253125</v>
+        <v>46146.94229197917</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6576,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="P87" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="P87" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6592,17 +6600,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.62106385417</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.77531146991</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6627,13 +6635,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6653,17 +6661,17 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.62106844907</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.7757059375</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6688,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6704,17 +6712,17 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.621073692135</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.77570342593</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6739,13 +6747,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6755,17 +6763,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.6210928125</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.77530659722</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6790,13 +6798,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6816,17 +6824,17 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.62109759259</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.77578200231</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6851,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6867,17 +6875,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.62110192129</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.775778923606</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6902,13 +6910,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6918,17 +6926,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.62111905093</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.77389681713</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -6952,7 +6960,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -6965,26 +6973,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.621122453704</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.77631427083</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7000,13 +7008,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7026,26 +7034,26 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.62112762731</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.77597652777</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7061,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7077,26 +7085,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.621131747685</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.77597726852</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7112,13 +7120,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7128,17 +7136,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.6211480787</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.77622869213</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7163,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7189,17 +7197,17 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.62115233796</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.77619097222</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7224,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7240,17 +7248,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.62115648148</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.77618863426</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7275,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7291,26 +7299,26 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.62122486111</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.776493067126</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7326,13 +7334,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7352,26 +7360,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.62123096065</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.77676126157</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7387,13 +7395,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7403,26 +7411,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.62123871528</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.77679804398</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7438,13 +7446,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7454,26 +7462,26 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.621261504624</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.77660861111</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7489,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7515,26 +7523,26 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.62126774306</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.77665572916</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7550,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7566,26 +7574,26 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.62127246527</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.77665320602</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7601,13 +7609,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7617,17 +7625,17 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.62129130787</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.77389685185</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7651,7 +7659,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7664,26 +7672,26 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.62129487269</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.77686291667</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7701,13 +7709,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7727,17 +7735,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.6213005787</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.701034618054</v>
+        <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7764,13 +7772,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46146.94140628472</v>
+        <v>46197.83476153935</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5449,10 +5449,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46146.941706412035</v>
+        <v>46197.83481741898</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5510,10 +5510,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46146.94170292824</v>
+        <v>46197.83486086805</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>228</v>
@@ -5561,10 +5561,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -772,37 +772,37 @@
     <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
+    <t>1214508463084766</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214508463084767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245155134</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214508463084766</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214508463084767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT  4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245155134</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511245155149</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46197.16872233796</v>
+        <v>46198.20551991898</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5146,8 +5146,8 @@
       <c r="R61" s="9">
         <v>46197</v>
       </c>
-      <c r="S61" s="12" t="s">
-        <v>226</v>
+      <c r="S61" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5168,7 +5168,7 @@
         <v>46197.168706122684</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5198,10 +5198,10 @@
         <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5211,7 +5211,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5221,7 +5221,7 @@
         <v>46197.16870811343</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5251,10 +5251,10 @@
         <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5274,7 +5274,7 @@
         <v>46197.17484288194</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5304,7 +5304,7 @@
         <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>219</v>
@@ -5316,7 +5316,7 @@
         <v>46204</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5337,7 +5337,7 @@
         <v>46146.941607465276</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5364,7 +5364,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>238</v>
@@ -5390,7 +5390,7 @@
         <v>46146.941604074076</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5417,7 +5417,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>238</v>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46197.83476153935</v>
+        <v>46198.185393287036</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5482,8 +5482,8 @@
       <c r="R67" s="9">
         <v>46205</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>105</v>
+      <c r="S67" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5504,7 +5504,7 @@
         <v>46197.83481741898</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5555,7 +5555,7 @@
         <v>46197.83486086805</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.7868665162</v>
+        <v>46146.62019984954</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.872097534724</v>
+        <v>46175.70543086805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.872111840275</v>
+        <v>46175.70544517361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.78699289352</v>
+        <v>46146.620326226854</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.8720717824</v>
+        <v>46175.70540511574</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87209800926</v>
+        <v>46175.70543134259</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.786996319446</v>
+        <v>46146.62032965278</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87207239583</v>
+        <v>46175.70540572917</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87209802083</v>
+        <v>46175.70543135417</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.78699966436</v>
+        <v>46146.620332997685</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8720727662</v>
+        <v>46175.705406099536</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.872098576394</v>
+        <v>46175.70543190972</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.7870025</v>
+        <v>46146.62033583333</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872073136576</v>
+        <v>46175.705406469904</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87209884259</v>
+        <v>46175.70543217592</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.787006631945</v>
+        <v>46146.62033996527</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87207366899</v>
+        <v>46175.705407002315</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87209942129</v>
+        <v>46175.70543275463</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.78687210648</v>
+        <v>46146.620205439816</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.64946785879</v>
+        <v>46197.482801192135</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.6494803588</v>
+        <v>46197.48281369213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.787010162036</v>
+        <v>46146.62034349537</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.64821641204</v>
+        <v>46197.48154974537</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.64823298611</v>
+        <v>46197.481566319446</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.7870155787</v>
+        <v>46146.62034891204</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.648967245375</v>
+        <v>46197.482300578704</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.64898236111</v>
+        <v>46197.48231569445</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.787021400465</v>
+        <v>46146.620354733794</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.64945164352</v>
+        <v>46197.48278497685</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.6494675463</v>
+        <v>46197.48280087963</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,11 +2345,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.7868765162</v>
+        <v>46146.62020984954</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.784095717594</v>
+        <v>46191.61742905092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2392,11 +2392,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.7870415625</v>
+        <v>46146.620374895836</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.64823577546</v>
+        <v>46197.4815691088</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2455,11 +2455,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.78704743055</v>
+        <v>46146.62038076389</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.64899046296</v>
+        <v>46197.4823237963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2518,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.78705320602</v>
+        <v>46146.62038653935</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.784087754626</v>
+        <v>46191.61742108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.64899056713</v>
+        <v>46197.48232390046</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2583,11 +2583,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.78705905093</v>
+        <v>46146.620392384255</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.17029900463</v>
+        <v>46178.00363233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2646,11 +2646,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.78706952547</v>
+        <v>46146.620402858796</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.1703008912</v>
+        <v>46178.00363422454</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2709,11 +2709,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.78707340278</v>
+        <v>46146.62040673611</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.170302349536</v>
+        <v>46178.00363568287</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2772,11 +2772,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.78707737269</v>
+        <v>46146.62041070602</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.17030399306</v>
+        <v>46178.00363732639</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2835,11 +2835,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.786881064814</v>
+        <v>46146.62021439815</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.92635412037</v>
+        <v>46195.759687453705</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2882,11 +2882,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.78708193287</v>
+        <v>46146.6204152662</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.858700868055</v>
+        <v>46169.69203420139</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2945,11 +2945,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.78708679398</v>
+        <v>46146.620420127314</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.858957557866</v>
+        <v>46169.6922908912</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3004,11 +3004,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.78709203703</v>
+        <v>46146.62042537037</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.85897216435</v>
+        <v>46169.69230549769</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3063,13 +3063,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.78709759259</v>
+        <v>46146.62043092593</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.92634351852</v>
+        <v>46195.759676851856</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.92635861111</v>
+        <v>46195.75969194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3128,13 +3128,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.78710313658</v>
+        <v>46146.62043646991</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.92632717593</v>
+        <v>46195.759660509255</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.92632960648</v>
+        <v>46195.75966293982</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3189,13 +3189,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.787108969904</v>
+        <v>46146.62044230324</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.78550167824</v>
+        <v>46191.61883501157</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.9263380787</v>
+        <v>46195.75967141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3250,11 +3250,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.78711427083</v>
+        <v>46146.62044760417</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.18668917824</v>
+        <v>46191.02002251157</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3313,11 +3313,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.78711935185</v>
+        <v>46146.62045268518</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.859063067124</v>
+        <v>46169.69239640047</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3372,11 +3372,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.78712466435</v>
+        <v>46146.620457997684</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.16874317129</v>
+        <v>46190.00207650463</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3431,11 +3431,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.78712987268</v>
+        <v>46146.62046320602</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46197.71192840278</v>
+        <v>46197.545261736115</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3490,11 +3490,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.78718802083</v>
+        <v>46146.62052135417</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.18189784722</v>
+        <v>46190.01523118056</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3553,11 +3553,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.78719326389</v>
+        <v>46146.620526597224</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.168845277774</v>
+        <v>46182.00217861111</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3612,11 +3612,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.78719805555</v>
+        <v>46146.62053138889</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.16864960648</v>
+        <v>46189.001982939815</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3671,11 +3671,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.78721570602</v>
+        <v>46146.62054903935</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.18189791667</v>
+        <v>46190.01523125</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3734,11 +3734,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.787218854166</v>
+        <v>46146.6205521875</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.168843391206</v>
+        <v>46182.002176724534</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3787,11 +3787,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.78722290509</v>
+        <v>46146.62055623843</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.16864146991</v>
+        <v>46189.001974803235</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3840,11 +3840,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.78722673611</v>
+        <v>46146.620560069445</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.85880202547</v>
+        <v>46169.6921353588</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3903,11 +3903,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.787229884256</v>
+        <v>46146.62056321759</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.169576643515</v>
+        <v>46185.00290997685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3956,11 +3956,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.787233807874</v>
+        <v>46146.6205671412</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.85930840278</v>
+        <v>46169.69264173611</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4009,11 +4009,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.92145594908</v>
+        <v>46146.75478928241</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859332141205</v>
+        <v>46169.69266547453</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4060,11 +4060,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.78723741898</v>
+        <v>46146.62057075232</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.1818981713</v>
+        <v>46190.01523150463</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4123,11 +4123,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.78724063658</v>
+        <v>46146.62057396991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.16884665509</v>
+        <v>46182.00217998843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4176,11 +4176,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.78724467593</v>
+        <v>46146.62057800926</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.168642951394</v>
+        <v>46189.00197628472</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4229,11 +4229,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.78688576389</v>
+        <v>46146.620219097225</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.71096577546</v>
+        <v>46197.54429910879</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4276,13 +4276,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.78724949074</v>
+        <v>46146.62058282408</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.710958564814</v>
+        <v>46197.54429189815</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.711020393515</v>
+        <v>46197.54435372685</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4341,11 +4341,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.7872546412</v>
+        <v>46146.62058797454</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.7115691088</v>
+        <v>46197.544902442125</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4404,11 +4404,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.787260625</v>
+        <v>46146.62059395833</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.71167261574</v>
+        <v>46197.545005949076</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4465,11 +4465,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.78727884259</v>
+        <v>46146.620612175924</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.93970905093</v>
+        <v>46146.77304238426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4526,11 +4526,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.78728261574</v>
+        <v>46146.620615949076</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.939574814816</v>
+        <v>46146.77290814815</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4577,11 +4577,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.787286527775</v>
+        <v>46146.62061986111</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939575474535</v>
+        <v>46146.77290880787</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4628,11 +4628,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.787341759264</v>
+        <v>46146.62067509259</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.91453674769</v>
+        <v>46146.74787008102</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4675,11 +4675,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.787345254634</v>
+        <v>46146.62067858796</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46192.17325630787</v>
+        <v>46192.006589641205</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4738,11 +4738,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.787358877315</v>
+        <v>46146.62069221065</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46193.182386307875</v>
+        <v>46193.015719641204</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4799,11 +4799,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.78735064815</v>
+        <v>46146.620683981484</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.17324446759</v>
+        <v>46192.00657780093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4862,11 +4862,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.79730351851</v>
+        <v>46146.630636851856</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46193.18238616898</v>
+        <v>46193.01571950231</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4925,11 +4925,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.78735449074</v>
+        <v>46146.62068782408</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.17323068287</v>
+        <v>46192.00656401621</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4988,11 +4988,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.79750996528</v>
+        <v>46146.63084329861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46193.182386203705</v>
+        <v>46193.01571953704</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5051,11 +5051,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.787364398144</v>
+        <v>46146.62069773149</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46146.91939417824</v>
+        <v>46146.75272751157</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5098,11 +5098,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.78736695602</v>
+        <v>46146.62070028935</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.20551991898</v>
+        <v>46198.038853252314</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5161,11 +5161,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.79438380787</v>
+        <v>46146.62771714121</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46197.168706122684</v>
+        <v>46197.00203945602</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5214,11 +5214,11 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.79440119213</v>
+        <v>46146.627734525464</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46197.16870811343</v>
+        <v>46197.00204144676</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5267,11 +5267,11 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.78737179398</v>
+        <v>46146.620705127316</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.17484288194</v>
+        <v>46197.00817621528</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5330,11 +5330,11 @@
         <v>237</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.78737561342</v>
+        <v>46146.620708946764</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.941607465276</v>
+        <v>46146.77494079861</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5383,11 +5383,11 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.78738193287</v>
+        <v>46146.6207152662</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.941604074076</v>
+        <v>46146.774937407405</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5436,11 +5436,11 @@
         <v>241</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.78740461805</v>
+        <v>46146.62073795139</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.185393287036</v>
+        <v>46198.01872662037</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5497,11 +5497,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.787408564815</v>
+        <v>46146.62074189815</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.83481741898</v>
+        <v>46197.66815075232</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5548,11 +5548,11 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.78741372685</v>
+        <v>46146.62074706018</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.83486086805</v>
+        <v>46197.66819420139</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5599,11 +5599,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.78743457176</v>
+        <v>46146.62076790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.92121962963</v>
+        <v>46146.754552962964</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5646,11 +5646,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.787437465275</v>
+        <v>46146.62077079861</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.78551768519</v>
+        <v>46191.61885101852</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5707,11 +5707,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.78744341435</v>
+        <v>46146.62077674769</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.18259200231</v>
+        <v>46157.01592533565</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5768,11 +5768,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.7874489699</v>
+        <v>46146.620782303246</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.17326015046</v>
+        <v>46192.00659348379</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5829,11 +5829,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.78746039352</v>
+        <v>46146.62079372685</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.94183069444</v>
+        <v>46146.77516402778</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5890,11 +5890,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.78750452546</v>
+        <v>46146.6208378588</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.58902260417</v>
+        <v>46197.422355937495</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -5937,11 +5937,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.787508912035</v>
+        <v>46146.62084224537</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.94199042824</v>
+        <v>46146.77532376157</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6000,11 +6000,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.78752016203</v>
+        <v>46146.62085349537</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.942057465276</v>
+        <v>46146.77539079861</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6053,11 +6053,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.78752439815</v>
+        <v>46146.62085773148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.942050451384</v>
+        <v>46146.77538378473</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6106,13 +6106,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.78758131944</v>
+        <v>46146.620914652776</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.58901480324</v>
+        <v>46197.42234813658</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.5890270949</v>
+        <v>46197.422360428245</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6169,13 +6169,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.78758657408</v>
+        <v>46146.62091990741</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.58893424769</v>
+        <v>46197.422267581016</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.58893591435</v>
+        <v>46197.42226924769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6222,13 +6222,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.787592939814</v>
+        <v>46146.62092627315</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.58900142361</v>
+        <v>46197.42233475695</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.58900278935</v>
+        <v>46197.42233612269</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6275,11 +6275,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.78761755787</v>
+        <v>46146.6209508912</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.94198379629</v>
+        <v>46146.77531712963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6338,11 +6338,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.78762708334</v>
+        <v>46146.620960416665</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.588939629626</v>
+        <v>46197.42227296296</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6389,11 +6389,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.78763331019</v>
+        <v>46146.62096664352</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.5890109375</v>
+        <v>46197.42234427083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6440,11 +6440,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.78769865741</v>
+        <v>46146.62103199074</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.941980902775</v>
+        <v>46146.77531423611</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6501,11 +6501,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.787703553244</v>
+        <v>46146.62103688657</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.9422950463</v>
+        <v>46146.77562837963</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6552,11 +6552,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.78770892361</v>
+        <v>46146.62104225694</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.94229197917</v>
+        <v>46146.7756253125</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6603,11 +6603,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.78773052084</v>
+        <v>46146.62106385417</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94197813657</v>
+        <v>46146.77531146991</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6664,11 +6664,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.78773511574</v>
+        <v>46146.62106844907</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94237260417</v>
+        <v>46146.7757059375</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6715,11 +6715,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.78774035879</v>
+        <v>46146.621073692135</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237009259</v>
+        <v>46146.77570342593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6766,11 +6766,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.787759479164</v>
+        <v>46146.6210928125</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94197326389</v>
+        <v>46146.77530659722</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6827,11 +6827,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.78776425926</v>
+        <v>46146.62109759259</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94244866898</v>
+        <v>46146.77578200231</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6878,11 +6878,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.787768587965</v>
+        <v>46146.62110192129</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244559028</v>
+        <v>46146.775778923606</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6929,11 +6929,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.78778571759</v>
+        <v>46146.62111905093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.9405634838</v>
+        <v>46146.77389681713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -6976,11 +6976,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.78778912037</v>
+        <v>46146.621122453704</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9429809375</v>
+        <v>46146.77631427083</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7037,11 +7037,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.78779429398</v>
+        <v>46146.62112762731</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.942643194445</v>
+        <v>46146.77597652777</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7088,11 +7088,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.787798414356</v>
+        <v>46146.621131747685</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.94264393518</v>
+        <v>46146.77597726852</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7139,11 +7139,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.787814745374</v>
+        <v>46146.6211480787</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94289535879</v>
+        <v>46146.77622869213</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7200,11 +7200,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.78781900463</v>
+        <v>46146.62115233796</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94285763889</v>
+        <v>46146.77619097222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7251,11 +7251,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.787823148145</v>
+        <v>46146.62115648148</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285530093</v>
+        <v>46146.77618863426</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7302,11 +7302,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.787891527776</v>
+        <v>46146.62122486111</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.9431597338</v>
+        <v>46146.776493067126</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7363,11 +7363,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.78789762731</v>
+        <v>46146.62123096065</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.94342792824</v>
+        <v>46146.77676126157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7414,11 +7414,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.78790538195</v>
+        <v>46146.62123871528</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94346471065</v>
+        <v>46146.77679804398</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7465,11 +7465,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.787928171296</v>
+        <v>46146.621261504624</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94327527778</v>
+        <v>46146.77660861111</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7526,11 +7526,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.787934409724</v>
+        <v>46146.62126774306</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94332239583</v>
+        <v>46146.77665572916</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7577,11 +7577,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.787939131944</v>
+        <v>46146.62127246527</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.943319872684</v>
+        <v>46146.77665320602</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7628,11 +7628,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.787957974535</v>
+        <v>46146.62129130787</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.94056351852</v>
+        <v>46146.77389685185</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7675,11 +7675,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.78796153935</v>
+        <v>46146.62129487269</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94352958333</v>
+        <v>46146.77686291667</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7738,11 +7738,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.78796724537</v>
+        <v>46146.6213005787</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.86770128472</v>
+        <v>46196.701034618054</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.62019984954</v>
+        <v>46146.7868665162</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70543086805</v>
+        <v>46175.872097534724</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70544517361</v>
+        <v>46175.872111840275</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.620326226854</v>
+        <v>46146.78699289352</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70540511574</v>
+        <v>46175.8720717824</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70543134259</v>
+        <v>46175.87209800926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.62032965278</v>
+        <v>46146.786996319446</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70540572917</v>
+        <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70543135417</v>
+        <v>46175.87209802083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.620332997685</v>
+        <v>46146.78699966436</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.705406099536</v>
+        <v>46175.8720727662</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70543190972</v>
+        <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.62033583333</v>
+        <v>46146.7870025</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.705406469904</v>
+        <v>46175.872073136576</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70543217592</v>
+        <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.62033996527</v>
+        <v>46146.787006631945</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.705407002315</v>
+        <v>46175.87207366899</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70543275463</v>
+        <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.620205439816</v>
+        <v>46146.78687210648</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.482801192135</v>
+        <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.48281369213</v>
+        <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.62034349537</v>
+        <v>46146.787010162036</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.48154974537</v>
+        <v>46197.64821641204</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.481566319446</v>
+        <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.62034891204</v>
+        <v>46146.7870155787</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.482300578704</v>
+        <v>46197.648967245375</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.48231569445</v>
+        <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.620354733794</v>
+        <v>46146.787021400465</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.48278497685</v>
+        <v>46197.64945164352</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.48280087963</v>
+        <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,11 +2345,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.62020984954</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.61742905092</v>
+        <v>46191.784095717594</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2392,11 +2392,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.620374895836</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.4815691088</v>
+        <v>46197.64823577546</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2455,11 +2455,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.62038076389</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.4823237963</v>
+        <v>46197.64899046296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2518,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.62038653935</v>
+        <v>46146.78705320602</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.61742108796</v>
+        <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.48232390046</v>
+        <v>46197.64899056713</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2583,11 +2583,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.620392384255</v>
+        <v>46146.78705905093</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.00363233796</v>
+        <v>46178.17029900463</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2646,11 +2646,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.620402858796</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.00363422454</v>
+        <v>46178.1703008912</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2709,11 +2709,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.62040673611</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.00363568287</v>
+        <v>46178.170302349536</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2772,11 +2772,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.62041070602</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.00363732639</v>
+        <v>46178.17030399306</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2835,11 +2835,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.62021439815</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.759687453705</v>
+        <v>46195.92635412037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2882,11 +2882,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.6204152662</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.69203420139</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2945,11 +2945,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.620420127314</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.6922908912</v>
+        <v>46169.858957557866</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3004,11 +3004,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.62042537037</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.69230549769</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3063,13 +3063,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.62043092593</v>
+        <v>46146.78709759259</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.759676851856</v>
+        <v>46195.92634351852</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.75969194445</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3128,13 +3128,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.62043646991</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.759660509255</v>
+        <v>46195.92632717593</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.75966293982</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3189,13 +3189,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.62044230324</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.61883501157</v>
+        <v>46191.78550167824</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.75967141204</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3250,11 +3250,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.62044760417</v>
+        <v>46146.78711427083</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.02002251157</v>
+        <v>46191.18668917824</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3313,11 +3313,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.62045268518</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.69239640047</v>
+        <v>46169.859063067124</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3372,11 +3372,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.620457997684</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.00207650463</v>
+        <v>46190.16874317129</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3431,11 +3431,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.62046320602</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46197.545261736115</v>
+        <v>46197.71192840278</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3490,11 +3490,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.62052135417</v>
+        <v>46146.78718802083</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.01523118056</v>
+        <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3553,11 +3553,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.620526597224</v>
+        <v>46146.78719326389</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.00217861111</v>
+        <v>46182.168845277774</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3612,11 +3612,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.62053138889</v>
+        <v>46146.78719805555</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.001982939815</v>
+        <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3671,11 +3671,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.62054903935</v>
+        <v>46146.78721570602</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.01523125</v>
+        <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3734,11 +3734,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.6205521875</v>
+        <v>46146.787218854166</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.002176724534</v>
+        <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3787,11 +3787,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.62055623843</v>
+        <v>46146.78722290509</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.001974803235</v>
+        <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3840,11 +3840,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.620560069445</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.6921353588</v>
+        <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3903,11 +3903,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.62056321759</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.00290997685</v>
+        <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3956,11 +3956,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.6205671412</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69264173611</v>
+        <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4009,11 +4009,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.75478928241</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69266547453</v>
+        <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4060,11 +4060,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.62057075232</v>
+        <v>46146.78723741898</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.01523150463</v>
+        <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4123,11 +4123,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.62057396991</v>
+        <v>46146.78724063658</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.00217998843</v>
+        <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4176,11 +4176,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.62057800926</v>
+        <v>46146.78724467593</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.00197628472</v>
+        <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4229,11 +4229,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.620219097225</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.54429910879</v>
+        <v>46197.71096577546</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4276,13 +4276,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.62058282408</v>
+        <v>46146.78724949074</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.54429189815</v>
+        <v>46197.710958564814</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.54435372685</v>
+        <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4341,11 +4341,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.62058797454</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.544902442125</v>
+        <v>46197.7115691088</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4404,11 +4404,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.62059395833</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.545005949076</v>
+        <v>46197.71167261574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4465,11 +4465,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.620612175924</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.77304238426</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4526,11 +4526,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.620615949076</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.77290814815</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4577,11 +4577,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.62061986111</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.77290880787</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4628,11 +4628,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.62067509259</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.74787008102</v>
+        <v>46146.91453674769</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4675,11 +4675,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.62067858796</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46192.006589641205</v>
+        <v>46192.17325630787</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4738,11 +4738,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.62069221065</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46193.015719641204</v>
+        <v>46193.182386307875</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4799,11 +4799,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.620683981484</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.00657780093</v>
+        <v>46192.17324446759</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4862,11 +4862,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.630636851856</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46193.01571950231</v>
+        <v>46193.18238616898</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4925,11 +4925,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.62068782408</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.00656401621</v>
+        <v>46192.17323068287</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4988,11 +4988,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.63084329861</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46193.01571953704</v>
+        <v>46193.182386203705</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5051,11 +5051,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.62069773149</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46146.75272751157</v>
+        <v>46146.91939417824</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5098,11 +5098,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.62070028935</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.038853252314</v>
+        <v>46198.20551991898</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5161,11 +5161,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.62771714121</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46197.00203945602</v>
+        <v>46197.168706122684</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5214,11 +5214,11 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.627734525464</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46197.00204144676</v>
+        <v>46197.16870811343</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5267,11 +5267,11 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.620705127316</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.00817621528</v>
+        <v>46197.17484288194</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5330,11 +5330,11 @@
         <v>237</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.620708946764</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46146.77494079861</v>
+        <v>46146.941607465276</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5383,11 +5383,11 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.6207152662</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46146.774937407405</v>
+        <v>46146.941604074076</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5436,11 +5436,11 @@
         <v>241</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.62073795139</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.01872662037</v>
+        <v>46198.185393287036</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5497,11 +5497,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.62074189815</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.66815075232</v>
+        <v>46197.83481741898</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5548,11 +5548,11 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.62074706018</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.66819420139</v>
+        <v>46197.83486086805</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5599,11 +5599,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.62076790509</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.754552962964</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5646,11 +5646,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.62077079861</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.61885101852</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5707,11 +5707,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.62077674769</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.01592533565</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5768,11 +5768,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.620782303246</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.00659348379</v>
+        <v>46192.17326015046</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5829,11 +5829,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.62079372685</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.77516402778</v>
+        <v>46146.94183069444</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5890,11 +5890,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.6208378588</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.422355937495</v>
+        <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -5937,11 +5937,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.62084224537</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.77532376157</v>
+        <v>46146.94199042824</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6000,11 +6000,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.62085349537</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.77539079861</v>
+        <v>46146.942057465276</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6053,11 +6053,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.62085773148</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.77538378473</v>
+        <v>46146.942050451384</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6106,13 +6106,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.620914652776</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.42234813658</v>
+        <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.422360428245</v>
+        <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6169,13 +6169,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.62091990741</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.422267581016</v>
+        <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42226924769</v>
+        <v>46197.58893591435</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6222,13 +6222,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.62092627315</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42233475695</v>
+        <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.42233612269</v>
+        <v>46197.58900278935</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6275,11 +6275,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.6209508912</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.77531712963</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6338,11 +6338,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.620960416665</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.42227296296</v>
+        <v>46197.588939629626</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6389,11 +6389,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.62096664352</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.42234427083</v>
+        <v>46197.5890109375</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6440,11 +6440,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.62103199074</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.77531423611</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6501,11 +6501,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.62103688657</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.77562837963</v>
+        <v>46146.9422950463</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6552,11 +6552,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.62104225694</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.7756253125</v>
+        <v>46146.94229197917</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6603,11 +6603,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.62106385417</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.77531146991</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6664,11 +6664,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.62106844907</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.7757059375</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6715,11 +6715,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.621073692135</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.77570342593</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6766,11 +6766,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.6210928125</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.77530659722</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6827,11 +6827,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.62109759259</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.77578200231</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6878,11 +6878,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.62110192129</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.775778923606</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6929,11 +6929,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.62111905093</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.77389681713</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -6976,11 +6976,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.621122453704</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.77631427083</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7037,11 +7037,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.62112762731</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.77597652777</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7088,11 +7088,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.621131747685</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.77597726852</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7139,11 +7139,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.6211480787</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.77622869213</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7200,11 +7200,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.62115233796</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.77619097222</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7251,11 +7251,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.62115648148</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.77618863426</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7302,11 +7302,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.62122486111</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.776493067126</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7363,11 +7363,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.62123096065</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.77676126157</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7414,11 +7414,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.62123871528</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.77679804398</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7465,11 +7465,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.621261504624</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.77660861111</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7526,11 +7526,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.62126774306</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.77665572916</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7577,11 +7577,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.62127246527</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.77665320602</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7628,11 +7628,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.62129130787</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.77389685185</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7675,11 +7675,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.62129487269</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.77686291667</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7738,11 +7738,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.6213005787</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.701034618054</v>
+        <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46197.71192840278</v>
+        <v>46198.71236186342</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.7115691088</v>
+        <v>46198.71406938657</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46197.71167261574</v>
+        <v>46198.71808170139</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.64823577546</v>
+        <v>46198.80549762731</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46146.91939417824</v>
+        <v>46198.89404733796</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5100,9 +5100,11 @@
       <c r="B61" s="9">
         <v>46146.78736695602</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46198.893461747684</v>
+      </c>
       <c r="D61" s="9">
-        <v>46198.20551991898</v>
+        <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5150,10 +5152,10 @@
         <v>33</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5163,9 +5165,11 @@
       <c r="B62" s="5">
         <v>46146.79438380787</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46198.89361300926</v>
+      </c>
       <c r="D62" s="5">
-        <v>46197.168706122684</v>
+        <v>46198.89361449074</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5216,9 +5220,11 @@
       <c r="B63" s="9">
         <v>46146.79440119213</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46198.89383822917</v>
+      </c>
       <c r="D63" s="9">
-        <v>46197.16870811343</v>
+        <v>46198.89383956019</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5269,9 +5275,11 @@
       <c r="B64" s="5">
         <v>46146.78737179398</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46198.8940372338</v>
+      </c>
       <c r="D64" s="5">
-        <v>46197.17484288194</v>
+        <v>46198.894050752315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5319,10 +5327,10 @@
         <v>236</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5332,9 +5340,11 @@
       <c r="B65" s="9">
         <v>46146.78737561342</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46198.89402209491</v>
+      </c>
       <c r="D65" s="9">
-        <v>46146.941607465276</v>
+        <v>46198.894024050926</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5385,9 +5395,11 @@
       <c r="B66" s="5">
         <v>46146.78738193287</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46198.893706874995</v>
+      </c>
       <c r="D66" s="5">
-        <v>46146.941604074076</v>
+        <v>46198.893844606486</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5440,7 +5452,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.185393287036</v>
+        <v>46198.894457766204</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5501,7 +5513,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.83481741898</v>
+        <v>46198.89403201389</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5552,7 +5564,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.83486086805</v>
+        <v>46198.89371428241</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46198.80549762731</v>
+        <v>46199.810681828705</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46146.91453674769</v>
+        <v>46200.68378381945</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4668,7 +4668,9 @@
       <c r="R53" s="10"/>
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+      <c r="U53" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -4679,7 +4681,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46192.17325630787</v>
+        <v>46200.683703159724</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4727,10 +4729,10 @@
         <v>33</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4740,9 +4742,11 @@
       <c r="B55" s="9">
         <v>46146.787358877315</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46200.68377538194</v>
+      </c>
       <c r="D55" s="9">
-        <v>46193.182386307875</v>
+        <v>46200.6837771412</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4788,10 +4792,10 @@
         <v>33</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4864,9 +4868,11 @@
       <c r="B57" s="9">
         <v>46146.79730351851</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46200.68386630787</v>
+      </c>
       <c r="D57" s="9">
-        <v>46193.18238616898</v>
+        <v>46200.683887164356</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4914,10 +4920,10 @@
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4990,9 +4996,11 @@
       <c r="B59" s="9">
         <v>46146.79750996528</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46200.68395946759</v>
+      </c>
       <c r="D59" s="9">
-        <v>46193.182386203705</v>
+        <v>46200.68397615741</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5040,10 +5048,10 @@
         <v>33</v>
       </c>
       <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5053,9 +5061,11 @@
       <c r="B60" s="5">
         <v>46146.787364398144</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46200.683365590274</v>
+      </c>
       <c r="D60" s="5">
-        <v>46198.89404733796</v>
+        <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5090,8 +5100,12 @@
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
+      <c r="T60" s="6">
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
@@ -5169,7 +5183,7 @@
         <v>46198.89361300926</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.89361449074</v>
+        <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5224,7 +5238,7 @@
         <v>46198.89383822917</v>
       </c>
       <c r="D63" s="9">
-        <v>46198.89383956019</v>
+        <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5450,9 +5464,11 @@
       <c r="B67" s="9">
         <v>46146.78740461805</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46200.68334386574</v>
+      </c>
       <c r="D67" s="9">
-        <v>46198.894457766204</v>
+        <v>46200.69320390046</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5498,10 +5514,10 @@
         <v>236</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5511,9 +5527,11 @@
       <c r="B68" s="5">
         <v>46146.787408564815</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46200.69310333334</v>
+      </c>
       <c r="D68" s="5">
-        <v>46198.89403201389</v>
+        <v>46200.69310599537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5562,9 +5580,11 @@
       <c r="B69" s="9">
         <v>46146.78741372685</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46200.693189224534</v>
+      </c>
       <c r="D69" s="9">
-        <v>46198.89371428241</v>
+        <v>46200.69319106481</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5953,7 +5973,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46146.94199042824</v>
+        <v>46200.6931983449</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6016,7 +6036,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46146.942057465276</v>
+        <v>46200.693112696754</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6069,7 +6089,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46146.942050451384</v>
+        <v>46200.693198877314</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.7868665162</v>
+        <v>46146.62019984954</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.872097534724</v>
+        <v>46175.70543086805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.872111840275</v>
+        <v>46175.70544517361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.78699289352</v>
+        <v>46146.620326226854</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.8720717824</v>
+        <v>46175.70540511574</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87209800926</v>
+        <v>46175.70543134259</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.786996319446</v>
+        <v>46146.62032965278</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87207239583</v>
+        <v>46175.70540572917</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87209802083</v>
+        <v>46175.70543135417</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.78699966436</v>
+        <v>46146.620332997685</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8720727662</v>
+        <v>46175.705406099536</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.872098576394</v>
+        <v>46175.70543190972</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.7870025</v>
+        <v>46146.62033583333</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872073136576</v>
+        <v>46175.705406469904</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87209884259</v>
+        <v>46175.70543217592</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.787006631945</v>
+        <v>46146.62033996527</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87207366899</v>
+        <v>46175.705407002315</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87209942129</v>
+        <v>46175.70543275463</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.78687210648</v>
+        <v>46146.620205439816</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.64946785879</v>
+        <v>46197.482801192135</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.6494803588</v>
+        <v>46197.48281369213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.787010162036</v>
+        <v>46146.62034349537</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.64821641204</v>
+        <v>46197.48154974537</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.64823298611</v>
+        <v>46197.481566319446</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.7870155787</v>
+        <v>46146.62034891204</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.648967245375</v>
+        <v>46197.482300578704</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.64898236111</v>
+        <v>46197.48231569445</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.787021400465</v>
+        <v>46146.620354733794</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.64945164352</v>
+        <v>46197.48278497685</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.6494675463</v>
+        <v>46197.48280087963</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,11 +2345,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.7868765162</v>
+        <v>46146.62020984954</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.784095717594</v>
+        <v>46191.61742905092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2392,11 +2392,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.7870415625</v>
+        <v>46146.620374895836</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46199.810681828705</v>
+        <v>46199.64401516203</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2455,11 +2455,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.78704743055</v>
+        <v>46146.62038076389</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.64899046296</v>
+        <v>46197.4823237963</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2518,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.78705320602</v>
+        <v>46146.62038653935</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.784087754626</v>
+        <v>46191.61742108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.64899056713</v>
+        <v>46197.48232390046</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2583,11 +2583,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.78705905093</v>
+        <v>46146.620392384255</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.17029900463</v>
+        <v>46178.00363233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2646,11 +2646,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.78706952547</v>
+        <v>46146.620402858796</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.1703008912</v>
+        <v>46178.00363422454</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2709,11 +2709,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.78707340278</v>
+        <v>46146.62040673611</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.170302349536</v>
+        <v>46178.00363568287</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2772,11 +2772,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.78707737269</v>
+        <v>46146.62041070602</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.17030399306</v>
+        <v>46178.00363732639</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2835,11 +2835,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.786881064814</v>
+        <v>46146.62021439815</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.92635412037</v>
+        <v>46195.759687453705</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2882,11 +2882,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.78708193287</v>
+        <v>46146.6204152662</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.858700868055</v>
+        <v>46169.69203420139</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2945,11 +2945,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.78708679398</v>
+        <v>46146.620420127314</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.858957557866</v>
+        <v>46169.6922908912</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3004,11 +3004,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.78709203703</v>
+        <v>46146.62042537037</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.85897216435</v>
+        <v>46169.69230549769</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3063,13 +3063,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.78709759259</v>
+        <v>46146.62043092593</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.92634351852</v>
+        <v>46195.759676851856</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.92635861111</v>
+        <v>46195.75969194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3128,13 +3128,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.78710313658</v>
+        <v>46146.62043646991</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.92632717593</v>
+        <v>46195.759660509255</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.92632960648</v>
+        <v>46195.75966293982</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3189,13 +3189,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.787108969904</v>
+        <v>46146.62044230324</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.78550167824</v>
+        <v>46191.61883501157</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.9263380787</v>
+        <v>46195.75967141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3250,11 +3250,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.78711427083</v>
+        <v>46146.62044760417</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.18668917824</v>
+        <v>46191.02002251157</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3313,11 +3313,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.78711935185</v>
+        <v>46146.62045268518</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.859063067124</v>
+        <v>46169.69239640047</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3372,11 +3372,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.78712466435</v>
+        <v>46146.620457997684</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.16874317129</v>
+        <v>46190.00207650463</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3431,11 +3431,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.78712987268</v>
+        <v>46146.62046320602</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46198.71236186342</v>
+        <v>46198.545695196764</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3490,11 +3490,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.78718802083</v>
+        <v>46146.62052135417</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.18189784722</v>
+        <v>46190.01523118056</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3553,11 +3553,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.78719326389</v>
+        <v>46146.620526597224</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.168845277774</v>
+        <v>46182.00217861111</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3612,11 +3612,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.78719805555</v>
+        <v>46146.62053138889</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.16864960648</v>
+        <v>46189.001982939815</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3671,11 +3671,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.78721570602</v>
+        <v>46146.62054903935</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.18189791667</v>
+        <v>46190.01523125</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3734,11 +3734,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.787218854166</v>
+        <v>46146.6205521875</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.168843391206</v>
+        <v>46182.002176724534</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3787,11 +3787,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.78722290509</v>
+        <v>46146.62055623843</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.16864146991</v>
+        <v>46189.001974803235</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3840,11 +3840,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.78722673611</v>
+        <v>46146.620560069445</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.85880202547</v>
+        <v>46169.6921353588</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3903,11 +3903,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.787229884256</v>
+        <v>46146.62056321759</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.169576643515</v>
+        <v>46185.00290997685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3956,11 +3956,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.787233807874</v>
+        <v>46146.6205671412</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.85930840278</v>
+        <v>46169.69264173611</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4009,11 +4009,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.92145594908</v>
+        <v>46146.75478928241</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859332141205</v>
+        <v>46169.69266547453</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4060,11 +4060,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.78723741898</v>
+        <v>46146.62057075232</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.1818981713</v>
+        <v>46190.01523150463</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4123,11 +4123,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.78724063658</v>
+        <v>46146.62057396991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.16884665509</v>
+        <v>46182.00217998843</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4176,11 +4176,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.78724467593</v>
+        <v>46146.62057800926</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.168642951394</v>
+        <v>46189.00197628472</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4229,11 +4229,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.78688576389</v>
+        <v>46146.620219097225</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.71096577546</v>
+        <v>46197.54429910879</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4276,13 +4276,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.78724949074</v>
+        <v>46146.62058282408</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.710958564814</v>
+        <v>46197.54429189815</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.711020393515</v>
+        <v>46197.54435372685</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4341,11 +4341,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.7872546412</v>
+        <v>46146.62058797454</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46198.71406938657</v>
+        <v>46198.54740271991</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4404,11 +4404,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.787260625</v>
+        <v>46146.62059395833</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46198.71808170139</v>
+        <v>46198.55141503472</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4465,11 +4465,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.78727884259</v>
+        <v>46146.620612175924</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.93970905093</v>
+        <v>46146.77304238426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4526,11 +4526,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.78728261574</v>
+        <v>46146.620615949076</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.939574814816</v>
+        <v>46146.77290814815</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4577,11 +4577,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.787286527775</v>
+        <v>46146.62061986111</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939575474535</v>
+        <v>46146.77290880787</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4628,11 +4628,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.787341759264</v>
+        <v>46146.62067509259</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46200.68378381945</v>
+        <v>46200.517117152776</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4677,11 +4677,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.787345254634</v>
+        <v>46146.62067858796</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46200.683703159724</v>
+        <v>46200.51703649305</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4740,13 +4740,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.787358877315</v>
+        <v>46146.62069221065</v>
       </c>
       <c r="C55" s="9">
-        <v>46200.68377538194</v>
+        <v>46200.51710871528</v>
       </c>
       <c r="D55" s="9">
-        <v>46200.6837771412</v>
+        <v>46200.51711047454</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4803,11 +4803,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.78735064815</v>
+        <v>46146.620683981484</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.17324446759</v>
+        <v>46192.00657780093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4866,13 +4866,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.79730351851</v>
+        <v>46146.630636851856</v>
       </c>
       <c r="C57" s="9">
-        <v>46200.68386630787</v>
+        <v>46200.5171996412</v>
       </c>
       <c r="D57" s="9">
-        <v>46200.683887164356</v>
+        <v>46200.517220497684</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4931,11 +4931,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.78735449074</v>
+        <v>46146.62068782408</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.17323068287</v>
+        <v>46192.00656401621</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4994,13 +4994,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.79750996528</v>
+        <v>46146.63084329861</v>
       </c>
       <c r="C59" s="9">
-        <v>46200.68395946759</v>
+        <v>46200.51729280093</v>
       </c>
       <c r="D59" s="9">
-        <v>46200.68397615741</v>
+        <v>46200.51730949074</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5059,13 +5059,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.787364398144</v>
+        <v>46146.62069773149</v>
       </c>
       <c r="C60" s="5">
-        <v>46200.683365590274</v>
+        <v>46200.51669892361</v>
       </c>
       <c r="D60" s="5">
-        <v>46200.68337925926</v>
+        <v>46200.516712592595</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5112,13 +5112,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.78736695602</v>
+        <v>46146.62070028935</v>
       </c>
       <c r="C61" s="9">
-        <v>46198.893461747684</v>
+        <v>46198.72679508102</v>
       </c>
       <c r="D61" s="9">
-        <v>46198.89361756944</v>
+        <v>46198.72695090278</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5177,13 +5177,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.79438380787</v>
+        <v>46146.62771714121</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.89361300926</v>
+        <v>46198.72694634259</v>
       </c>
       <c r="D62" s="5">
-        <v>46200.6839671412</v>
+        <v>46200.51730047454</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5232,13 +5232,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.79440119213</v>
+        <v>46146.627734525464</v>
       </c>
       <c r="C63" s="9">
-        <v>46198.89383822917</v>
+        <v>46198.727171562496</v>
       </c>
       <c r="D63" s="9">
-        <v>46200.683967916666</v>
+        <v>46200.51730125</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5287,13 +5287,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.78737179398</v>
+        <v>46146.620705127316</v>
       </c>
       <c r="C64" s="5">
-        <v>46198.8940372338</v>
+        <v>46198.727370567125</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.894050752315</v>
+        <v>46198.72738408565</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5352,13 +5352,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.78737561342</v>
+        <v>46146.620708946764</v>
       </c>
       <c r="C65" s="9">
-        <v>46198.89402209491</v>
+        <v>46198.727355428244</v>
       </c>
       <c r="D65" s="9">
-        <v>46198.894024050926</v>
+        <v>46198.727357384254</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5407,13 +5407,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.78738193287</v>
+        <v>46146.6207152662</v>
       </c>
       <c r="C66" s="5">
-        <v>46198.893706874995</v>
+        <v>46198.72704020834</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.893844606486</v>
+        <v>46198.727177939814</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5462,13 +5462,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.78740461805</v>
+        <v>46146.62073795139</v>
       </c>
       <c r="C67" s="9">
-        <v>46200.68334386574</v>
+        <v>46200.51667719908</v>
       </c>
       <c r="D67" s="9">
-        <v>46200.69320390046</v>
+        <v>46200.526537233796</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5525,13 +5525,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.787408564815</v>
+        <v>46146.62074189815</v>
       </c>
       <c r="C68" s="5">
-        <v>46200.69310333334</v>
+        <v>46200.52643666667</v>
       </c>
       <c r="D68" s="5">
-        <v>46200.69310599537</v>
+        <v>46200.52643932871</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5578,13 +5578,13 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.78741372685</v>
+        <v>46146.62074706018</v>
       </c>
       <c r="C69" s="9">
-        <v>46200.693189224534</v>
+        <v>46200.52652255787</v>
       </c>
       <c r="D69" s="9">
-        <v>46200.69319106481</v>
+        <v>46200.52652439815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5631,11 +5631,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.78743457176</v>
+        <v>46146.62076790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.92121962963</v>
+        <v>46146.754552962964</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5678,11 +5678,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.787437465275</v>
+        <v>46146.62077079861</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.78551768519</v>
+        <v>46191.61885101852</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5739,11 +5739,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.78744341435</v>
+        <v>46146.62077674769</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.18259200231</v>
+        <v>46157.01592533565</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5800,11 +5800,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.7874489699</v>
+        <v>46146.620782303246</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.17326015046</v>
+        <v>46192.00659348379</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5861,11 +5861,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.78746039352</v>
+        <v>46146.62079372685</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.94183069444</v>
+        <v>46146.77516402778</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5922,11 +5922,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.78750452546</v>
+        <v>46146.6208378588</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.58902260417</v>
+        <v>46197.422355937495</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.787508912035</v>
+        <v>46146.62084224537</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46200.6931983449</v>
+        <v>46200.526531678246</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6032,11 +6032,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.78752016203</v>
+        <v>46146.62085349537</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46200.693112696754</v>
+        <v>46200.5264460301</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6085,11 +6085,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.78752439815</v>
+        <v>46146.62085773148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46200.693198877314</v>
+        <v>46200.52653221065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6138,13 +6138,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.78758131944</v>
+        <v>46146.620914652776</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.58901480324</v>
+        <v>46197.42234813658</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.5890270949</v>
+        <v>46197.422360428245</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6201,13 +6201,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.78758657408</v>
+        <v>46146.62091990741</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.58893424769</v>
+        <v>46197.422267581016</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.58893591435</v>
+        <v>46197.42226924769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6254,13 +6254,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.787592939814</v>
+        <v>46146.62092627315</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.58900142361</v>
+        <v>46197.42233475695</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.58900278935</v>
+        <v>46197.42233612269</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6307,11 +6307,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.78761755787</v>
+        <v>46146.6209508912</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.94198379629</v>
+        <v>46146.77531712963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6370,11 +6370,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.78762708334</v>
+        <v>46146.620960416665</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.588939629626</v>
+        <v>46197.42227296296</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6421,11 +6421,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.78763331019</v>
+        <v>46146.62096664352</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.5890109375</v>
+        <v>46197.42234427083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6472,11 +6472,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.78769865741</v>
+        <v>46146.62103199074</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.941980902775</v>
+        <v>46146.77531423611</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6533,11 +6533,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.787703553244</v>
+        <v>46146.62103688657</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.9422950463</v>
+        <v>46146.77562837963</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6584,11 +6584,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.78770892361</v>
+        <v>46146.62104225694</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.94229197917</v>
+        <v>46146.7756253125</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6635,11 +6635,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.78773052084</v>
+        <v>46146.62106385417</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94197813657</v>
+        <v>46146.77531146991</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6696,11 +6696,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.78773511574</v>
+        <v>46146.62106844907</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94237260417</v>
+        <v>46146.7757059375</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6747,11 +6747,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.78774035879</v>
+        <v>46146.621073692135</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237009259</v>
+        <v>46146.77570342593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6798,11 +6798,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.787759479164</v>
+        <v>46146.6210928125</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94197326389</v>
+        <v>46146.77530659722</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6859,11 +6859,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.78776425926</v>
+        <v>46146.62109759259</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94244866898</v>
+        <v>46146.77578200231</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6910,11 +6910,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.787768587965</v>
+        <v>46146.62110192129</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244559028</v>
+        <v>46146.775778923606</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6961,11 +6961,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.78778571759</v>
+        <v>46146.62111905093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.9405634838</v>
+        <v>46146.77389681713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7008,11 +7008,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.78778912037</v>
+        <v>46146.621122453704</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9429809375</v>
+        <v>46146.77631427083</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7069,11 +7069,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.78779429398</v>
+        <v>46146.62112762731</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.942643194445</v>
+        <v>46146.77597652777</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7120,11 +7120,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.787798414356</v>
+        <v>46146.621131747685</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.94264393518</v>
+        <v>46146.77597726852</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7171,11 +7171,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.787814745374</v>
+        <v>46146.6211480787</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94289535879</v>
+        <v>46146.77622869213</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7232,11 +7232,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.78781900463</v>
+        <v>46146.62115233796</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94285763889</v>
+        <v>46146.77619097222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7283,11 +7283,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.787823148145</v>
+        <v>46146.62115648148</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285530093</v>
+        <v>46146.77618863426</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7334,11 +7334,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.787891527776</v>
+        <v>46146.62122486111</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.9431597338</v>
+        <v>46146.776493067126</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7395,11 +7395,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.78789762731</v>
+        <v>46146.62123096065</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.94342792824</v>
+        <v>46146.77676126157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7446,11 +7446,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.78790538195</v>
+        <v>46146.62123871528</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94346471065</v>
+        <v>46146.77679804398</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7497,11 +7497,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.787928171296</v>
+        <v>46146.621261504624</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94327527778</v>
+        <v>46146.77660861111</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7558,11 +7558,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.787934409724</v>
+        <v>46146.62126774306</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94332239583</v>
+        <v>46146.77665572916</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7609,11 +7609,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.787939131944</v>
+        <v>46146.62127246527</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.943319872684</v>
+        <v>46146.77665320602</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7660,11 +7660,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.787957974535</v>
+        <v>46146.62129130787</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.94056351852</v>
+        <v>46146.77389685185</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7707,11 +7707,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.78796153935</v>
+        <v>46146.62129487269</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94352958333</v>
+        <v>46146.77686291667</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7770,11 +7770,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.78796724537</v>
+        <v>46146.6213005787</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.86770128472</v>
+        <v>46196.701034618054</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.62019984954</v>
+        <v>46146.7868665162</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70543086805</v>
+        <v>46175.872097534724</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70544517361</v>
+        <v>46175.872111840275</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.620326226854</v>
+        <v>46146.78699289352</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70540511574</v>
+        <v>46175.8720717824</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70543134259</v>
+        <v>46175.87209800926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.62032965278</v>
+        <v>46146.786996319446</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70540572917</v>
+        <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70543135417</v>
+        <v>46175.87209802083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.620332997685</v>
+        <v>46146.78699966436</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.705406099536</v>
+        <v>46175.8720727662</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70543190972</v>
+        <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.62033583333</v>
+        <v>46146.7870025</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.705406469904</v>
+        <v>46175.872073136576</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70543217592</v>
+        <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.62033996527</v>
+        <v>46146.787006631945</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.705407002315</v>
+        <v>46175.87207366899</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70543275463</v>
+        <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.620205439816</v>
+        <v>46146.78687210648</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.482801192135</v>
+        <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.48281369213</v>
+        <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.62034349537</v>
+        <v>46146.787010162036</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.48154974537</v>
+        <v>46197.64821641204</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.481566319446</v>
+        <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.62034891204</v>
+        <v>46146.7870155787</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.482300578704</v>
+        <v>46197.648967245375</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.48231569445</v>
+        <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.620354733794</v>
+        <v>46146.787021400465</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.48278497685</v>
+        <v>46197.64945164352</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.48280087963</v>
+        <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,11 +2345,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.62020984954</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.61742905092</v>
+        <v>46191.784095717594</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2392,11 +2392,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.620374895836</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46199.64401516203</v>
+        <v>46199.810681828705</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2455,11 +2455,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.62038076389</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46197.4823237963</v>
+        <v>46197.64899046296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2518,13 +2518,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.62038653935</v>
+        <v>46146.78705320602</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.61742108796</v>
+        <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.48232390046</v>
+        <v>46197.64899056713</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2583,11 +2583,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.620392384255</v>
+        <v>46146.78705905093</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.00363233796</v>
+        <v>46178.17029900463</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2646,11 +2646,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.620402858796</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.00363422454</v>
+        <v>46178.1703008912</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2709,11 +2709,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.62040673611</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.00363568287</v>
+        <v>46178.170302349536</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2772,11 +2772,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.62041070602</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.00363732639</v>
+        <v>46178.17030399306</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2835,11 +2835,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.62021439815</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.759687453705</v>
+        <v>46195.92635412037</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2882,11 +2882,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.6204152662</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.69203420139</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2945,11 +2945,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.620420127314</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.6922908912</v>
+        <v>46169.858957557866</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3004,11 +3004,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.62042537037</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.69230549769</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3063,13 +3063,13 @@
         <v>109</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.62043092593</v>
+        <v>46146.78709759259</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.759676851856</v>
+        <v>46195.92634351852</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.75969194445</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>110</v>
@@ -3128,13 +3128,13 @@
         <v>112</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.62043646991</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.759660509255</v>
+        <v>46195.92632717593</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.75966293982</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>113</v>
@@ -3189,13 +3189,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.62044230324</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.61883501157</v>
+        <v>46191.78550167824</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.75967141204</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3250,11 +3250,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.62044760417</v>
+        <v>46146.78711427083</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.02002251157</v>
+        <v>46191.18668917824</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3313,11 +3313,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.62045268518</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.69239640047</v>
+        <v>46169.859063067124</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3372,11 +3372,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.620457997684</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.00207650463</v>
+        <v>46190.16874317129</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3431,11 +3431,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.62046320602</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46198.545695196764</v>
+        <v>46198.71236186342</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3490,11 +3490,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.62052135417</v>
+        <v>46146.78718802083</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.01523118056</v>
+        <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3553,11 +3553,11 @@
         <v>135</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.620526597224</v>
+        <v>46146.78719326389</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.00217861111</v>
+        <v>46182.168845277774</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>136</v>
@@ -3612,11 +3612,11 @@
         <v>138</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.62053138889</v>
+        <v>46146.78719805555</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.001982939815</v>
+        <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>139</v>
@@ -3671,11 +3671,11 @@
         <v>141</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.62054903935</v>
+        <v>46146.78721570602</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.01523125</v>
+        <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -3734,11 +3734,11 @@
         <v>144</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.6205521875</v>
+        <v>46146.787218854166</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.002176724534</v>
+        <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3787,11 +3787,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.62055623843</v>
+        <v>46146.78722290509</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.001974803235</v>
+        <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -3840,11 +3840,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.620560069445</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.6921353588</v>
+        <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3903,11 +3903,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.62056321759</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.00290997685</v>
+        <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3956,11 +3956,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.6205671412</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69264173611</v>
+        <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>157</v>
@@ -4009,11 +4009,11 @@
         <v>159</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.75478928241</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69266547453</v>
+        <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>160</v>
@@ -4060,11 +4060,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.62057075232</v>
+        <v>46146.78723741898</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.01523150463</v>
+        <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4123,11 +4123,11 @@
         <v>166</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.62057396991</v>
+        <v>46146.78724063658</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.00217998843</v>
+        <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4176,11 +4176,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.62057800926</v>
+        <v>46146.78724467593</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.00197628472</v>
+        <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4229,11 +4229,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.620219097225</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.54429910879</v>
+        <v>46197.71096577546</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4276,13 +4276,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.62058282408</v>
+        <v>46146.78724949074</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.54429189815</v>
+        <v>46197.710958564814</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.54435372685</v>
+        <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4341,11 +4341,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.62058797454</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46198.54740271991</v>
+        <v>46198.71406938657</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4404,11 +4404,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.62059395833</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46198.55141503472</v>
+        <v>46198.71808170139</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4465,11 +4465,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.620612175924</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.77304238426</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4526,11 +4526,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.620615949076</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.77290814815</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4577,11 +4577,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.62061986111</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.77290880787</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4628,11 +4628,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.62067509259</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46200.517117152776</v>
+        <v>46200.68378381945</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4677,11 +4677,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.62067858796</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46200.51703649305</v>
+        <v>46200.683703159724</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4740,13 +4740,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.62069221065</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C55" s="9">
-        <v>46200.51710871528</v>
+        <v>46200.68377538194</v>
       </c>
       <c r="D55" s="9">
-        <v>46200.51711047454</v>
+        <v>46200.6837771412</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4803,11 +4803,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.620683981484</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.00657780093</v>
+        <v>46192.17324446759</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4866,13 +4866,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.630636851856</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C57" s="9">
-        <v>46200.5171996412</v>
+        <v>46200.68386630787</v>
       </c>
       <c r="D57" s="9">
-        <v>46200.517220497684</v>
+        <v>46200.683887164356</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4931,11 +4931,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.62068782408</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.00656401621</v>
+        <v>46192.17323068287</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4994,13 +4994,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.63084329861</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C59" s="9">
-        <v>46200.51729280093</v>
+        <v>46200.68395946759</v>
       </c>
       <c r="D59" s="9">
-        <v>46200.51730949074</v>
+        <v>46200.68397615741</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5059,13 +5059,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.62069773149</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C60" s="5">
-        <v>46200.51669892361</v>
+        <v>46200.683365590274</v>
       </c>
       <c r="D60" s="5">
-        <v>46200.516712592595</v>
+        <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5112,13 +5112,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.62070028935</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C61" s="9">
-        <v>46198.72679508102</v>
+        <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46198.72695090278</v>
+        <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5177,13 +5177,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.62771714121</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.72694634259</v>
+        <v>46198.89361300926</v>
       </c>
       <c r="D62" s="5">
-        <v>46200.51730047454</v>
+        <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5232,13 +5232,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.627734525464</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C63" s="9">
-        <v>46198.727171562496</v>
+        <v>46198.89383822917</v>
       </c>
       <c r="D63" s="9">
-        <v>46200.51730125</v>
+        <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5287,13 +5287,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.620705127316</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46198.727370567125</v>
+        <v>46198.8940372338</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.72738408565</v>
+        <v>46198.894050752315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5352,13 +5352,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.620708946764</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C65" s="9">
-        <v>46198.727355428244</v>
+        <v>46198.89402209491</v>
       </c>
       <c r="D65" s="9">
-        <v>46198.727357384254</v>
+        <v>46198.894024050926</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5407,13 +5407,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.6207152662</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C66" s="5">
-        <v>46198.72704020834</v>
+        <v>46198.893706874995</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.727177939814</v>
+        <v>46198.893844606486</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5462,13 +5462,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.62073795139</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C67" s="9">
-        <v>46200.51667719908</v>
+        <v>46200.68334386574</v>
       </c>
       <c r="D67" s="9">
-        <v>46200.526537233796</v>
+        <v>46200.69320390046</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>242</v>
@@ -5525,13 +5525,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.62074189815</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C68" s="5">
-        <v>46200.52643666667</v>
+        <v>46200.69310333334</v>
       </c>
       <c r="D68" s="5">
-        <v>46200.52643932871</v>
+        <v>46200.69310599537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5578,13 +5578,13 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.62074706018</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C69" s="9">
-        <v>46200.52652255787</v>
+        <v>46200.693189224534</v>
       </c>
       <c r="D69" s="9">
-        <v>46200.52652439815</v>
+        <v>46200.69319106481</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5631,11 +5631,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.62076790509</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.754552962964</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5678,11 +5678,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.62077079861</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.61885101852</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5739,11 +5739,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.62077674769</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.01592533565</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5800,11 +5800,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.620782303246</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.00659348379</v>
+        <v>46192.17326015046</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5861,11 +5861,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.62079372685</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.77516402778</v>
+        <v>46146.94183069444</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5922,11 +5922,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.6208378588</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.422355937495</v>
+        <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.62084224537</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46200.526531678246</v>
+        <v>46200.6931983449</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6032,11 +6032,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.62085349537</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46200.5264460301</v>
+        <v>46200.693112696754</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6085,11 +6085,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.62085773148</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46200.52653221065</v>
+        <v>46200.693198877314</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6138,13 +6138,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.620914652776</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.42234813658</v>
+        <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.422360428245</v>
+        <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6201,13 +6201,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.62091990741</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.422267581016</v>
+        <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.42226924769</v>
+        <v>46197.58893591435</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6254,13 +6254,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.62092627315</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42233475695</v>
+        <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.42233612269</v>
+        <v>46197.58900278935</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6307,11 +6307,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.6209508912</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.77531712963</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6370,11 +6370,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.620960416665</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.42227296296</v>
+        <v>46197.588939629626</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6421,11 +6421,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.62096664352</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.42234427083</v>
+        <v>46197.5890109375</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6472,11 +6472,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.62103199074</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.77531423611</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6533,11 +6533,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.62103688657</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.77562837963</v>
+        <v>46146.9422950463</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6584,11 +6584,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.62104225694</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.7756253125</v>
+        <v>46146.94229197917</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6635,11 +6635,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.62106385417</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.77531146991</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6696,11 +6696,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.62106844907</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.7757059375</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6747,11 +6747,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.621073692135</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.77570342593</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6798,11 +6798,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.6210928125</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.77530659722</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6859,11 +6859,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.62109759259</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.77578200231</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6910,11 +6910,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.62110192129</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.775778923606</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6961,11 +6961,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.62111905093</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.77389681713</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7008,11 +7008,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.621122453704</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.77631427083</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7069,11 +7069,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.62112762731</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.77597652777</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7120,11 +7120,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.621131747685</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.77597726852</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7171,11 +7171,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.6211480787</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.77622869213</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7232,11 +7232,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.62115233796</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.77619097222</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7283,11 +7283,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.62115648148</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.77618863426</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7334,11 +7334,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.62122486111</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.776493067126</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7395,11 +7395,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.62123096065</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.77676126157</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7446,11 +7446,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.62123871528</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.77679804398</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7497,11 +7497,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.621261504624</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.77660861111</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7558,11 +7558,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.62126774306</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.77665572916</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7609,11 +7609,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.62127246527</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.77665320602</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7660,11 +7660,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.62129130787</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.77389685185</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7707,11 +7707,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.62129487269</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.77686291667</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7770,11 +7770,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.6213005787</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.701034618054</v>
+        <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -304,30 +304,30 @@
     <t>Generación OC motor OT 4309,Propuesta compras:</t>
   </si>
   <si>
+    <t>1214511142378696</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4309</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142378716</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4309</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214511142378696</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4309</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142378716</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4309</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
     <t>1214511155793305</t>
   </si>
   <si>
@@ -346,58 +346,58 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4309</t>
   </si>
   <si>
+    <t>1214511198886127</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198886137</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198886147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa OT 4309 </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084762</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>1214511244996574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214511198886127</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198886137</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198886147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa OT 4309 </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084762</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>1214511244996574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
   </si>
   <si>
     <t>1214511244996589</t>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.784095717594</v>
+        <v>46203.709446678244</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2394,9 +2394,11 @@
       <c r="B15" s="9">
         <v>46146.7870415625</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46203.70939159722</v>
+      </c>
       <c r="D15" s="9">
-        <v>46199.810681828705</v>
+        <v>46203.70941623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2444,25 +2446,27 @@
         <v>33</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46146.78704743055</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46203.70944197917</v>
+      </c>
       <c r="D16" s="5">
-        <v>46197.64899046296</v>
+        <v>46203.70945753472</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2495,7 +2499,7 @@
         <v>57</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="5">
         <v>46149</v>
@@ -2507,15 +2511,15 @@
         <v>33</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="9">
         <v>46146.78705320602</v>
@@ -2527,16 +2531,16 @@
         <v>46197.64899056713</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I17" s="9">
         <v>46149</v>
@@ -2560,7 +2564,7 @@
         <v>57</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2575,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46178.17029900463</v>
+        <v>46203.714959756944</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2637,23 +2641,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>84</v>
+      <c r="U18" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46178.1703008912</v>
+        <v>46203.71496125</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2686,7 +2690,7 @@
         <v>82</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2700,23 +2704,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>84</v>
+      <c r="U19" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46178.170302349536</v>
+        <v>46203.71495998843</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2749,7 +2753,7 @@
         <v>82</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2763,23 +2767,23 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>84</v>
+      <c r="U20" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46178.17030399306</v>
+        <v>46203.71496114583</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2812,7 +2816,7 @@
         <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2826,23 +2830,23 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
-        <v>84</v>
+      <c r="U21" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46195.92635412037</v>
+        <v>46203.710007118054</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2866,7 +2870,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2879,7 +2883,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2889,16 +2893,16 @@
         <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2916,13 +2920,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2937,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2949,7 +2953,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.858957557866</v>
+        <v>46203.70944847222</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -2958,10 +2962,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2979,10 +2983,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>104</v>
@@ -2996,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3017,10 +3021,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3038,7 +3042,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>103</v>
@@ -3055,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3078,10 +3082,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3099,13 +3103,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3143,10 +3147,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3167,7 +3171,7 @@
         <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>114</v>
@@ -3181,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3204,10 +3208,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3242,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3252,9 +3256,11 @@
       <c r="B29" s="9">
         <v>46146.78711427083</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46203.70999099537</v>
+      </c>
       <c r="D29" s="9">
-        <v>46191.18668917824</v>
+        <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>119</v>
@@ -3263,10 +3269,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3284,13 +3290,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3302,10 +3308,10 @@
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3315,9 +3321,11 @@
       <c r="B30" s="5">
         <v>46146.78711935185</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46203.7099115625</v>
+      </c>
       <c r="D30" s="5">
-        <v>46169.859063067124</v>
+        <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3326,10 +3334,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3364,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3374,9 +3382,11 @@
       <c r="B31" s="9">
         <v>46146.78712466435</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46203.70997548611</v>
+      </c>
       <c r="D31" s="9">
-        <v>46190.16874317129</v>
+        <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3385,10 +3395,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3423,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3433,9 +3443,11 @@
       <c r="B32" s="5">
         <v>46146.78712987268</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46203.70995884259</v>
+      </c>
       <c r="D32" s="5">
-        <v>46198.71236186342</v>
+        <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3444,10 +3456,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3482,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3524,13 +3536,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3545,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3604,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3663,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3705,7 +3717,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>143</v>
@@ -3726,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3741,7 +3753,7 @@
         <v>46182.168843391206</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3771,7 +3783,7 @@
         <v>142</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>145</v>
@@ -3824,7 +3836,7 @@
         <v>142</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>148</v>
@@ -3874,7 +3886,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>153</v>
@@ -3895,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3910,7 +3922,7 @@
         <v>46185.169576643515</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3940,7 +3952,7 @@
         <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>155</v>
@@ -3993,7 +4005,7 @@
         <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>158</v>
@@ -4094,7 +4106,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>165</v>
@@ -4115,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4130,7 +4142,7 @@
         <v>46182.16884665509</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4160,7 +4172,7 @@
         <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>167</v>
@@ -4213,7 +4225,7 @@
         <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>170</v>
@@ -4233,7 +4245,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.71096577546</v>
+        <v>46203.71489604167</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4269,7 +4281,9 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -4343,9 +4357,11 @@
       <c r="B48" s="5">
         <v>46146.7872546412</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46203.714861863424</v>
+      </c>
       <c r="D48" s="5">
-        <v>46198.71406938657</v>
+        <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4393,10 +4409,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4406,9 +4422,11 @@
       <c r="B49" s="9">
         <v>46146.787260625</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46203.71491821759</v>
+      </c>
       <c r="D49" s="9">
-        <v>46198.71808170139</v>
+        <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>82</v>
@@ -4454,10 +4472,10 @@
         <v>33</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>84</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4518,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4669,7 +4687,7 @@
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="12" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4858,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4986,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5358,7 +5376,7 @@
         <v>46198.89402209491</v>
       </c>
       <c r="D65" s="9">
-        <v>46198.894024050926</v>
+        <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5413,7 +5431,7 @@
         <v>46198.893706874995</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.893844606486</v>
+        <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5517,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5531,7 +5549,7 @@
         <v>46200.69310333334</v>
       </c>
       <c r="D68" s="5">
-        <v>46200.69310599537</v>
+        <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5584,7 +5602,7 @@
         <v>46200.693189224534</v>
       </c>
       <c r="D69" s="9">
-        <v>46200.69319106481</v>
+        <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5731,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5792,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5804,7 +5822,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46192.17326015046</v>
+        <v>46203.70999737269</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5852,8 +5870,8 @@
       <c r="T73" s="10">
         <v>0</v>
       </c>
-      <c r="U73" s="11" t="s">
-        <v>84</v>
+      <c r="U73" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5914,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5982,10 +6000,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I76" s="5">
         <v>46219</v>
@@ -6024,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6045,10 +6063,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I77" s="9">
         <v>46219</v>
@@ -6098,10 +6116,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I78" s="5">
         <v>46219</v>
@@ -6153,10 +6171,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6207,7 +6225,7 @@
         <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46197.58893591435</v>
+        <v>46203.71494715278</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6216,10 +6234,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6260,7 +6278,7 @@
         <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46197.58900278935</v>
+        <v>46203.71494597222</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6269,10 +6287,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6320,10 +6338,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I82" s="5">
         <v>46227</v>
@@ -6362,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6374,7 +6392,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46197.588939629626</v>
+        <v>46203.71494815972</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6383,10 +6401,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6425,7 +6443,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.5890109375</v>
+        <v>46203.71494907407</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6434,10 +6452,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6485,10 +6503,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6525,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6537,7 +6555,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46146.9422950463</v>
+        <v>46203.71494643518</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6546,10 +6564,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6588,7 +6606,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46146.94229197917</v>
+        <v>46203.7149375</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6597,10 +6615,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6648,10 +6666,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6688,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6709,10 +6727,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6760,10 +6778,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6811,10 +6829,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6851,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6872,10 +6890,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6923,10 +6941,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -7061,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7184,10 +7202,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7224,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7245,10 +7263,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7296,10 +7314,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7387,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7550,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7762,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7825,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -325,295 +325,295 @@
     <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
   </si>
   <si>
+    <t>1214511155793305</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198886127</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198886137</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511198886147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa OT 4309 </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084762</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>1214511244996574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214511244996589</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1214511142420461</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>Alabe OT 4309 ,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214511142420479</t>
+  </si>
+  <si>
+    <t>rodete OT 4309</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4309,Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240948634</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>rodete OT 4309,Fabricación Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240948652</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>rodete OT 4309,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214511142420756</t>
+  </si>
+  <si>
+    <t>Motor OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142420771</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511155826380</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214511155826398</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511240963370</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240963385</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511245068713</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002704</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>1214511199002729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214511142484065</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142484075</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973505</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084879</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214511240973520</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973530</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199027682</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084764</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214511155793305</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198886127</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198886137</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511198886147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa OT 4309 </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084762</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>1214511244996574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214511244996589</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1214511142420461</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>Alabe OT 4309 ,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214511142420479</t>
-  </si>
-  <si>
-    <t>rodete OT 4309</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4309,Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240948634</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>rodete OT 4309,Fabricación Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240948652</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>rodete OT 4309,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214511142420756</t>
-  </si>
-  <si>
-    <t>Motor OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142420771</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511155826380</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214511155826398</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511240963370</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240963385</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511245068713</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002704</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>1214511199002729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214511142484065</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142484075</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973505</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084879</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214511240973520</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973530</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199027682</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084764</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
   </si>
   <si>
     <t>1214511199027697</t>
@@ -2347,9 +2347,11 @@
       <c r="B14" s="5">
         <v>46146.7868765162</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46204.90800548611</v>
+      </c>
       <c r="D14" s="5">
-        <v>46203.709446678244</v>
+        <v>46204.908018587965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2384,8 +2386,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2528,7 +2534,7 @@
         <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.64899056713</v>
+        <v>46204.907181365736</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2578,32 +2584,34 @@
       <c r="T17" s="10">
         <v>1</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>77</v>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46146.78705905093</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46204.90713112269</v>
+      </c>
       <c r="D18" s="5">
-        <v>46203.714959756944</v>
+        <v>46204.90714847222</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I18" s="5">
         <v>46177</v>
@@ -2624,10 +2632,10 @@
         <v>65</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46146</v>
@@ -2639,34 +2647,36 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46204.90751574074</v>
+      </c>
       <c r="D19" s="9">
-        <v>46203.71496125</v>
+        <v>46204.9075317824</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I19" s="9">
         <v>46177</v>
@@ -2687,10 +2697,10 @@
         <v>65</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2702,34 +2712,36 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46204.90776649305</v>
+      </c>
       <c r="D20" s="5">
-        <v>46203.71495998843</v>
+        <v>46204.90778255787</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="I20" s="5">
         <v>46177</v>
@@ -2750,10 +2762,10 @@
         <v>65</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2765,34 +2777,36 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46204.90798908565</v>
+      </c>
       <c r="D21" s="9">
-        <v>46203.71496114583</v>
+        <v>46204.90800618056</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="I21" s="9">
         <v>46177</v>
@@ -2813,10 +2827,10 @@
         <v>65</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2828,15 +2842,15 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2846,7 +2860,7 @@
         <v>46203.710007118054</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2870,7 +2884,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2883,7 +2897,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2893,16 +2907,16 @@
         <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2920,13 +2934,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2941,12 +2955,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2956,16 +2970,16 @@
         <v>46203.70944847222</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2983,29 +2997,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3015,16 +3029,16 @@
         <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3042,29 +3056,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3076,16 +3090,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3103,13 +3117,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3129,7 +3143,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3141,16 +3155,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3168,29 +3182,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3202,16 +3216,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3229,29 +3243,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3263,16 +3277,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3290,13 +3304,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3316,7 +3330,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3328,16 +3342,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3355,29 +3369,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3389,16 +3403,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3416,29 +3430,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3450,16 +3464,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3477,29 +3491,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3509,16 +3523,16 @@
         <v>46190.18189784722</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3536,13 +3550,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3557,31 +3571,31 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.168845277774</v>
+        <v>46204.90714231481</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3599,29 +3613,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3631,16 +3645,16 @@
         <v>46189.16864960648</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3658,29 +3672,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3690,16 +3704,16 @@
         <v>46190.18189791667</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3717,10 +3731,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3738,31 +3752,31 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.168843391206</v>
+        <v>46204.90752599537</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3780,13 +3794,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3796,7 +3810,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3806,16 +3820,16 @@
         <v>46189.16864146991</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3833,13 +3847,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3849,7 +3863,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3859,16 +3873,16 @@
         <v>46169.85880202547</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3886,10 +3900,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3901,37 +3915,37 @@
         <v>46217</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.169576643515</v>
+        <v>46204.90799690972</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3949,13 +3963,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3965,7 +3979,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -3975,16 +3989,16 @@
         <v>46169.85930840278</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4002,13 +4016,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4018,7 +4032,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4028,16 +4042,16 @@
         <v>46169.859332141205</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4053,10 +4067,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4069,7 +4083,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4079,16 +4093,16 @@
         <v>46190.1818981713</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4106,10 +4120,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4127,31 +4141,31 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.16884665509</v>
+        <v>46204.90777372685</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4169,13 +4183,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4185,7 +4199,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4195,16 +4209,16 @@
         <v>46189.168642951394</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4222,13 +4236,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4238,7 +4252,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4248,7 +4262,7 @@
         <v>46203.71489604167</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4272,7 +4286,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4282,7 +4296,7 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4326,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
@@ -4391,7 +4405,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>181</v>
@@ -4429,7 +4443,7 @@
         <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4454,7 +4468,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>180</v>
@@ -4515,7 +4529,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>191</v>
@@ -4530,13 +4544,13 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4687,7 +4701,7 @@
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4732,7 +4746,7 @@
         <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>203</v>
@@ -4773,10 +4787,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4858,7 +4872,7 @@
         <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>210</v>
@@ -4876,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4899,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4986,7 +5000,7 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>216</v>
@@ -5004,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5027,10 +5041,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5495,10 +5509,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5535,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5558,10 +5572,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5611,10 +5625,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5731,7 +5745,7 @@
         <v>197</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>251</v>
@@ -5749,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5792,7 +5806,7 @@
         <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>254</v>
@@ -5810,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5853,7 +5867,7 @@
         <v>197</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>251</v>
@@ -5871,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5914,7 +5928,7 @@
         <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>259</v>
@@ -5926,13 +5940,13 @@
         <v>46218</v>
       </c>
       <c r="S74" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,13 +6050,13 @@
         <v>46225</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6205,7 +6219,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6374,13 +6388,13 @@
         <v>46227</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6537,13 +6551,13 @@
         <v>46230</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6700,13 +6714,13 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6863,13 +6877,13 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7073,13 +7087,13 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7236,13 +7250,13 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7399,13 +7413,13 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7562,13 +7576,13 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7774,13 +7788,13 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7837,13 +7851,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -802,25 +802,25 @@
     <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
   </si>
   <si>
+    <t>1214511245155149</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142568769</t>
+  </si>
+  <si>
+    <t>1214511245167372</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511245155149</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142568769</t>
-  </si>
-  <si>
-    <t>1214511245167372</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
   </si>
   <si>
     <t>1214511245167387</t>
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.7868665162</v>
+        <v>46146.62019984954</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.872097534724</v>
+        <v>46175.70543086805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.872111840275</v>
+        <v>46175.70544517361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.78699289352</v>
+        <v>46146.620326226854</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.8720717824</v>
+        <v>46175.70540511574</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87209800926</v>
+        <v>46175.70543134259</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.786996319446</v>
+        <v>46146.62032965278</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87207239583</v>
+        <v>46175.70540572917</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87209802083</v>
+        <v>46175.70543135417</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.78699966436</v>
+        <v>46146.620332997685</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8720727662</v>
+        <v>46175.705406099536</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.872098576394</v>
+        <v>46175.70543190972</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.7870025</v>
+        <v>46146.62033583333</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872073136576</v>
+        <v>46175.705406469904</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87209884259</v>
+        <v>46175.70543217592</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.787006631945</v>
+        <v>46146.62033996527</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87207366899</v>
+        <v>46175.705407002315</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87209942129</v>
+        <v>46175.70543275463</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.78687210648</v>
+        <v>46146.620205439816</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.64946785879</v>
+        <v>46197.482801192135</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.6494803588</v>
+        <v>46197.48281369213</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.787010162036</v>
+        <v>46146.62034349537</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.64821641204</v>
+        <v>46197.48154974537</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.64823298611</v>
+        <v>46197.481566319446</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.7870155787</v>
+        <v>46146.62034891204</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.648967245375</v>
+        <v>46197.482300578704</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.64898236111</v>
+        <v>46197.48231569445</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.787021400465</v>
+        <v>46146.620354733794</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.64945164352</v>
+        <v>46197.48278497685</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.6494675463</v>
+        <v>46197.48280087963</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,13 +2345,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.7868765162</v>
+        <v>46146.62020984954</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.90800548611</v>
+        <v>46204.74133881944</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.908018587965</v>
+        <v>46204.7413519213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2398,13 +2398,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.7870415625</v>
+        <v>46146.620374895836</v>
       </c>
       <c r="C15" s="9">
-        <v>46203.70939159722</v>
+        <v>46203.54272493055</v>
       </c>
       <c r="D15" s="9">
-        <v>46203.70941623843</v>
+        <v>46203.54274957176</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2463,13 +2463,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.78704743055</v>
+        <v>46146.62038076389</v>
       </c>
       <c r="C16" s="5">
-        <v>46203.70944197917</v>
+        <v>46203.5427753125</v>
       </c>
       <c r="D16" s="5">
-        <v>46203.70945753472</v>
+        <v>46203.54279086806</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2528,13 +2528,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.78705320602</v>
+        <v>46146.62038653935</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.784087754626</v>
+        <v>46191.61742108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.907181365736</v>
+        <v>46204.74051469908</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2593,13 +2593,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.78705905093</v>
+        <v>46146.620392384255</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.90713112269</v>
+        <v>46204.740464456016</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.90714847222</v>
+        <v>46204.74048180555</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2658,13 +2658,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.78706952547</v>
+        <v>46146.620402858796</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.90751574074</v>
+        <v>46204.74084907408</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.9075317824</v>
+        <v>46204.740865115746</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2723,13 +2723,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.78707340278</v>
+        <v>46146.62040673611</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.90776649305</v>
+        <v>46204.74109982639</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.90778255787</v>
+        <v>46204.7411158912</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2788,13 +2788,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.78707737269</v>
+        <v>46146.62041070602</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.90798908565</v>
+        <v>46204.74132241898</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.90800618056</v>
+        <v>46204.74133951389</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2853,11 +2853,11 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.786881064814</v>
+        <v>46146.62021439815</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46203.710007118054</v>
+        <v>46203.54334045139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2900,11 +2900,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.78708193287</v>
+        <v>46146.6204152662</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.858700868055</v>
+        <v>46169.69203420139</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2963,11 +2963,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.78708679398</v>
+        <v>46146.620420127314</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46203.70944847222</v>
+        <v>46203.542781805554</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3022,11 +3022,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.78709203703</v>
+        <v>46146.62042537037</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.85897216435</v>
+        <v>46169.69230549769</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3081,13 +3081,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.78709759259</v>
+        <v>46146.62043092593</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.92634351852</v>
+        <v>46195.759676851856</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.92635861111</v>
+        <v>46195.75969194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3146,13 +3146,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.78710313658</v>
+        <v>46146.62043646991</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.92632717593</v>
+        <v>46195.759660509255</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.92632960648</v>
+        <v>46195.75966293982</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3207,13 +3207,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.787108969904</v>
+        <v>46146.62044230324</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.78550167824</v>
+        <v>46191.61883501157</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.9263380787</v>
+        <v>46195.75967141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3268,13 +3268,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.78711427083</v>
+        <v>46146.62044760417</v>
       </c>
       <c r="C29" s="9">
-        <v>46203.70999099537</v>
+        <v>46203.543324328704</v>
       </c>
       <c r="D29" s="9">
-        <v>46203.71001635416</v>
+        <v>46203.543349687505</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3333,13 +3333,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.78711935185</v>
+        <v>46146.62045268518</v>
       </c>
       <c r="C30" s="5">
-        <v>46203.7099115625</v>
+        <v>46203.54324489583</v>
       </c>
       <c r="D30" s="5">
-        <v>46203.70991413195</v>
+        <v>46203.54324746528</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3394,13 +3394,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.78712466435</v>
+        <v>46146.620457997684</v>
       </c>
       <c r="C31" s="9">
-        <v>46203.70997548611</v>
+        <v>46203.54330881944</v>
       </c>
       <c r="D31" s="9">
-        <v>46203.70997798612</v>
+        <v>46203.543311319445</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3455,13 +3455,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.78712987268</v>
+        <v>46146.62046320602</v>
       </c>
       <c r="C32" s="5">
-        <v>46203.70995884259</v>
+        <v>46203.54329217593</v>
       </c>
       <c r="D32" s="5">
-        <v>46203.709962685185</v>
+        <v>46203.54329601851</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3516,11 +3516,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.78718802083</v>
+        <v>46146.62052135417</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46190.18189784722</v>
+        <v>46190.01523118056</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3579,11 +3579,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.78719326389</v>
+        <v>46146.620526597224</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46204.90714231481</v>
+        <v>46204.74047564815</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3638,11 +3638,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.78719805555</v>
+        <v>46146.62053138889</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46189.16864960648</v>
+        <v>46189.001982939815</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3697,11 +3697,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.78721570602</v>
+        <v>46146.62054903935</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.18189791667</v>
+        <v>46190.01523125</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3760,11 +3760,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.787218854166</v>
+        <v>46146.6205521875</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46204.90752599537</v>
+        <v>46204.740859328704</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>85</v>
@@ -3813,11 +3813,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.78722290509</v>
+        <v>46146.62055623843</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.16864146991</v>
+        <v>46189.001974803235</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3866,11 +3866,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.78722673611</v>
-      </c>
-      <c r="C39" s="10"/>
+        <v>46146.620560069445</v>
+      </c>
+      <c r="C39" s="9">
+        <v>46205.425039027774</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.85880202547</v>
+        <v>46205.42512828704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3918,10 +3920,10 @@
         <v>104</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3929,11 +3931,13 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.787229884256</v>
-      </c>
-      <c r="C40" s="6"/>
+        <v>46146.62056321759</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46205.38085069445</v>
+      </c>
       <c r="D40" s="5">
-        <v>46204.90799690972</v>
+        <v>46205.38085299768</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>91</v>
@@ -3982,11 +3986,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.787233807874</v>
-      </c>
-      <c r="C41" s="10"/>
+        <v>46146.6205671412</v>
+      </c>
+      <c r="C41" s="9">
+        <v>46205.424983460645</v>
+      </c>
       <c r="D41" s="9">
-        <v>46169.85930840278</v>
+        <v>46205.42498578704</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4035,11 +4041,13 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.92145594908</v>
-      </c>
-      <c r="C42" s="6"/>
+        <v>46146.75478928241</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46205.42502674769</v>
+      </c>
       <c r="D42" s="5">
-        <v>46169.859332141205</v>
+        <v>46205.425028125</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4086,11 +4094,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.78723741898</v>
+        <v>46146.62057075232</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46190.1818981713</v>
+        <v>46190.01523150463</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4149,11 +4157,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.78724063658</v>
+        <v>46146.62057396991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.90777372685</v>
+        <v>46204.74110706018</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>88</v>
@@ -4202,11 +4210,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.78724467593</v>
+        <v>46146.62057800926</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46189.168642951394</v>
+        <v>46189.00197628472</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4255,11 +4263,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.78688576389</v>
+        <v>46146.620219097225</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.71489604167</v>
+        <v>46203.548229374996</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4304,13 +4312,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.78724949074</v>
+        <v>46146.62058282408</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.710958564814</v>
+        <v>46197.54429189815</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.711020393515</v>
+        <v>46197.54435372685</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4369,13 +4377,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.7872546412</v>
+        <v>46146.62058797454</v>
       </c>
       <c r="C48" s="5">
-        <v>46203.714861863424</v>
+        <v>46203.54819519676</v>
       </c>
       <c r="D48" s="5">
-        <v>46203.71488673611</v>
+        <v>46203.548220069446</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4434,13 +4442,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.787260625</v>
+        <v>46146.62059395833</v>
       </c>
       <c r="C49" s="9">
-        <v>46203.71491821759</v>
+        <v>46203.54825155092</v>
       </c>
       <c r="D49" s="9">
-        <v>46203.71493509259</v>
+        <v>46203.548268425926</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>81</v>
@@ -4497,11 +4505,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.78727884259</v>
+        <v>46146.620612175924</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.93970905093</v>
+        <v>46146.77304238426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4558,11 +4566,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.78728261574</v>
+        <v>46146.620615949076</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.939574814816</v>
+        <v>46146.77290814815</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4609,11 +4617,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.787286527775</v>
+        <v>46146.62061986111</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939575474535</v>
+        <v>46146.77290880787</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4660,11 +4668,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.787341759264</v>
+        <v>46146.62067509259</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46200.68378381945</v>
+        <v>46200.517117152776</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4709,11 +4717,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.787345254634</v>
+        <v>46146.62067858796</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46200.683703159724</v>
+        <v>46200.51703649305</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4772,13 +4780,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.787358877315</v>
+        <v>46146.62069221065</v>
       </c>
       <c r="C55" s="9">
-        <v>46200.68377538194</v>
+        <v>46200.51710871528</v>
       </c>
       <c r="D55" s="9">
-        <v>46200.6837771412</v>
+        <v>46200.51711047454</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4835,11 +4843,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.78735064815</v>
+        <v>46146.620683981484</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.17324446759</v>
+        <v>46192.00657780093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4898,13 +4906,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.79730351851</v>
+        <v>46146.630636851856</v>
       </c>
       <c r="C57" s="9">
-        <v>46200.68386630787</v>
+        <v>46200.5171996412</v>
       </c>
       <c r="D57" s="9">
-        <v>46200.683887164356</v>
+        <v>46200.517220497684</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4963,11 +4971,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.78735449074</v>
+        <v>46146.62068782408</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.17323068287</v>
+        <v>46192.00656401621</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -5026,13 +5034,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.79750996528</v>
+        <v>46146.63084329861</v>
       </c>
       <c r="C59" s="9">
-        <v>46200.68395946759</v>
+        <v>46200.51729280093</v>
       </c>
       <c r="D59" s="9">
-        <v>46200.68397615741</v>
+        <v>46200.51730949074</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5091,13 +5099,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.787364398144</v>
+        <v>46146.62069773149</v>
       </c>
       <c r="C60" s="5">
-        <v>46200.683365590274</v>
+        <v>46200.51669892361</v>
       </c>
       <c r="D60" s="5">
-        <v>46200.68337925926</v>
+        <v>46200.516712592595</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5144,13 +5152,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.78736695602</v>
+        <v>46146.62070028935</v>
       </c>
       <c r="C61" s="9">
-        <v>46198.893461747684</v>
+        <v>46198.72679508102</v>
       </c>
       <c r="D61" s="9">
-        <v>46198.89361756944</v>
+        <v>46198.72695090278</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5209,13 +5217,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.79438380787</v>
+        <v>46146.62771714121</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.89361300926</v>
+        <v>46198.72694634259</v>
       </c>
       <c r="D62" s="5">
-        <v>46200.6839671412</v>
+        <v>46200.51730047454</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5264,13 +5272,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.79440119213</v>
+        <v>46146.627734525464</v>
       </c>
       <c r="C63" s="9">
-        <v>46198.89383822917</v>
+        <v>46198.727171562496</v>
       </c>
       <c r="D63" s="9">
-        <v>46200.683967916666</v>
+        <v>46200.51730125</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5319,13 +5327,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.78737179398</v>
+        <v>46146.620705127316</v>
       </c>
       <c r="C64" s="5">
-        <v>46198.8940372338</v>
+        <v>46198.727370567125</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.894050752315</v>
+        <v>46205.03654446759</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5369,8 +5377,8 @@
       <c r="R64" s="5">
         <v>46204</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>236</v>
+      <c r="S64" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5381,16 +5389,16 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.78737561342</v>
+        <v>46146.620708946764</v>
       </c>
       <c r="C65" s="9">
-        <v>46198.89402209491</v>
+        <v>46198.727355428244</v>
       </c>
       <c r="D65" s="9">
-        <v>46203.71492597222</v>
+        <v>46203.54825930556</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5423,10 +5431,10 @@
         <v>234</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5436,16 +5444,16 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.78738193287</v>
+        <v>46146.6207152662</v>
       </c>
       <c r="C66" s="5">
-        <v>46198.893706874995</v>
+        <v>46198.72704020834</v>
       </c>
       <c r="D66" s="5">
-        <v>46203.714927361114</v>
+        <v>46203.54826069444</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5478,10 +5486,10 @@
         <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5491,19 +5499,19 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B67" s="9">
+        <v>46146.62073795139</v>
+      </c>
+      <c r="C67" s="9">
+        <v>46200.51667719908</v>
+      </c>
+      <c r="D67" s="9">
+        <v>46200.526537233796</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="B67" s="9">
-        <v>46146.78740461805</v>
-      </c>
-      <c r="C67" s="9">
-        <v>46200.68334386574</v>
-      </c>
-      <c r="D67" s="9">
-        <v>46200.69320390046</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5543,7 +5551,7 @@
         <v>46205</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5557,13 +5565,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.787408564815</v>
+        <v>46146.62074189815</v>
       </c>
       <c r="C68" s="5">
-        <v>46200.69310333334</v>
+        <v>46200.52643666667</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.7149283912</v>
+        <v>46203.548261724536</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5591,10 +5599,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>244</v>
@@ -5610,13 +5618,13 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.78741372685</v>
+        <v>46146.62074706018</v>
       </c>
       <c r="C69" s="9">
-        <v>46200.693189224534</v>
+        <v>46200.52652255787</v>
       </c>
       <c r="D69" s="9">
-        <v>46203.714929317124</v>
+        <v>46203.54826265047</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5644,7 +5652,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>246</v>
@@ -5663,11 +5671,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.78743457176</v>
+        <v>46146.62076790509</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.92121962963</v>
+        <v>46146.754552962964</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5710,11 +5718,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.787437465275</v>
+        <v>46146.62077079861</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.78551768519</v>
+        <v>46191.61885101852</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5771,11 +5779,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.78744341435</v>
+        <v>46146.62077674769</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.18259200231</v>
+        <v>46157.01592533565</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5832,11 +5840,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.7874489699</v>
+        <v>46146.620782303246</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46203.70999737269</v>
+        <v>46203.543330706016</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5893,11 +5901,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.78746039352</v>
+        <v>46146.62079372685</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46146.94183069444</v>
+        <v>46205.42500519676</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5945,8 +5953,8 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>100</v>
+      <c r="U74" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5954,11 +5962,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.78750452546</v>
+        <v>46146.6208378588</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.58902260417</v>
+        <v>46197.422355937495</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -6001,11 +6009,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.787508912035</v>
+        <v>46146.62084224537</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46200.6931983449</v>
+        <v>46200.526531678246</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6064,11 +6072,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.78752016203</v>
+        <v>46146.62085349537</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46200.693112696754</v>
+        <v>46200.5264460301</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6117,11 +6125,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.78752439815</v>
+        <v>46146.62085773148</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46200.693198877314</v>
+        <v>46200.52653221065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6170,13 +6178,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.78758131944</v>
+        <v>46146.620914652776</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.58901480324</v>
+        <v>46197.42234813658</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.5890270949</v>
+        <v>46197.422360428245</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6233,13 +6241,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.78758657408</v>
+        <v>46146.62091990741</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.58893424769</v>
+        <v>46197.422267581016</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.71494715278</v>
+        <v>46203.54828048611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6286,13 +6294,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.787592939814</v>
+        <v>46146.62092627315</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.58900142361</v>
+        <v>46197.42233475695</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.71494597222</v>
+        <v>46203.548279305556</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6339,11 +6347,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.78761755787</v>
+        <v>46146.6209508912</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.94198379629</v>
+        <v>46146.77531712963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6402,11 +6410,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.78762708334</v>
+        <v>46146.620960416665</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46203.71494815972</v>
+        <v>46203.54828149306</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6453,11 +6461,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.78763331019</v>
+        <v>46146.62096664352</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46203.71494907407</v>
+        <v>46203.548282407406</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6504,11 +6512,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.78769865741</v>
+        <v>46146.62103199074</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.941980902775</v>
+        <v>46146.77531423611</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6565,11 +6573,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.787703553244</v>
+        <v>46146.62103688657</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46203.71494643518</v>
+        <v>46203.54827976852</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6616,11 +6624,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.78770892361</v>
+        <v>46146.62104225694</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46203.7149375</v>
+        <v>46203.54827083333</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6667,11 +6675,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.78773052084</v>
+        <v>46146.62106385417</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94197813657</v>
+        <v>46146.77531146991</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6728,11 +6736,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.78773511574</v>
+        <v>46146.62106844907</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94237260417</v>
+        <v>46146.7757059375</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6779,11 +6787,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.78774035879</v>
+        <v>46146.621073692135</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237009259</v>
+        <v>46146.77570342593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6830,11 +6838,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.787759479164</v>
+        <v>46146.6210928125</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94197326389</v>
+        <v>46146.77530659722</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6891,11 +6899,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.78776425926</v>
+        <v>46146.62109759259</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94244866898</v>
+        <v>46146.77578200231</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6942,11 +6950,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.787768587965</v>
+        <v>46146.62110192129</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244559028</v>
+        <v>46146.775778923606</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6993,11 +7001,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.78778571759</v>
+        <v>46146.62111905093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.9405634838</v>
+        <v>46146.77389681713</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7040,11 +7048,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.78778912037</v>
+        <v>46146.621122453704</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9429809375</v>
+        <v>46146.77631427083</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7101,11 +7109,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.78779429398</v>
+        <v>46146.62112762731</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.942643194445</v>
+        <v>46146.77597652777</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7152,11 +7160,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.787798414356</v>
+        <v>46146.621131747685</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.94264393518</v>
+        <v>46146.77597726852</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7203,11 +7211,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.787814745374</v>
+        <v>46146.6211480787</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94289535879</v>
+        <v>46146.77622869213</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7264,11 +7272,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.78781900463</v>
+        <v>46146.62115233796</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94285763889</v>
+        <v>46146.77619097222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7315,11 +7323,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.787823148145</v>
+        <v>46146.62115648148</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285530093</v>
+        <v>46146.77618863426</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7366,11 +7374,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.787891527776</v>
+        <v>46146.62122486111</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.9431597338</v>
+        <v>46146.776493067126</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7427,11 +7435,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.78789762731</v>
+        <v>46146.62123096065</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.94342792824</v>
+        <v>46146.77676126157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7478,11 +7486,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.78790538195</v>
+        <v>46146.62123871528</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94346471065</v>
+        <v>46146.77679804398</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7529,11 +7537,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.787928171296</v>
+        <v>46146.621261504624</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94327527778</v>
+        <v>46146.77660861111</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7590,11 +7598,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.787934409724</v>
+        <v>46146.62126774306</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94332239583</v>
+        <v>46146.77665572916</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7641,11 +7649,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.787939131944</v>
+        <v>46146.62127246527</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.943319872684</v>
+        <v>46146.77665320602</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7692,11 +7700,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.787957974535</v>
+        <v>46146.62129130787</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.94056351852</v>
+        <v>46146.77389685185</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7739,11 +7747,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.78796153935</v>
+        <v>46146.62129487269</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94352958333</v>
+        <v>46146.77686291667</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7802,11 +7810,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.78796724537</v>
+        <v>46146.6213005787</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.86770128472</v>
+        <v>46196.701034618054</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1729,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46146.62019984954</v>
+        <v>46146.7868665162</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70543086805</v>
+        <v>46175.872097534724</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.70544517361</v>
+        <v>46175.872111840275</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1782,13 +1782,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46146.620326226854</v>
+        <v>46146.78699289352</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70540511574</v>
+        <v>46175.8720717824</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70543134259</v>
+        <v>46175.87209800926</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1845,13 +1845,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46146.62032965278</v>
+        <v>46146.786996319446</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70540572917</v>
+        <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.70543135417</v>
+        <v>46175.87209802083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1908,13 +1908,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46146.620332997685</v>
+        <v>46146.78699966436</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.705406099536</v>
+        <v>46175.8720727662</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.70543190972</v>
+        <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -1971,13 +1971,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46146.62033583333</v>
+        <v>46146.7870025</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.705406469904</v>
+        <v>46175.872073136576</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70543217592</v>
+        <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2034,13 +2034,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46146.62033996527</v>
+        <v>46146.787006631945</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.705407002315</v>
+        <v>46175.87207366899</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70543275463</v>
+        <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2097,13 +2097,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46146.620205439816</v>
+        <v>46146.78687210648</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.482801192135</v>
+        <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.48281369213</v>
+        <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2150,13 +2150,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46146.62034349537</v>
+        <v>46146.787010162036</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.48154974537</v>
+        <v>46197.64821641204</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.481566319446</v>
+        <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2215,13 +2215,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46146.62034891204</v>
+        <v>46146.7870155787</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.482300578704</v>
+        <v>46197.648967245375</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.48231569445</v>
+        <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2280,13 +2280,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46146.620354733794</v>
+        <v>46146.787021400465</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.48278497685</v>
+        <v>46197.64945164352</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.48280087963</v>
+        <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2345,13 +2345,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46146.62020984954</v>
+        <v>46146.7868765162</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.74133881944</v>
+        <v>46204.90800548611</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.7413519213</v>
+        <v>46204.908018587965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2398,13 +2398,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46146.620374895836</v>
+        <v>46146.7870415625</v>
       </c>
       <c r="C15" s="9">
-        <v>46203.54272493055</v>
+        <v>46203.70939159722</v>
       </c>
       <c r="D15" s="9">
-        <v>46203.54274957176</v>
+        <v>46203.70941623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2463,13 +2463,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46146.62038076389</v>
+        <v>46146.78704743055</v>
       </c>
       <c r="C16" s="5">
-        <v>46203.5427753125</v>
+        <v>46203.70944197917</v>
       </c>
       <c r="D16" s="5">
-        <v>46203.54279086806</v>
+        <v>46203.70945753472</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2528,13 +2528,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46146.62038653935</v>
+        <v>46146.78705320602</v>
       </c>
       <c r="C17" s="9">
-        <v>46191.61742108796</v>
+        <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.74051469908</v>
+        <v>46204.907181365736</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2593,13 +2593,13 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46146.620392384255</v>
+        <v>46146.78705905093</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.740464456016</v>
+        <v>46204.90713112269</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.74048180555</v>
+        <v>46204.90714847222</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2658,13 +2658,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46146.620402858796</v>
+        <v>46146.78706952547</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.74084907408</v>
+        <v>46204.90751574074</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.740865115746</v>
+        <v>46204.9075317824</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2723,13 +2723,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46146.62040673611</v>
+        <v>46146.78707340278</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.74109982639</v>
+        <v>46204.90776649305</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.7411158912</v>
+        <v>46204.90778255787</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2788,13 +2788,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46146.62041070602</v>
+        <v>46146.78707737269</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.74132241898</v>
+        <v>46204.90798908565</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.74133951389</v>
+        <v>46204.90800618056</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2853,11 +2853,11 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46146.62021439815</v>
+        <v>46146.786881064814</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46203.54334045139</v>
+        <v>46205.606627430556</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2900,11 +2900,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46146.6204152662</v>
+        <v>46146.78708193287</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.69203420139</v>
+        <v>46169.858700868055</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2963,11 +2963,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46146.620420127314</v>
+        <v>46146.78708679398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46203.542781805554</v>
+        <v>46203.70944847222</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3022,11 +3022,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46146.62042537037</v>
+        <v>46146.78709203703</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.69230549769</v>
+        <v>46169.85897216435</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3081,13 +3081,13 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46146.62043092593</v>
+        <v>46146.78709759259</v>
       </c>
       <c r="C26" s="5">
-        <v>46195.759676851856</v>
+        <v>46195.92634351852</v>
       </c>
       <c r="D26" s="5">
-        <v>46195.75969194445</v>
+        <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3146,13 +3146,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46146.62043646991</v>
+        <v>46146.78710313658</v>
       </c>
       <c r="C27" s="9">
-        <v>46195.759660509255</v>
+        <v>46195.92632717593</v>
       </c>
       <c r="D27" s="9">
-        <v>46195.75966293982</v>
+        <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3207,13 +3207,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46146.62044230324</v>
+        <v>46146.787108969904</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.61883501157</v>
+        <v>46191.78550167824</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.75967141204</v>
+        <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3268,13 +3268,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46146.62044760417</v>
+        <v>46146.78711427083</v>
       </c>
       <c r="C29" s="9">
-        <v>46203.543324328704</v>
+        <v>46203.70999099537</v>
       </c>
       <c r="D29" s="9">
-        <v>46203.543349687505</v>
+        <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3333,13 +3333,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46146.62045268518</v>
+        <v>46146.78711935185</v>
       </c>
       <c r="C30" s="5">
-        <v>46203.54324489583</v>
+        <v>46203.7099115625</v>
       </c>
       <c r="D30" s="5">
-        <v>46203.54324746528</v>
+        <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3394,13 +3394,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46146.620457997684</v>
+        <v>46146.78712466435</v>
       </c>
       <c r="C31" s="9">
-        <v>46203.54330881944</v>
+        <v>46203.70997548611</v>
       </c>
       <c r="D31" s="9">
-        <v>46203.543311319445</v>
+        <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3455,13 +3455,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46146.62046320602</v>
+        <v>46146.78712987268</v>
       </c>
       <c r="C32" s="5">
-        <v>46203.54329217593</v>
+        <v>46203.70995884259</v>
       </c>
       <c r="D32" s="5">
-        <v>46203.54329601851</v>
+        <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3516,11 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46146.62052135417</v>
-      </c>
-      <c r="C33" s="10"/>
+        <v>46146.78718802083</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46205.60661743056</v>
+      </c>
       <c r="D33" s="9">
-        <v>46190.01523118056</v>
+        <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3568,10 +3570,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3579,11 +3581,13 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46146.620526597224</v>
-      </c>
-      <c r="C34" s="6"/>
+        <v>46146.78719326389</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46205.60655060185</v>
+      </c>
       <c r="D34" s="5">
-        <v>46204.74047564815</v>
+        <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3638,11 +3642,13 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46146.62053138889</v>
-      </c>
-      <c r="C35" s="10"/>
+        <v>46146.78719805555</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46205.60660341435</v>
+      </c>
       <c r="D35" s="9">
-        <v>46189.001982939815</v>
+        <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3697,11 +3703,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46146.62054903935</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>46146.78721570602</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46205.60684907407</v>
+      </c>
       <c r="D36" s="5">
-        <v>46190.01523125</v>
+        <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3749,10 +3757,10 @@
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3760,11 +3768,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46146.6205521875</v>
-      </c>
-      <c r="C37" s="10"/>
+        <v>46146.787218854166</v>
+      </c>
+      <c r="C37" s="9">
+        <v>46205.60679372685</v>
+      </c>
       <c r="D37" s="9">
-        <v>46204.740859328704</v>
+        <v>46205.60679543982</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>85</v>
@@ -3813,11 +3823,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46146.62055623843</v>
-      </c>
-      <c r="C38" s="6"/>
+        <v>46146.78722290509</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46205.606834363425</v>
+      </c>
       <c r="D38" s="5">
-        <v>46189.001974803235</v>
+        <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3866,13 +3878,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46146.620560069445</v>
+        <v>46146.78722673611</v>
       </c>
       <c r="C39" s="9">
-        <v>46205.425039027774</v>
+        <v>46205.591705694445</v>
       </c>
       <c r="D39" s="9">
-        <v>46205.42512828704</v>
+        <v>46205.5917949537</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3931,13 +3943,13 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46146.62056321759</v>
+        <v>46146.787229884256</v>
       </c>
       <c r="C40" s="5">
-        <v>46205.38085069445</v>
+        <v>46205.54751736111</v>
       </c>
       <c r="D40" s="5">
-        <v>46205.38085299768</v>
+        <v>46205.54751966435</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>91</v>
@@ -3986,13 +3998,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46146.6205671412</v>
+        <v>46146.787233807874</v>
       </c>
       <c r="C41" s="9">
-        <v>46205.424983460645</v>
+        <v>46205.59165012732</v>
       </c>
       <c r="D41" s="9">
-        <v>46205.42498578704</v>
+        <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4041,13 +4053,13 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46146.75478928241</v>
+        <v>46146.92145594908</v>
       </c>
       <c r="C42" s="5">
-        <v>46205.42502674769</v>
+        <v>46205.59169341435</v>
       </c>
       <c r="D42" s="5">
-        <v>46205.425028125</v>
+        <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4094,11 +4106,13 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46146.62057075232</v>
-      </c>
-      <c r="C43" s="10"/>
+        <v>46146.78723741898</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46205.6073940162</v>
+      </c>
       <c r="D43" s="9">
-        <v>46190.01523150463</v>
+        <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4146,10 +4160,10 @@
         <v>33</v>
       </c>
       <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4157,11 +4171,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46146.62057396991</v>
-      </c>
-      <c r="C44" s="6"/>
+        <v>46146.78724063658</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46205.607339317125</v>
+      </c>
       <c r="D44" s="5">
-        <v>46204.74110706018</v>
+        <v>46205.607340787035</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>88</v>
@@ -4210,11 +4226,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46146.62057800926</v>
-      </c>
-      <c r="C45" s="10"/>
+        <v>46146.78724467593</v>
+      </c>
+      <c r="C45" s="9">
+        <v>46205.607378009256</v>
+      </c>
       <c r="D45" s="9">
-        <v>46189.00197628472</v>
+        <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4263,11 +4281,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46146.620219097225</v>
+        <v>46146.78688576389</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.548229374996</v>
+        <v>46203.71489604167</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4312,13 +4330,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46146.62058282408</v>
+        <v>46146.78724949074</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.54429189815</v>
+        <v>46197.710958564814</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.54435372685</v>
+        <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4377,13 +4395,13 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46146.62058797454</v>
+        <v>46146.7872546412</v>
       </c>
       <c r="C48" s="5">
-        <v>46203.54819519676</v>
+        <v>46203.714861863424</v>
       </c>
       <c r="D48" s="5">
-        <v>46203.548220069446</v>
+        <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4442,13 +4460,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46146.62059395833</v>
+        <v>46146.787260625</v>
       </c>
       <c r="C49" s="9">
-        <v>46203.54825155092</v>
+        <v>46203.71491821759</v>
       </c>
       <c r="D49" s="9">
-        <v>46203.548268425926</v>
+        <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>81</v>
@@ -4505,11 +4523,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46146.620612175924</v>
+        <v>46146.78727884259</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.77304238426</v>
+        <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4566,11 +4584,11 @@
         <v>192</v>
       </c>
       <c r="B51" s="9">
-        <v>46146.620615949076</v>
+        <v>46146.78728261574</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.77290814815</v>
+        <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>193</v>
@@ -4617,11 +4635,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46146.62061986111</v>
+        <v>46146.787286527775</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.77290880787</v>
+        <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4668,11 +4686,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46146.62067509259</v>
+        <v>46146.787341759264</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46200.517117152776</v>
+        <v>46200.68378381945</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4717,11 +4735,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46146.62067858796</v>
+        <v>46146.787345254634</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46200.51703649305</v>
+        <v>46205.60662056713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4771,8 +4789,8 @@
       <c r="T54" s="6">
         <v>1</v>
       </c>
-      <c r="U54" s="7" t="s">
-        <v>27</v>
+      <c r="U54" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4780,13 +4798,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="9">
-        <v>46146.62069221065</v>
+        <v>46146.787358877315</v>
       </c>
       <c r="C55" s="9">
-        <v>46200.51710871528</v>
+        <v>46200.68377538194</v>
       </c>
       <c r="D55" s="9">
-        <v>46200.51711047454</v>
+        <v>46200.6837771412</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>205</v>
@@ -4843,11 +4861,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46146.620683981484</v>
+        <v>46146.78735064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46192.00657780093</v>
+        <v>46205.606852488425</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4897,8 +4915,8 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="11" t="s">
-        <v>100</v>
+      <c r="U56" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4906,13 +4924,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="9">
-        <v>46146.630636851856</v>
+        <v>46146.79730351851</v>
       </c>
       <c r="C57" s="9">
-        <v>46200.5171996412</v>
+        <v>46200.68386630787</v>
       </c>
       <c r="D57" s="9">
-        <v>46200.517220497684</v>
+        <v>46200.683887164356</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>212</v>
@@ -4971,11 +4989,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46146.62068782408</v>
+        <v>46146.78735449074</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.00656401621</v>
+        <v>46205.607397581014</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -5025,8 +5043,8 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>100</v>
+      <c r="U58" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5034,13 +5052,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46146.63084329861</v>
+        <v>46146.79750996528</v>
       </c>
       <c r="C59" s="9">
-        <v>46200.51729280093</v>
+        <v>46200.68395946759</v>
       </c>
       <c r="D59" s="9">
-        <v>46200.51730949074</v>
+        <v>46200.68397615741</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -5099,13 +5117,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46146.62069773149</v>
+        <v>46146.787364398144</v>
       </c>
       <c r="C60" s="5">
-        <v>46200.51669892361</v>
+        <v>46200.683365590274</v>
       </c>
       <c r="D60" s="5">
-        <v>46200.516712592595</v>
+        <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5152,13 +5170,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46146.62070028935</v>
+        <v>46146.78736695602</v>
       </c>
       <c r="C61" s="9">
-        <v>46198.72679508102</v>
+        <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46198.72695090278</v>
+        <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5217,13 +5235,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46146.62771714121</v>
+        <v>46146.79438380787</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.72694634259</v>
+        <v>46198.89361300926</v>
       </c>
       <c r="D62" s="5">
-        <v>46200.51730047454</v>
+        <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5272,13 +5290,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46146.627734525464</v>
+        <v>46146.79440119213</v>
       </c>
       <c r="C63" s="9">
-        <v>46198.727171562496</v>
+        <v>46198.89383822917</v>
       </c>
       <c r="D63" s="9">
-        <v>46200.51730125</v>
+        <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>227</v>
@@ -5327,13 +5345,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46146.620705127316</v>
+        <v>46146.78737179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46198.727370567125</v>
+        <v>46198.8940372338</v>
       </c>
       <c r="D64" s="5">
-        <v>46205.03654446759</v>
+        <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5392,13 +5410,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="9">
-        <v>46146.620708946764</v>
+        <v>46146.78737561342</v>
       </c>
       <c r="C65" s="9">
-        <v>46198.727355428244</v>
+        <v>46198.89402209491</v>
       </c>
       <c r="D65" s="9">
-        <v>46203.54825930556</v>
+        <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>227</v>
@@ -5447,13 +5465,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46146.6207152662</v>
+        <v>46146.78738193287</v>
       </c>
       <c r="C66" s="5">
-        <v>46198.72704020834</v>
+        <v>46198.893706874995</v>
       </c>
       <c r="D66" s="5">
-        <v>46203.54826069444</v>
+        <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5502,13 +5520,13 @@
         <v>240</v>
       </c>
       <c r="B67" s="9">
-        <v>46146.62073795139</v>
+        <v>46146.78740461805</v>
       </c>
       <c r="C67" s="9">
-        <v>46200.51667719908</v>
+        <v>46200.68334386574</v>
       </c>
       <c r="D67" s="9">
-        <v>46200.526537233796</v>
+        <v>46200.69320390046</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>241</v>
@@ -5565,13 +5583,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46146.62074189815</v>
+        <v>46146.787408564815</v>
       </c>
       <c r="C68" s="5">
-        <v>46200.52643666667</v>
+        <v>46200.69310333334</v>
       </c>
       <c r="D68" s="5">
-        <v>46203.548261724536</v>
+        <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5618,13 +5636,13 @@
         <v>245</v>
       </c>
       <c r="B69" s="9">
-        <v>46146.62074706018</v>
+        <v>46146.78741372685</v>
       </c>
       <c r="C69" s="9">
-        <v>46200.52652255787</v>
+        <v>46200.693189224534</v>
       </c>
       <c r="D69" s="9">
-        <v>46203.54826265047</v>
+        <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5671,11 +5689,11 @@
         <v>247</v>
       </c>
       <c r="B70" s="5">
-        <v>46146.62076790509</v>
+        <v>46146.78743457176</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.754552962964</v>
+        <v>46146.92121962963</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>197</v>
@@ -5718,11 +5736,11 @@
         <v>249</v>
       </c>
       <c r="B71" s="9">
-        <v>46146.62077079861</v>
+        <v>46146.787437465275</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46191.61885101852</v>
+        <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5779,11 +5797,11 @@
         <v>252</v>
       </c>
       <c r="B72" s="5">
-        <v>46146.62077674769</v>
+        <v>46146.78744341435</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46157.01592533565</v>
+        <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5840,11 +5858,11 @@
         <v>255</v>
       </c>
       <c r="B73" s="9">
-        <v>46146.620782303246</v>
+        <v>46146.7874489699</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46203.543330706016</v>
+        <v>46203.70999737269</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5901,11 +5919,11 @@
         <v>257</v>
       </c>
       <c r="B74" s="5">
-        <v>46146.62079372685</v>
+        <v>46146.78746039352</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46205.42500519676</v>
+        <v>46205.591671863425</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5962,11 +5980,11 @@
         <v>260</v>
       </c>
       <c r="B75" s="9">
-        <v>46146.6208378588</v>
+        <v>46146.78750452546</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.422355937495</v>
+        <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -6009,11 +6027,11 @@
         <v>263</v>
       </c>
       <c r="B76" s="5">
-        <v>46146.62084224537</v>
+        <v>46146.787508912035</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46200.526531678246</v>
+        <v>46200.6931983449</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6072,11 +6090,11 @@
         <v>266</v>
       </c>
       <c r="B77" s="9">
-        <v>46146.62085349537</v>
+        <v>46146.78752016203</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46200.5264460301</v>
+        <v>46200.693112696754</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6125,11 +6143,11 @@
         <v>268</v>
       </c>
       <c r="B78" s="5">
-        <v>46146.62085773148</v>
+        <v>46146.78752439815</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46200.52653221065</v>
+        <v>46200.693198877314</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6178,13 +6196,13 @@
         <v>269</v>
       </c>
       <c r="B79" s="9">
-        <v>46146.620914652776</v>
+        <v>46146.78758131944</v>
       </c>
       <c r="C79" s="9">
-        <v>46197.42234813658</v>
+        <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.422360428245</v>
+        <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6241,13 +6259,13 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46146.62091990741</v>
+        <v>46146.78758657408</v>
       </c>
       <c r="C80" s="5">
-        <v>46197.422267581016</v>
+        <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.54828048611</v>
+        <v>46203.71494715278</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6294,13 +6312,13 @@
         <v>274</v>
       </c>
       <c r="B81" s="9">
-        <v>46146.62092627315</v>
+        <v>46146.787592939814</v>
       </c>
       <c r="C81" s="9">
-        <v>46197.42233475695</v>
+        <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.548279305556</v>
+        <v>46203.71494597222</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>193</v>
@@ -6347,11 +6365,11 @@
         <v>276</v>
       </c>
       <c r="B82" s="5">
-        <v>46146.6209508912</v>
+        <v>46146.78761755787</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46146.77531712963</v>
+        <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6410,11 +6428,11 @@
         <v>278</v>
       </c>
       <c r="B83" s="9">
-        <v>46146.620960416665</v>
+        <v>46146.78762708334</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46203.54828149306</v>
+        <v>46203.71494815972</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6461,11 +6479,11 @@
         <v>280</v>
       </c>
       <c r="B84" s="5">
-        <v>46146.62096664352</v>
+        <v>46146.78763331019</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46203.548282407406</v>
+        <v>46203.71494907407</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6512,11 +6530,11 @@
         <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46146.62103199074</v>
+        <v>46146.78769865741</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46146.77531423611</v>
+        <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6573,11 +6591,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46146.62103688657</v>
+        <v>46146.787703553244</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46203.54827976852</v>
+        <v>46203.71494643518</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6624,11 +6642,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46146.62104225694</v>
+        <v>46146.78770892361</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46203.54827083333</v>
+        <v>46203.7149375</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6675,11 +6693,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46146.62106385417</v>
+        <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.77531146991</v>
+        <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6736,11 +6754,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46146.62106844907</v>
+        <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.7757059375</v>
+        <v>46146.94237260417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6787,11 +6805,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46146.621073692135</v>
+        <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.77570342593</v>
+        <v>46146.94237009259</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -6838,11 +6856,11 @@
         <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46146.6210928125</v>
+        <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.77530659722</v>
+        <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>294</v>
@@ -6899,11 +6917,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46146.62109759259</v>
+        <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.77578200231</v>
+        <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>193</v>
@@ -6950,11 +6968,11 @@
         <v>298</v>
       </c>
       <c r="B93" s="9">
-        <v>46146.62110192129</v>
+        <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.775778923606</v>
+        <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -7001,11 +7019,11 @@
         <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46146.62111905093</v>
+        <v>46146.78778571759</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.77389681713</v>
+        <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7048,11 +7066,11 @@
         <v>302</v>
       </c>
       <c r="B95" s="9">
-        <v>46146.621122453704</v>
+        <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.77631427083</v>
+        <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -7109,11 +7127,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46146.62112762731</v>
+        <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.77597652777</v>
+        <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7160,11 +7178,11 @@
         <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46146.621131747685</v>
+        <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.77597726852</v>
+        <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7211,11 +7229,11 @@
         <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46146.6211480787</v>
+        <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.77622869213</v>
+        <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>312</v>
@@ -7272,11 +7290,11 @@
         <v>313</v>
       </c>
       <c r="B99" s="9">
-        <v>46146.62115233796</v>
+        <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.77619097222</v>
+        <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7323,11 +7341,11 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <v>46146.62115648148</v>
+        <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.77618863426</v>
+        <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7374,11 +7392,11 @@
         <v>317</v>
       </c>
       <c r="B101" s="9">
-        <v>46146.62122486111</v>
+        <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.776493067126</v>
+        <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>318</v>
@@ -7435,11 +7453,11 @@
         <v>319</v>
       </c>
       <c r="B102" s="5">
-        <v>46146.62123096065</v>
+        <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.77676126157</v>
+        <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7486,11 +7504,11 @@
         <v>321</v>
       </c>
       <c r="B103" s="9">
-        <v>46146.62123871528</v>
+        <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.77679804398</v>
+        <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>193</v>
@@ -7537,11 +7555,11 @@
         <v>323</v>
       </c>
       <c r="B104" s="5">
-        <v>46146.621261504624</v>
+        <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.77660861111</v>
+        <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>324</v>
@@ -7598,11 +7616,11 @@
         <v>326</v>
       </c>
       <c r="B105" s="9">
-        <v>46146.62126774306</v>
+        <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.77665572916</v>
+        <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>193</v>
@@ -7649,11 +7667,11 @@
         <v>327</v>
       </c>
       <c r="B106" s="5">
-        <v>46146.62127246527</v>
+        <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.77665320602</v>
+        <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>193</v>
@@ -7700,11 +7718,11 @@
         <v>328</v>
       </c>
       <c r="B107" s="9">
-        <v>46146.62129130787</v>
+        <v>46146.787957974535</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46146.77389685185</v>
+        <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>329</v>
@@ -7747,11 +7765,11 @@
         <v>331</v>
       </c>
       <c r="B108" s="5">
-        <v>46146.62129487269</v>
+        <v>46146.78796153935</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.77686291667</v>
+        <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>332</v>
@@ -7810,11 +7828,11 @@
         <v>335</v>
       </c>
       <c r="B109" s="9">
-        <v>46146.6213005787</v>
+        <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.701034618054</v>
+        <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>336</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="336">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -818,9 +818,6 @@
   </si>
   <si>
     <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214511245167387</t>
@@ -5526,7 +5523,7 @@
         <v>46200.68334386574</v>
       </c>
       <c r="D67" s="9">
-        <v>46200.69320390046</v>
+        <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>241</v>
@@ -5568,8 +5565,8 @@
       <c r="R67" s="9">
         <v>46205</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>242</v>
+      <c r="S67" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5580,7 +5577,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5623,7 +5620,7 @@
         <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5633,7 +5630,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5673,10 +5670,10 @@
         <v>241</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5686,7 +5683,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5720,7 +5717,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5733,7 +5730,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5743,7 +5740,7 @@
         <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5774,7 +5771,7 @@
         <v>115</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5794,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5804,7 +5801,7 @@
         <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5835,7 +5832,7 @@
         <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5855,7 +5852,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5865,7 +5862,7 @@
         <v>46203.70999737269</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5896,7 +5893,7 @@
         <v>124</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5916,7 +5913,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5926,7 +5923,7 @@
         <v>46205.591671863425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5957,7 +5954,7 @@
         <v>156</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5977,7 +5974,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -5987,7 +5984,7 @@
         <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6011,7 +6008,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6034,7 +6031,7 @@
         <v>46200.6931983449</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6061,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6087,7 +6084,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6124,10 +6121,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6177,10 +6174,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6193,7 +6190,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6205,7 +6202,7 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6230,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6256,7 +6253,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6293,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6346,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6362,7 +6359,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6372,7 +6369,7 @@
         <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6399,13 +6396,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6425,7 +6422,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6460,13 +6457,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6476,7 +6473,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6511,13 +6508,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6527,7 +6524,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6537,7 +6534,7 @@
         <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6562,13 +6559,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6588,7 +6585,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6623,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6639,7 +6636,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6674,13 +6671,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6690,7 +6687,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6700,7 +6697,7 @@
         <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6725,13 +6722,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6751,7 +6748,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6786,13 +6783,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6802,7 +6799,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6837,13 +6834,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6853,7 +6850,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6863,7 +6860,7 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6888,13 +6885,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6914,7 +6911,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6949,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6965,7 +6962,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -7000,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7016,7 +7013,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7026,7 +7023,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7050,7 +7047,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7063,7 +7060,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7073,16 +7070,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="H95" s="10" t="s">
         <v>304</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7098,13 +7095,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7140,10 +7137,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>304</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>305</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7159,13 +7156,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7175,7 +7172,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7191,10 +7188,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>304</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7210,13 +7207,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7226,7 +7223,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7236,7 +7233,7 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7261,13 +7258,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7287,7 +7284,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7322,13 +7319,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7338,7 +7335,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7373,13 +7370,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7389,7 +7386,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7399,7 +7396,7 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7424,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7450,7 +7447,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7485,13 +7482,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7501,7 +7498,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7536,13 +7533,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7552,7 +7549,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7562,7 +7559,7 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7587,13 +7584,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7613,7 +7610,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7648,13 +7645,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7664,7 +7661,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7699,13 +7696,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7715,7 +7712,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7725,7 +7722,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7749,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7762,7 +7759,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7772,16 +7769,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>334</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7799,13 +7796,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7825,7 +7822,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7835,7 +7832,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7862,13 +7859,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -553,6 +553,9 @@
     <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214511142484075</t>
   </si>
   <si>
@@ -613,82 +616,82 @@
     <t>Planos preliminar,Planos definitivos</t>
   </si>
   <si>
+    <t>1214511199027697</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199035045</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214511240985139</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901576</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901586</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901596</t>
+  </si>
+  <si>
+    <t>1214511155796713</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214511199027697</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199035045</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214511240985139</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901576</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901586</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901596</t>
-  </si>
-  <si>
-    <t>1214511155796713</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214511155796723</t>
@@ -3881,7 +3884,7 @@
         <v>46205.591705694445</v>
       </c>
       <c r="D39" s="9">
-        <v>46205.5917949537</v>
+        <v>46210.16859381944</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3925,8 +3928,8 @@
       <c r="R39" s="9">
         <v>46217</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>104</v>
+      <c r="S39" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3982,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3992,7 +3995,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4004,7 +4007,7 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4037,7 +4040,7 @@
         <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4047,7 +4050,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4059,16 +4062,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4087,7 +4090,7 @@
         <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4100,7 +4103,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4112,7 +4115,7 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4142,7 +4145,7 @@
         <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4165,7 +4168,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4204,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4232,7 +4235,7 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4259,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4275,17 +4278,19 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46210.528579108795</v>
+      </c>
       <c r="D46" s="5">
-        <v>46203.71489604167</v>
+        <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4309,7 +4314,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4317,9 +4322,11 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="12" t="s">
-        <v>173</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4363,7 +4370,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
@@ -4428,7 +4435,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>181</v>
@@ -4491,7 +4498,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>180</v>
@@ -4552,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>191</v>
@@ -4724,12 +4731,12 @@
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4739,16 +4746,16 @@
         <v>46205.60662056713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4772,7 +4779,7 @@
         <v>138</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4787,12 +4794,12 @@
         <v>1</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4804,16 +4811,16 @@
         <v>46200.6837771412</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4832,10 +4839,10 @@
         <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4855,7 +4862,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4865,16 +4872,16 @@
         <v>46205.606852488425</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4898,7 +4905,7 @@
         <v>146</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4913,12 +4920,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4930,16 +4937,16 @@
         <v>46200.683887164356</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4960,10 +4967,10 @@
         <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4983,7 +4990,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -4993,16 +5000,16 @@
         <v>46205.607397581014</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5023,10 +5030,10 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5041,12 +5048,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5058,16 +5065,16 @@
         <v>46200.68397615741</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5088,10 +5095,10 @@
         <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5111,7 +5118,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5123,7 +5130,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5147,7 +5154,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5164,7 +5171,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5176,16 +5183,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5203,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5229,7 +5236,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5241,16 +5248,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5268,13 +5275,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5284,7 +5291,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5296,16 +5303,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5323,13 +5330,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5339,7 +5346,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5351,16 +5358,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5378,13 +5385,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5404,7 +5411,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5416,16 +5423,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5443,13 +5450,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5459,7 +5466,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5471,16 +5478,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5498,13 +5505,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5514,7 +5521,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5526,16 +5533,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5551,13 +5558,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5572,12 +5579,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5589,16 +5596,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5614,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5630,7 +5637,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5642,16 +5649,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5667,13 +5674,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5683,7 +5690,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5717,7 +5724,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5730,7 +5737,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5740,16 +5747,16 @@
         <v>46191.78551768519</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5771,7 +5778,7 @@
         <v>115</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5786,12 +5793,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5801,16 +5808,16 @@
         <v>46157.18259200231</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5832,7 +5839,7 @@
         <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5852,7 +5859,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5862,16 +5869,16 @@
         <v>46203.70999737269</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5893,7 +5900,7 @@
         <v>124</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5908,12 +5915,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5923,16 +5930,16 @@
         <v>46205.591671863425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5951,10 +5958,10 @@
         <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5969,12 +5976,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -5984,7 +5991,7 @@
         <v>46197.58902260417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6008,7 +6015,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6021,7 +6028,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6031,7 +6038,7 @@
         <v>46200.6931983449</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6058,13 +6065,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6084,7 +6091,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6121,10 +6128,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6137,7 +6144,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6174,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6190,7 +6197,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6202,7 +6209,7 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6227,13 +6234,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6253,7 +6260,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6290,13 +6297,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6306,7 +6313,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6343,13 +6350,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6359,7 +6366,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6369,7 +6376,7 @@
         <v>46146.94198379629</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6396,13 +6403,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6422,7 +6429,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6457,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6473,7 +6480,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6508,13 +6515,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6524,7 +6531,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6534,7 +6541,7 @@
         <v>46146.941980902775</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6559,13 +6566,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6585,7 +6592,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6620,13 +6627,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6636,7 +6643,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6671,13 +6678,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6687,7 +6694,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6697,7 +6704,7 @@
         <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6722,13 +6729,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6748,7 +6755,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6783,13 +6790,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6799,7 +6806,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6834,13 +6841,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6850,7 +6857,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6860,7 +6867,7 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6885,13 +6892,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6911,7 +6918,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6946,13 +6953,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6962,7 +6969,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -6997,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7013,7 +7020,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7023,7 +7030,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7047,7 +7054,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7060,7 +7067,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7070,16 +7077,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7095,13 +7102,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7121,7 +7128,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7137,10 +7144,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7156,13 +7163,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7172,7 +7179,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7188,10 +7195,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7207,13 +7214,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7223,7 +7230,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7233,7 +7240,7 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7258,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7284,7 +7291,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7319,13 +7326,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7335,7 +7342,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7370,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7386,7 +7393,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7396,16 +7403,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7421,13 +7428,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7447,7 +7454,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7463,10 +7470,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7482,13 +7489,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7498,7 +7505,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7514,10 +7521,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7533,13 +7540,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7549,7 +7556,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7559,16 +7566,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7584,13 +7591,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7610,7 +7617,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7626,10 +7633,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7645,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7661,7 +7668,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7677,10 +7684,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7696,13 +7703,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7712,7 +7719,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7722,7 +7729,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7746,7 +7753,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7759,7 +7766,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7769,16 +7776,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7796,13 +7803,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7822,7 +7829,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7832,7 +7839,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7859,13 +7866,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5988,7 +5988,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46197.58902260417</v>
+        <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -6033,9 +6033,11 @@
       <c r="B76" s="5">
         <v>46146.787508912035</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46210.669946180555</v>
+      </c>
       <c r="D76" s="5">
-        <v>46200.6931983449</v>
+        <v>46210.669961203705</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6083,10 +6085,10 @@
         <v>104</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6096,9 +6098,11 @@
       <c r="B77" s="9">
         <v>46146.78752016203</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9">
+        <v>46210.66987290509</v>
+      </c>
       <c r="D77" s="9">
-        <v>46200.693112696754</v>
+        <v>46210.66987453704</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6149,9 +6153,11 @@
       <c r="B78" s="5">
         <v>46146.78752439815</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46210.66993070602</v>
+      </c>
       <c r="D78" s="5">
-        <v>46200.693198877314</v>
+        <v>46210.66993231481</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6371,9 +6377,11 @@
       <c r="B82" s="5">
         <v>46146.78761755787</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46210.670091631946</v>
+      </c>
       <c r="D82" s="5">
-        <v>46146.94198379629</v>
+        <v>46210.670105150464</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6421,10 +6429,10 @@
         <v>104</v>
       </c>
       <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U82" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6434,9 +6442,11 @@
       <c r="B83" s="9">
         <v>46146.78762708334</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46210.66999793981</v>
+      </c>
       <c r="D83" s="9">
-        <v>46203.71494815972</v>
+        <v>46210.66999954861</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6485,9 +6495,11 @@
       <c r="B84" s="5">
         <v>46146.78763331019</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46210.67007324074</v>
+      </c>
       <c r="D84" s="5">
-        <v>46203.71494907407</v>
+        <v>46210.670075243055</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6536,9 +6548,11 @@
       <c r="B85" s="9">
         <v>46146.78769865741</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46210.670307418986</v>
+      </c>
       <c r="D85" s="9">
-        <v>46146.941980902775</v>
+        <v>46210.67032010417</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6584,10 +6598,10 @@
         <v>104</v>
       </c>
       <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6597,9 +6611,11 @@
       <c r="B86" s="5">
         <v>46146.787703553244</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46210.67028576389</v>
+      </c>
       <c r="D86" s="5">
-        <v>46203.71494643518</v>
+        <v>46210.67028814815</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6648,9 +6664,11 @@
       <c r="B87" s="9">
         <v>46146.78770892361</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9">
+        <v>46210.67029284722</v>
+      </c>
       <c r="D87" s="9">
-        <v>46203.7149375</v>
+        <v>46210.67029388889</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6762,7 +6780,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46146.94237260417</v>
+        <v>46210.670293460644</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6813,7 +6831,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46146.94237009259</v>
+        <v>46210.67030641204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5927,7 +5927,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46205.591671863425</v>
+        <v>46211.19095658565</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>258</v>
@@ -5969,8 +5969,8 @@
       <c r="R74" s="5">
         <v>46218</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>104</v>
+      <c r="S74" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="337">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -379,6 +379,9 @@
     <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214511244996574</t>
   </si>
   <si>
@@ -394,21 +397,21 @@
     <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
   </si>
   <si>
+    <t>1214511244996589</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1214511244996589</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
     <t>1214511142420461</t>
   </si>
   <si>
@@ -689,9 +692,6 @@
   </si>
   <si>
     <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214511155796723</t>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46205.606627430556</v>
+        <v>46212.66398305555</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2893,30 +2893,34 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46212.6639628125</v>
+      </c>
       <c r="D23" s="9">
-        <v>46169.858700868055</v>
+        <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2937,7 +2941,7 @@
         <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>93</v>
@@ -2952,10 +2956,10 @@
         <v>33</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2965,9 +2969,11 @@
       <c r="B24" s="5">
         <v>46146.78708679398</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46212.66391207176</v>
+      </c>
       <c r="D24" s="5">
-        <v>46203.70944847222</v>
+        <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -2976,10 +2982,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2997,7 +3003,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>71</v>
@@ -3014,31 +3020,33 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46212.663946967594</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.85897216435</v>
+        <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3056,13 +3064,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3073,12 +3081,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3090,16 +3098,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3120,7 +3128,7 @@
         <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>93</v>
@@ -3143,7 +3151,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3155,16 +3163,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3182,13 +3190,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3199,12 +3207,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3216,16 +3224,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3243,13 +3251,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3260,12 +3268,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3277,16 +3285,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3307,7 +3315,7 @@
         <v>93</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>93</v>
@@ -3330,7 +3338,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3342,16 +3350,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3369,13 +3377,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3386,12 +3394,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3403,16 +3411,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3430,13 +3438,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3447,12 +3455,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3464,16 +3472,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3491,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3508,12 +3516,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3525,16 +3533,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3555,7 +3563,7 @@
         <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>93</v>
@@ -3578,7 +3586,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3590,16 +3598,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3617,13 +3625,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3634,12 +3642,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3651,16 +3659,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3678,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3695,12 +3703,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3712,16 +3720,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3742,7 +3750,7 @@
         <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3765,7 +3773,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3783,10 +3791,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3804,13 +3812,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3820,7 +3828,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3832,16 +3840,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3859,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3875,7 +3883,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3887,16 +3895,16 @@
         <v>46210.16859381944</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3917,7 +3925,7 @@
         <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3929,7 +3937,7 @@
         <v>46217</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3940,7 +3948,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3958,10 +3966,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3979,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3995,7 +4003,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4007,16 +4015,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4034,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4050,7 +4058,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4062,16 +4070,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4087,10 +4095,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4103,7 +4111,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4115,16 +4123,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4145,7 +4153,7 @@
         <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4168,7 +4176,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4186,10 +4194,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4207,13 +4215,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4223,7 +4231,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4235,16 +4243,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4262,13 +4270,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4278,7 +4286,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4290,7 +4298,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4314,7 +4322,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4331,7 +4339,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4343,16 +4351,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4370,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4396,7 +4404,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4408,16 +4416,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4435,13 +4443,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4461,7 +4469,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4479,10 +4487,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4498,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4524,7 +4532,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4534,16 +4542,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4559,10 +4567,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4580,12 +4588,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4595,16 +4603,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4620,13 +4628,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4636,7 +4644,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4646,16 +4654,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4671,13 +4679,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4687,7 +4695,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4697,7 +4705,7 @@
         <v>46200.68378381945</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4721,7 +4729,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4731,7 +4739,7 @@
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4773,10 +4781,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>204</v>
@@ -4794,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4817,10 +4825,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4836,7 +4844,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>207</v>
@@ -4899,10 +4907,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>211</v>
@@ -4920,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4943,10 +4951,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4964,7 +4972,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>210</v>
@@ -5027,10 +5035,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>217</v>
@@ -5048,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5071,10 +5079,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5092,7 +5100,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>216</v>
@@ -5539,10 +5547,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5579,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5602,10 +5610,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5655,10 +5663,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5697,10 +5705,10 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46146.92121962963</v>
+        <v>46212.664260949074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5733,7 +5741,9 @@
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
       <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="U70" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
@@ -5742,9 +5752,11 @@
       <c r="B71" s="9">
         <v>46146.787437465275</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46212.66404712963</v>
+      </c>
       <c r="D71" s="9">
-        <v>46191.78551768519</v>
+        <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>250</v>
@@ -5772,10 +5784,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>251</v>
@@ -5790,10 +5802,10 @@
         <v>33</v>
       </c>
       <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="12" t="s">
-        <v>199</v>
+        <v>1</v>
+      </c>
+      <c r="U71" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5803,9 +5815,11 @@
       <c r="B72" s="5">
         <v>46146.78744341435</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46212.66403994213</v>
+      </c>
       <c r="D72" s="5">
-        <v>46157.18259200231</v>
+        <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>253</v>
@@ -5833,10 +5847,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>254</v>
@@ -5851,10 +5865,10 @@
         <v>33</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5864,9 +5878,11 @@
       <c r="B73" s="9">
         <v>46146.7874489699</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46212.66424371528</v>
+      </c>
       <c r="D73" s="9">
-        <v>46203.70999737269</v>
+        <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>256</v>
@@ -5894,10 +5910,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>251</v>
@@ -5912,10 +5928,10 @@
         <v>33</v>
       </c>
       <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>199</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5955,10 +5971,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>259</v>
@@ -5970,13 +5986,13 @@
         <v>46218</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6105,7 +6121,7 @@
         <v>46210.66987453704</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6160,7 +6176,7 @@
         <v>46210.66993231481</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6243,7 +6259,7 @@
         <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>261</v>
@@ -6275,10 +6291,10 @@
         <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.71494715278</v>
+        <v>46212.66404658565</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6328,10 +6344,10 @@
         <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.71494597222</v>
+        <v>46212.66404525463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6414,7 +6430,7 @@
         <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>261</v>
@@ -6446,10 +6462,10 @@
         <v>46210.66999793981</v>
       </c>
       <c r="D83" s="9">
-        <v>46210.66999954861</v>
+        <v>46212.66405841435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6499,10 +6515,10 @@
         <v>46210.67007324074</v>
       </c>
       <c r="D84" s="5">
-        <v>46210.670075243055</v>
+        <v>46212.664059675924</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6583,7 +6599,7 @@
         <v>261</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>261</v>
@@ -6615,10 +6631,10 @@
         <v>46210.67028576389</v>
       </c>
       <c r="D86" s="5">
-        <v>46210.67028814815</v>
+        <v>46212.664253379626</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6668,10 +6684,10 @@
         <v>46210.67029284722</v>
       </c>
       <c r="D87" s="9">
-        <v>46210.67029388889</v>
+        <v>46212.6642540625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6750,7 +6766,7 @@
         <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>261</v>
@@ -6768,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6783,7 +6799,7 @@
         <v>46210.670293460644</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6811,7 +6827,7 @@
         <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>291</v>
@@ -6834,7 +6850,7 @@
         <v>46210.67030641204</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6862,7 +6878,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6913,7 +6929,7 @@
         <v>261</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>295</v>
@@ -6931,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6946,7 +6962,7 @@
         <v>46146.94244866898</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6974,7 +6990,7 @@
         <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>297</v>
@@ -6997,7 +7013,7 @@
         <v>46146.94244559028</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7025,7 +7041,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>297</v>
@@ -7141,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7156,7 +7172,7 @@
         <v>46146.942643194445</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7184,7 +7200,7 @@
         <v>303</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>308</v>
@@ -7207,7 +7223,7 @@
         <v>46146.94264393518</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7235,7 +7251,7 @@
         <v>303</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>310</v>
@@ -7286,7 +7302,7 @@
         <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>300</v>
@@ -7304,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7319,7 +7335,7 @@
         <v>46146.94285763889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7347,7 +7363,7 @@
         <v>312</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>314</v>
@@ -7370,7 +7386,7 @@
         <v>46146.94285530093</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7398,7 +7414,7 @@
         <v>312</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>316</v>
@@ -7449,7 +7465,7 @@
         <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>300</v>
@@ -7467,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7482,7 +7498,7 @@
         <v>46146.94342792824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7510,7 +7526,7 @@
         <v>318</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>320</v>
@@ -7533,7 +7549,7 @@
         <v>46146.94346471065</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7561,7 +7577,7 @@
         <v>318</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>322</v>
@@ -7612,7 +7628,7 @@
         <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>325</v>
@@ -7630,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7645,7 +7661,7 @@
         <v>46146.94332239583</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7673,7 +7689,7 @@
         <v>324</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>324</v>
@@ -7696,7 +7712,7 @@
         <v>46146.943319872684</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7724,7 +7740,7 @@
         <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>324</v>
@@ -7842,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7905,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="342">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -379,348 +379,354 @@
     <t xml:space="preserve">rodete OT 4309,Motor OT 4309,Materiales corte Laser OT 4309,Alabe OT 4309 </t>
   </si>
   <si>
+    <t>1214511244996574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>1214511244996589</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214511142420461</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4309</t>
+  </si>
+  <si>
+    <t>Alabe OT 4309 ,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214511142420479</t>
+  </si>
+  <si>
+    <t>rodete OT 4309</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4309,Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240948634</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>rodete OT 4309,Fabricación Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240948652</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4309</t>
+  </si>
+  <si>
+    <t>rodete OT 4309,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214511142420756</t>
+  </si>
+  <si>
+    <t>Motor OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511142420771</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>1214511155826380</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214511155826398</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Motor OT 4309,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511240963370</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240963385</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511245068713</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4309</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002704</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199002714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>1214511199002729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214511142484065</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1214511142484075</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973505</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084879</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214511240973520</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973530</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199027682</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084764</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199027697</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199035045</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214511240985139</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901576</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901586</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901596</t>
+  </si>
+  <si>
+    <t>ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155796713</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511155796723</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511245146577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214511244996574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4309,Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>1214511244996589</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4309,Alabe OT 4309 </t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214511142420461</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4309</t>
-  </si>
-  <si>
-    <t>Alabe OT 4309 ,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214511142420479</t>
-  </si>
-  <si>
-    <t>rodete OT 4309</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4309,Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240948634</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>rodete OT 4309,Fabricación Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240948652</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4309</t>
-  </si>
-  <si>
-    <t>rodete OT 4309,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214511142420756</t>
-  </si>
-  <si>
-    <t>Motor OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511142420771</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Fabricación motor OT 4309,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>1214511155826380</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214511155826398</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Motor OT 4309,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511240963370</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240963385</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4309,Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511245068713</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4309</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002704</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4309 ,Generación OC Corte Plasma  OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199002714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4309,Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>1214511199002729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4309 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4309,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214511142484065</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1214511142484075</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973505</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084879</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214511240973520</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973530</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199027682</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084764</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199027697</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199035045</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214511240985139</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901576</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901586</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901596</t>
-  </si>
-  <si>
-    <t>1214511155796713</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511155796723</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511245146577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
-  </si>
-  <si>
     <t>1214511155961778</t>
   </si>
   <si>
@@ -949,7 +955,7 @@
     <t>Recepcion motor,check planos</t>
   </si>
   <si>
-    <t>Montaje motor,ZVN 1-9-75/2</t>
+    <t>Montaje motor,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511241215787</t>
@@ -958,12 +964,18 @@
     <t>check planos,Recepcion motor</t>
   </si>
   <si>
+    <t>Montaje motor,ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>1214511241247725</t>
   </si>
   <si>
     <t>Pruebas FAT</t>
   </si>
   <si>
+    <t>ot 4309- ZVN 1-9-75/2,ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>1214511241247740</t>
   </si>
   <si>
@@ -979,13 +991,16 @@
     <t>RE-PINTADO</t>
   </si>
   <si>
+    <t>ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1214511245386084</t>
   </si>
   <si>
-    <t>RE-PINTADO,ZVN 1-9-75/2</t>
+    <t>RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511245386099</t>
@@ -1012,19 +1027,19 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>ZVN 1-9-75/2,RE-PINTADO,ZVN 1-9-75/2</t>
+    <t>ot 4309- ZVN 1-9-75/2,RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511245412281</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,ZVN 1-9-75/2</t>
+    <t>Coordinacion Entrega con Cliente,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511241300240</t>
   </si>
   <si>
-    <t>ZVN 1-9-75/2,Coordinacion Entrega con Cliente</t>
+    <t>ot 4309- ZVN 1-9-75/2,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1214511245415624</t>
@@ -1036,13 +1051,13 @@
     <t>1214511245415639</t>
   </si>
   <si>
-    <t>ZVN 1-9-75/2,Embalaje</t>
+    <t>ot 4309- ZVN 1-9-75/2,Embalaje</t>
   </si>
   <si>
     <t>1214511245415654</t>
   </si>
   <si>
-    <t>Embalaje,ZVN 1-9-75/2</t>
+    <t>Embalaje,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511156219005</t>
@@ -1054,13 +1069,13 @@
     <t>1214511241390749</t>
   </si>
   <si>
-    <t>PACKING LIST,Planos Preliminar,ZVN 1-9-75/2</t>
+    <t>PACKING LIST,Planos Preliminar,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511241390769</t>
   </si>
   <si>
-    <t>Planos Preliminar,PACKING LIST,ZVN 1-9-75/2</t>
+    <t>Planos Preliminar,PACKING LIST,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511142894089</t>
@@ -2855,9 +2870,11 @@
       <c r="B22" s="5">
         <v>46146.786881064814</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46212.77674577547</v>
+      </c>
       <c r="D22" s="5">
-        <v>46212.66398305555</v>
+        <v>46212.77676006945</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2892,14 +2909,16 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="12" t="s">
-        <v>95</v>
+      <c r="T22" s="6">
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2911,16 +2930,16 @@
         <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2941,7 +2960,7 @@
         <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>93</v>
@@ -2964,7 +2983,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2976,16 +2995,16 @@
         <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -3003,29 +3022,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3037,16 +3056,16 @@
         <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3064,29 +3083,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3098,16 +3117,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3128,7 +3147,7 @@
         <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>93</v>
@@ -3151,7 +3170,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3163,16 +3182,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3190,29 +3209,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3224,16 +3243,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3251,29 +3270,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3285,16 +3304,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3315,7 +3334,7 @@
         <v>93</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>93</v>
@@ -3338,7 +3357,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3350,16 +3369,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3377,29 +3396,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3411,16 +3430,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>99</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3438,29 +3457,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3472,16 +3491,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3499,29 +3518,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3533,16 +3552,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3563,7 +3582,7 @@
         <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>93</v>
@@ -3586,7 +3605,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3598,16 +3617,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3625,29 +3644,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3659,16 +3678,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3686,29 +3705,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3720,16 +3739,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3750,7 +3769,7 @@
         <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3773,7 +3792,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3791,10 +3810,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3812,13 +3831,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3828,7 +3847,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3840,16 +3859,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3867,13 +3886,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3883,7 +3902,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3895,16 +3914,16 @@
         <v>46210.16859381944</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3925,7 +3944,7 @@
         <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3937,7 +3956,7 @@
         <v>46217</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3948,7 +3967,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3966,10 +3985,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3987,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4003,7 +4022,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4015,16 +4034,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4042,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4058,7 +4077,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4070,16 +4089,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4095,10 +4114,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4111,7 +4130,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4123,16 +4142,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4153,7 +4172,7 @@
         <v>93</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4176,7 +4195,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4194,10 +4213,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4215,13 +4234,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4231,7 +4250,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4243,16 +4262,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4270,13 +4289,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4286,7 +4305,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4298,7 +4317,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4322,7 +4341,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4339,7 +4358,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4351,16 +4370,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4378,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4404,7 +4423,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4416,16 +4435,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4443,13 +4462,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4469,7 +4488,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4487,10 +4506,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4506,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4532,7 +4551,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4542,16 +4561,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4567,10 +4586,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4582,18 +4601,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4603,16 +4622,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4628,7 +4647,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>194</v>
@@ -4654,16 +4673,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4679,10 +4698,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>195</v>
@@ -4695,17 +4714,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46212.77632917824</v>
+      </c>
       <c r="D53" s="9">
-        <v>46200.68378381945</v>
+        <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4729,7 +4750,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4737,33 +4758,37 @@
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
       <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="12" t="s">
-        <v>95</v>
+      <c r="T53" s="10">
+        <v>1</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46212.77629162037</v>
+      </c>
       <c r="D54" s="5">
-        <v>46205.60662056713</v>
+        <v>46212.77630914352</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4781,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4801,13 +4826,13 @@
       <c r="T54" s="6">
         <v>1</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>95</v>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4816,19 +4841,19 @@
         <v>46200.68377538194</v>
       </c>
       <c r="D55" s="9">
-        <v>46200.6837771412</v>
+        <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4844,13 +4869,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4864,32 +4889,34 @@
       <c r="T55" s="10">
         <v>1</v>
       </c>
-      <c r="U55" s="7" t="s">
-        <v>27</v>
+      <c r="U55" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46212.77630217593</v>
+      </c>
       <c r="D56" s="5">
-        <v>46205.606852488425</v>
+        <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4907,13 +4934,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4925,15 +4952,15 @@
         <v>33</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4942,19 +4969,19 @@
         <v>46200.68386630787</v>
       </c>
       <c r="D57" s="9">
-        <v>46200.683887164356</v>
+        <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4972,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4992,32 +5019,34 @@
       <c r="T57" s="10">
         <v>1</v>
       </c>
-      <c r="U57" s="7" t="s">
-        <v>27</v>
+      <c r="U57" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46212.77631068287</v>
+      </c>
       <c r="D58" s="5">
-        <v>46205.607397581014</v>
+        <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5035,13 +5064,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5053,15 +5082,15 @@
         <v>33</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5070,19 +5099,19 @@
         <v>46200.68395946759</v>
       </c>
       <c r="D59" s="9">
-        <v>46200.68397615741</v>
+        <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5100,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5120,13 +5149,13 @@
       <c r="T59" s="10">
         <v>1</v>
       </c>
-      <c r="U59" s="7" t="s">
-        <v>27</v>
+      <c r="U59" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5138,7 +5167,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5162,7 +5191,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5179,7 +5208,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5191,16 +5220,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5218,13 +5247,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5244,7 +5273,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5256,16 +5285,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5283,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5299,7 +5328,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5311,16 +5340,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5338,13 +5367,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5354,7 +5383,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5366,16 +5395,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5393,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5419,7 +5448,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5431,16 +5460,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5458,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5474,7 +5503,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5486,16 +5515,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5513,13 +5542,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5529,7 +5558,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5541,16 +5570,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5566,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5587,12 +5616,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>95</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5604,16 +5633,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5629,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5645,7 +5674,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5657,16 +5686,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5682,13 +5711,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>244</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5698,17 +5727,19 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46212.77656946759</v>
+      </c>
       <c r="D70" s="5">
-        <v>46212.664260949074</v>
+        <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5732,7 +5763,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5740,14 +5771,16 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="12" t="s">
-        <v>95</v>
+      <c r="T70" s="6">
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5759,16 +5792,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5784,13 +5817,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5810,7 +5843,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5822,16 +5855,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5847,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5873,7 +5906,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5885,16 +5918,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5910,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5936,26 +5969,28 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46212.77655145833</v>
+      </c>
       <c r="D74" s="5">
-        <v>46211.19095658565</v>
+        <v>46212.776568009256</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5971,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5986,18 +6021,18 @@
         <v>46218</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="12" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="U74" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6007,7 +6042,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6031,7 +6066,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6044,7 +6079,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6053,10 +6088,10 @@
         <v>46210.669946180555</v>
       </c>
       <c r="D76" s="5">
-        <v>46210.669961203705</v>
+        <v>46212.776568437504</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6083,13 +6118,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6098,18 +6133,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
-      <c r="U76" s="7" t="s">
-        <v>27</v>
+      <c r="U76" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6118,10 +6153,10 @@
         <v>46210.66987290509</v>
       </c>
       <c r="D77" s="9">
-        <v>46210.66987453704</v>
+        <v>46212.77656100695</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6148,10 +6183,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6164,7 +6199,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6173,10 +6208,10 @@
         <v>46210.66993070602</v>
       </c>
       <c r="D78" s="5">
-        <v>46210.66993231481</v>
+        <v>46212.7765616088</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6203,10 +6238,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6219,7 +6254,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6231,7 +6266,7 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6256,13 +6291,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6271,7 +6306,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6282,7 +6317,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6294,7 +6329,7 @@
         <v>46212.66404658565</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6319,13 +6354,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6335,7 +6370,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6347,7 +6382,7 @@
         <v>46212.66404525463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6372,13 +6407,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6388,7 +6423,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6400,7 +6435,7 @@
         <v>46210.670105150464</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6427,13 +6462,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6442,7 +6477,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6453,7 +6488,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6465,7 +6500,7 @@
         <v>46212.66405841435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6490,13 +6525,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6506,7 +6541,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6518,7 +6553,7 @@
         <v>46212.664059675924</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6543,13 +6578,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6559,7 +6594,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6571,7 +6606,7 @@
         <v>46210.67032010417</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6596,13 +6631,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6611,7 +6646,7 @@
         <v>46230</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6622,7 +6657,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6634,7 +6669,7 @@
         <v>46212.664253379626</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6659,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6675,7 +6710,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6687,7 +6722,7 @@
         <v>46212.6642540625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6712,13 +6747,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6728,7 +6763,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6738,7 +6773,7 @@
         <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6763,13 +6798,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>192</v>
+        <v>293</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6778,25 +6813,25 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46210.670293460644</v>
+        <v>46212.77709833333</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>194</v>
@@ -6824,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6840,17 +6875,17 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46210.67030641204</v>
+        <v>46212.777147280096</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6875,13 +6910,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6891,7 +6926,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6901,7 +6936,7 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6926,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6941,25 +6976,25 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46146.94244866898</v>
+        <v>46212.77733467593</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>194</v>
@@ -6987,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7003,14 +7038,14 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46146.94244559028</v>
+        <v>46212.77735347222</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>194</v>
@@ -7038,13 +7073,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7054,7 +7089,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7064,7 +7099,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7088,7 +7123,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7101,7 +7136,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7111,16 +7146,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7136,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7151,25 +7186,25 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46146.942643194445</v>
+        <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>194</v>
@@ -7178,10 +7213,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7197,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7213,14 +7248,14 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46146.94264393518</v>
+        <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>194</v>
@@ -7229,10 +7264,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7248,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7264,7 +7299,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7274,7 +7309,7 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7299,13 +7334,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7314,25 +7349,25 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46146.94285763889</v>
+        <v>46212.777429884256</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>194</v>
@@ -7360,13 +7395,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7376,14 +7411,14 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46146.94285530093</v>
+        <v>46212.77744148148</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>194</v>
@@ -7411,13 +7446,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7427,7 +7462,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7437,16 +7472,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7462,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7477,25 +7512,25 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46146.94342792824</v>
+        <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>194</v>
@@ -7504,10 +7539,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7523,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7539,14 +7574,14 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46146.94346471065</v>
+        <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>194</v>
@@ -7555,10 +7590,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7574,13 +7609,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7590,7 +7625,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7600,16 +7635,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7625,13 +7660,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7640,25 +7675,25 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46146.94332239583</v>
+        <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>194</v>
@@ -7667,10 +7702,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7686,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7702,14 +7737,14 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46146.943319872684</v>
+        <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>194</v>
@@ -7718,10 +7753,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7737,13 +7772,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7753,7 +7788,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7763,7 +7798,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7787,7 +7822,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7800,7 +7835,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7810,16 +7845,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7837,13 +7872,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="O108" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="O108" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="P108" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7852,18 +7887,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7873,7 +7908,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7900,13 +7935,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="O109" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="O109" s="10" t="s">
-        <v>324</v>
-      </c>
       <c r="P109" s="10" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7915,13 +7950,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="341">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -119,30 +119,6 @@
   </si>
   <si>
     <t>Apertura pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para el pedido 1466 se deben suministrar 5 unidades ZVN 1-10-126/2 para Zitron Perú (Cía. Minera Poderosa):
-    Fabricación / Planos:
-·         O/4302; Ventilador ZVN 1-10-126/2 con motor WEG.
-·         Alcance: Tobera + Rejilla + Carcasa
-    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-    Tratamiento superficial estándar Zitron:
-        Preparación de superficie: Arenado SSPC-SP10
-        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
-        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001 Blanco.
-    Datos eléctricos motor:
-·         Motor WEG 90 kW; 2 Polos; IE3
-·         Frame 280
-·         460V, 60HZ
-·         OC19034: 23-04-2026
-·         Se requiere duplicado de placas.
-    Fecha de entrega: 30-04-2026
-</t>
   </si>
   <si>
     <t>1214511244960122</t>
@@ -1866,7 +1842,7 @@
         <v>46175.87207239583</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87209802083</v>
+        <v>46213.69123809028</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1888,7 +1864,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1920,7 +1896,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46146.78699966436</v>
@@ -1932,7 +1908,7 @@
         <v>46175.872098576394</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1951,7 +1927,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -1983,7 +1959,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>46146.7870025</v>
@@ -1995,7 +1971,7 @@
         <v>46175.87209884259</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2014,7 +1990,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2026,7 +2002,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="5">
         <v>46147</v>
@@ -2046,7 +2022,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="9">
         <v>46146.787006631945</v>
@@ -2058,7 +2034,7 @@
         <v>46175.87209942129</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -2077,7 +2053,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>26</v>
@@ -2109,7 +2085,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5">
         <v>46146.78687210648</v>
@@ -2121,7 +2097,7 @@
         <v>46197.6494803588</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2145,7 +2121,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2162,7 +2138,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="9">
         <v>46146.787010162036</v>
@@ -2174,16 +2150,16 @@
         <v>46197.64823298611</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I11" s="9">
         <v>46147</v>
@@ -2195,19 +2171,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="Q11" s="9">
         <v>46147</v>
@@ -2227,7 +2203,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46146.7870155787</v>
@@ -2239,16 +2215,16 @@
         <v>46197.64898236111</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I12" s="5">
         <v>46147</v>
@@ -2260,19 +2236,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46147</v>
@@ -2292,7 +2268,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46146.787021400465</v>
@@ -2304,16 +2280,16 @@
         <v>46197.6494675463</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I13" s="9">
         <v>46147</v>
@@ -2325,19 +2301,19 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="Q13" s="9">
         <v>46147</v>
@@ -2357,7 +2333,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46146.7868765162</v>
@@ -2369,7 +2345,7 @@
         <v>46204.908018587965</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2393,7 +2369,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2410,7 +2386,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="9">
         <v>46146.7870415625</v>
@@ -2422,16 +2398,16 @@
         <v>46203.70941623843</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I15" s="9">
         <v>46149</v>
@@ -2449,13 +2425,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q15" s="9">
         <v>46149</v>
@@ -2475,7 +2451,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>46146.78704743055</v>
@@ -2487,16 +2463,16 @@
         <v>46203.70945753472</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I16" s="5">
         <v>46149</v>
@@ -2514,13 +2490,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46149</v>
@@ -2540,7 +2516,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="9">
         <v>46146.78705320602</v>
@@ -2552,16 +2528,16 @@
         <v>46204.907181365736</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46149</v>
@@ -2579,13 +2555,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2605,7 +2581,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46146.78705905093</v>
@@ -2617,16 +2593,16 @@
         <v>46204.90714847222</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I18" s="5">
         <v>46177</v>
@@ -2644,13 +2620,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46146</v>
@@ -2670,7 +2646,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
@@ -2682,16 +2658,16 @@
         <v>46204.9075317824</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I19" s="9">
         <v>46177</v>
@@ -2709,13 +2685,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2735,7 +2711,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
@@ -2747,16 +2723,16 @@
         <v>46204.90778255787</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I20" s="5">
         <v>46177</v>
@@ -2774,13 +2750,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2800,7 +2776,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
@@ -2812,16 +2788,16 @@
         <v>46204.90800618056</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="I21" s="9">
         <v>46177</v>
@@ -2839,13 +2815,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2865,7 +2841,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2877,7 +2853,7 @@
         <v>46212.77676006945</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2901,7 +2877,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2918,7 +2894,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2930,16 +2906,16 @@
         <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2957,13 +2933,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2983,7 +2959,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2995,16 +2971,16 @@
         <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -3022,29 +2998,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3056,16 +3032,16 @@
         <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3083,29 +3059,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3117,16 +3093,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3144,13 +3120,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3170,7 +3146,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3182,16 +3158,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3209,29 +3185,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3243,16 +3219,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3270,29 +3246,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3304,16 +3280,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3331,13 +3307,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3357,7 +3333,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3369,16 +3345,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3396,29 +3372,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3430,16 +3406,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3457,29 +3433,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3491,16 +3467,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3518,29 +3494,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3552,16 +3528,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3579,13 +3555,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3605,7 +3581,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3617,16 +3593,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3644,29 +3620,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3678,16 +3654,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3705,29 +3681,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3739,16 +3715,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3766,10 +3742,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3792,7 +3768,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3804,16 +3780,16 @@
         <v>46205.60679543982</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3831,13 +3807,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3847,7 +3823,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3859,16 +3835,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3886,13 +3862,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3902,7 +3878,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3914,16 +3890,16 @@
         <v>46210.16859381944</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3941,10 +3917,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3956,7 +3932,7 @@
         <v>46217</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3967,7 +3943,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3979,16 +3955,16 @@
         <v>46205.54751966435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -4006,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4022,7 +3998,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4034,16 +4010,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4061,13 +4037,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4077,7 +4053,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4089,16 +4065,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4114,10 +4090,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4130,7 +4106,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4142,16 +4118,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4169,10 +4145,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4195,7 +4171,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4207,16 +4183,16 @@
         <v>46205.607340787035</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4234,13 +4210,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4250,7 +4226,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4262,16 +4238,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4289,13 +4265,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4305,7 +4281,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4317,7 +4293,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4341,7 +4317,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4358,7 +4334,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4370,16 +4346,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4397,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4423,7 +4399,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4435,16 +4411,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4462,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4488,7 +4464,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4500,16 +4476,16 @@
         <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4525,13 +4501,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4551,7 +4527,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4561,16 +4537,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4586,10 +4562,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4601,18 +4577,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4622,16 +4598,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4647,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4663,7 +4639,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4673,16 +4649,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4698,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4714,7 +4690,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4726,7 +4702,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4750,7 +4726,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4767,7 +4743,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4779,16 +4755,16 @@
         <v>46212.77630914352</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4806,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4832,7 +4808,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4844,16 +4820,16 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4869,13 +4845,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4890,12 +4866,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4907,16 +4883,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4934,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4960,7 +4936,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4972,16 +4948,16 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4999,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -5020,12 +4996,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5037,16 +5013,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5064,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5090,7 +5066,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5102,16 +5078,16 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5129,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5150,12 +5126,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5167,7 +5143,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5191,7 +5167,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5208,7 +5184,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5220,16 +5196,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5247,13 +5223,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5273,7 +5249,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5285,16 +5261,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5312,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5328,7 +5304,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5340,16 +5316,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5367,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5383,7 +5359,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5395,16 +5371,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5422,13 +5398,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5448,7 +5424,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5460,16 +5436,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5487,13 +5463,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5503,7 +5479,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5515,16 +5491,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5542,13 +5518,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5558,7 +5534,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5570,16 +5546,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5595,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5616,12 +5592,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5633,16 +5609,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5658,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5674,7 +5650,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5686,16 +5662,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5711,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5727,7 +5703,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5739,7 +5715,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5763,7 +5739,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5780,7 +5756,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5792,16 +5768,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5817,13 +5793,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5843,7 +5819,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5855,16 +5831,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5880,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5906,7 +5882,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5918,16 +5894,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5943,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5969,7 +5945,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5981,16 +5957,16 @@
         <v>46212.776568009256</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -6006,13 +5982,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -6021,7 +5997,7 @@
         <v>46218</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6032,7 +6008,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6042,7 +6018,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6066,7 +6042,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6079,7 +6055,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6091,16 +6067,16 @@
         <v>46212.776568437504</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I76" s="5">
         <v>46219</v>
@@ -6118,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6133,18 +6109,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6156,16 +6132,16 @@
         <v>46212.77656100695</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I77" s="9">
         <v>46219</v>
@@ -6183,10 +6159,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6199,7 +6175,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6211,16 +6187,16 @@
         <v>46212.7765616088</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78" s="5">
         <v>46219</v>
@@ -6238,10 +6214,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6254,7 +6230,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6266,16 +6242,16 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6291,13 +6267,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6306,7 +6282,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6317,7 +6293,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6329,16 +6305,16 @@
         <v>46212.66404658565</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6354,13 +6330,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6370,7 +6346,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6382,16 +6358,16 @@
         <v>46212.66404525463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6407,13 +6383,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6423,7 +6399,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6435,16 +6411,16 @@
         <v>46210.670105150464</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I82" s="5">
         <v>46227</v>
@@ -6462,13 +6438,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6477,7 +6453,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6488,7 +6464,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6500,16 +6476,16 @@
         <v>46212.66405841435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6525,13 +6501,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6541,7 +6517,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6553,16 +6529,16 @@
         <v>46212.664059675924</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6578,13 +6554,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6594,7 +6570,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6606,16 +6582,16 @@
         <v>46210.67032010417</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6631,13 +6607,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6646,7 +6622,7 @@
         <v>46230</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6657,7 +6633,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6669,16 +6645,16 @@
         <v>46212.664253379626</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6694,13 +6670,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6710,7 +6686,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6722,16 +6698,16 @@
         <v>46212.6642540625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6747,13 +6723,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="P87" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="P87" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6763,7 +6739,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6773,16 +6749,16 @@
         <v>46146.94197813657</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6798,13 +6774,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6813,18 +6789,18 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6834,16 +6810,16 @@
         <v>46212.77709833333</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6859,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6875,7 +6851,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6885,16 +6861,16 @@
         <v>46212.777147280096</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6910,13 +6886,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6926,7 +6902,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6936,16 +6912,16 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6961,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>299</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>300</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6976,18 +6952,18 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6997,16 +6973,16 @@
         <v>46212.77733467593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7022,13 +6998,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7038,7 +7014,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -7048,16 +7024,16 @@
         <v>46212.77735347222</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -7073,13 +7049,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7089,7 +7065,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7099,7 +7075,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7123,7 +7099,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7136,7 +7112,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7146,16 +7122,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="H95" s="10" t="s">
         <v>309</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>310</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7171,13 +7147,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7186,18 +7162,18 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7207,16 +7183,16 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7232,13 +7208,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7248,7 +7224,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7258,16 +7234,16 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>309</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>310</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7283,13 +7259,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7299,7 +7275,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7309,16 +7285,16 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7334,13 +7310,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7349,18 +7325,18 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7370,16 +7346,16 @@
         <v>46212.777429884256</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7395,13 +7371,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7411,7 +7387,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7421,16 +7397,16 @@
         <v>46212.77744148148</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7446,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7462,7 +7438,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7472,16 +7448,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7497,13 +7473,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7512,18 +7488,18 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7533,16 +7509,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7558,13 +7534,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7574,7 +7550,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7584,16 +7560,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7609,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7625,7 +7601,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7635,16 +7611,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7660,13 +7636,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7675,18 +7651,18 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7696,16 +7672,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7721,13 +7697,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7737,7 +7713,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7747,16 +7723,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7772,13 +7748,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7788,7 +7764,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7798,7 +7774,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7822,7 +7798,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7835,7 +7811,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7845,16 +7821,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>339</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7872,13 +7848,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7887,18 +7863,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7908,16 +7884,16 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I109" s="9">
         <v>46240</v>
@@ -7935,13 +7911,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7950,13 +7926,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -685,7 +685,7 @@
     <t>victor.munoz@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214511245146577</t>
@@ -4752,7 +4752,7 @@
         <v>46212.77629162037</v>
       </c>
       <c r="D54" s="5">
-        <v>46212.77630914352</v>
+        <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -6746,7 +6746,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46146.94197813657</v>
+        <v>46217.5950700463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>291</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -529,331 +529,331 @@
     <t>Generacion OC Fabricación Externa OT 4309,Fabricación estructura proveedor externo OT 4309</t>
   </si>
   <si>
+    <t>1214511142484075</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973505</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4309</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
+  </si>
+  <si>
+    <t>1214508463084879</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4309</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214511240973520</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511240973530</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>1214511199027682</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4309</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084764</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199027697</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214511199035045</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214511240985139</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901576</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901586</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901596</t>
+  </si>
+  <si>
+    <t>ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155796713</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511155796723</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511245146577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214511155961778</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214508463084772</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155961793</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084773</t>
+  </si>
+  <si>
+    <t>1214511241037947</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214511241037957</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214508463084766</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214508463084767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245155134</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245155149</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142568769</t>
+  </si>
+  <si>
+    <t>1214511245167372</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214511245167387</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142578821</t>
+  </si>
+  <si>
+    <t>OT  4309- ZVN 1-9-75/2,check planos</t>
+  </si>
+  <si>
+    <t>1214511241084950</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214511241084960</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245195202</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,Bodega:,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245195222</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214511241089613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511142484075</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4309,Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973505</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4309</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309,Recepcion fabricación externa ,Fabricación Externa  OT 4309</t>
-  </si>
-  <si>
-    <t>1214508463084879</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4309</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214511240973520</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511240973530</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>1214511199027682</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4309</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4309,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084764</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199027697</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214511199035045</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4309</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214511240985139</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Propuesta Fabricación externa OT 4309 ,ZVN 1-9-75/2,propuesta Corte Laser OT 4309,Propuesta Corte plasma  OT 4309,Propuesta Mecanizado OT 4309,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901576</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901586</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901596</t>
-  </si>
-  <si>
-    <t>ot 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155796713</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511155796723</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511245146577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214511155961778</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214508463084772</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155961793</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084773</t>
-  </si>
-  <si>
-    <t>1214511241037947</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214511241037957</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214508463084766</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214508463084767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT  4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245155134</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245155149</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142568769</t>
-  </si>
-  <si>
-    <t>1214511245167372</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214511245167387</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142578821</t>
-  </si>
-  <si>
-    <t>OT  4309- ZVN 1-9-75/2,check planos</t>
-  </si>
-  <si>
-    <t>1214511241084950</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214511241084960</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245195202</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,Bodega:,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245195222</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214511241089613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511155964046</t>
@@ -3887,7 +3887,7 @@
         <v>46205.591705694445</v>
       </c>
       <c r="D39" s="9">
-        <v>46210.16859381944</v>
+        <v>46218.17888028936</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3931,8 +3931,8 @@
       <c r="R39" s="9">
         <v>46217</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>152</v>
+      <c r="S39" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3988,7 +3988,7 @@
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4010,7 +4010,7 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4043,7 +4043,7 @@
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4053,7 +4053,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4065,16 +4065,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4093,7 +4093,7 @@
         <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4118,7 +4118,7 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4148,7 +4148,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4210,13 +4210,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4238,7 +4238,7 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4265,13 +4265,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4293,7 +4293,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4317,7 +4317,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4346,16 +4346,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4373,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4411,16 +4411,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4438,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4482,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4501,13 +4501,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4537,16 +4537,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4562,10 +4562,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4598,16 +4598,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4623,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>194</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4649,16 +4649,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4674,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4702,7 +4702,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4726,7 +4726,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4755,16 +4755,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4782,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4808,7 +4808,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4820,16 +4820,16 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4845,13 +4845,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4866,12 +4866,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4883,16 +4883,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4910,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4948,16 +4948,16 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4975,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4996,12 +4996,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5013,16 +5013,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5040,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5078,16 +5078,16 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5105,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5126,12 +5126,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5143,7 +5143,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5167,7 +5167,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5196,16 +5196,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5223,13 +5223,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5261,16 +5261,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5288,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5316,16 +5316,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5343,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5371,16 +5371,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5398,13 +5398,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5424,7 +5424,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5436,16 +5436,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5463,13 +5463,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5491,16 +5491,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5518,13 +5518,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5534,7 +5534,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5546,16 +5546,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5571,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5592,12 +5592,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5609,16 +5609,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5634,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5662,16 +5662,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5687,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5703,7 +5703,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5715,7 +5715,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5739,7 +5739,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5756,7 +5756,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5768,16 +5768,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5793,13 +5793,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>114</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5819,7 +5819,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5831,16 +5831,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5856,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5894,16 +5894,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5919,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>123</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5957,16 +5957,16 @@
         <v>46212.776568009256</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5982,13 +5982,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5997,7 +5997,7 @@
         <v>46218</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6064,7 +6064,7 @@
         <v>46210.669946180555</v>
       </c>
       <c r="D76" s="5">
-        <v>46212.776568437504</v>
+        <v>46218.171660567124</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>265</v>
@@ -6108,14 +6108,14 @@
       <c r="R76" s="5">
         <v>46225</v>
       </c>
-      <c r="S76" s="7" t="s">
-        <v>102</v>
+      <c r="S76" s="12" t="s">
+        <v>260</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6132,7 +6132,7 @@
         <v>46212.77656100695</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6187,7 +6187,7 @@
         <v>46212.7765616088</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6270,7 +6270,7 @@
         <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>262</v>
@@ -6305,7 +6305,7 @@
         <v>46212.66404658565</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6358,7 +6358,7 @@
         <v>46212.66404525463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6441,7 +6441,7 @@
         <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>262</v>
@@ -6476,7 +6476,7 @@
         <v>46212.66405841435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6529,7 +6529,7 @@
         <v>46212.664059675924</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6610,7 +6610,7 @@
         <v>262</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>262</v>
@@ -6645,7 +6645,7 @@
         <v>46212.664253379626</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6698,7 +6698,7 @@
         <v>46212.6642540625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46217.5950700463</v>
+        <v>46218.59600712963</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>291</v>
@@ -6810,7 +6810,7 @@
         <v>46212.77709833333</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6838,7 +6838,7 @@
         <v>291</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>294</v>
@@ -6861,7 +6861,7 @@
         <v>46212.777147280096</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6889,7 +6889,7 @@
         <v>291</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>294</v>
@@ -6973,7 +6973,7 @@
         <v>46212.77733467593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7001,7 +7001,7 @@
         <v>297</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>301</v>
@@ -7024,7 +7024,7 @@
         <v>46212.77735347222</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7052,7 +7052,7 @@
         <v>297</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>301</v>
@@ -7183,7 +7183,7 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7211,7 +7211,7 @@
         <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>312</v>
@@ -7234,7 +7234,7 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7262,7 +7262,7 @@
         <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>314</v>
@@ -7346,7 +7346,7 @@
         <v>46212.777429884256</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7374,7 +7374,7 @@
         <v>316</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>318</v>
@@ -7397,7 +7397,7 @@
         <v>46212.77744148148</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7425,7 +7425,7 @@
         <v>316</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>320</v>
@@ -7454,10 +7454,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7509,16 +7509,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7537,7 +7537,7 @@
         <v>322</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>324</v>
@@ -7560,16 +7560,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7588,7 +7588,7 @@
         <v>322</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>326</v>
@@ -7617,10 +7617,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7672,16 +7672,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>226</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7700,7 +7700,7 @@
         <v>328</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>328</v>
@@ -7723,16 +7723,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7751,7 +7751,7 @@
         <v>328</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>328</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="338">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -295,9 +295,6 @@
     <t>propuesta nucleo rodete OT 4309</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
   </si>
   <si>
@@ -305,12 +302,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4309</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2534,11 +2525,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46149</v>
       </c>
@@ -2561,7 +2550,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2581,7 +2570,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46146.78705905093</v>
@@ -2593,17 +2582,15 @@
         <v>46204.90714847222</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46177</v>
       </c>
@@ -2623,10 +2610,10 @@
         <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46146</v>
@@ -2646,7 +2633,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
@@ -2658,17 +2645,15 @@
         <v>46204.9075317824</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46177</v>
       </c>
@@ -2688,10 +2673,10 @@
         <v>64</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2711,7 +2696,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
@@ -2723,17 +2708,15 @@
         <v>46204.90778255787</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46177</v>
       </c>
@@ -2753,10 +2736,10 @@
         <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2776,7 +2759,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
@@ -2788,17 +2771,15 @@
         <v>46204.90800618056</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46177</v>
       </c>
@@ -2818,10 +2799,10 @@
         <v>64</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2841,7 +2822,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2853,7 +2834,7 @@
         <v>46212.77676006945</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2877,7 +2858,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2894,7 +2875,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2906,16 +2887,16 @@
         <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2933,13 +2914,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2959,7 +2940,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2971,16 +2952,16 @@
         <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2998,29 +2979,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3032,16 +3013,16 @@
         <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3059,29 +3040,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3093,16 +3074,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3120,13 +3101,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3146,7 +3127,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3158,16 +3139,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3185,29 +3166,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3219,16 +3200,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3246,29 +3227,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3280,16 +3261,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3307,13 +3288,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3333,7 +3314,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3345,16 +3326,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3372,29 +3353,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3406,16 +3387,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3433,29 +3414,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3467,16 +3448,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3494,29 +3475,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3528,16 +3509,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3555,13 +3536,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3581,7 +3562,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3593,16 +3574,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3620,29 +3601,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3654,16 +3635,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3681,29 +3662,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3715,16 +3696,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3742,10 +3723,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3768,7 +3749,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3780,16 +3761,16 @@
         <v>46205.60679543982</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3807,13 +3788,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3823,7 +3804,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3835,16 +3816,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3862,13 +3843,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3878,7 +3859,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3890,16 +3871,16 @@
         <v>46218.17888028936</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3917,10 +3898,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3943,7 +3924,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3955,16 +3936,16 @@
         <v>46205.54751966435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3982,13 +3963,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3998,7 +3979,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4010,16 +3991,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4037,13 +4018,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4053,7 +4034,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4065,16 +4046,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4090,10 +4071,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4106,7 +4087,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4118,16 +4099,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4145,10 +4126,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4171,7 +4152,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4183,16 +4164,16 @@
         <v>46205.607340787035</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4210,13 +4191,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4226,7 +4207,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4238,16 +4219,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4265,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4281,7 +4262,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4293,7 +4274,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4317,7 +4298,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4334,7 +4315,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4346,16 +4327,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4373,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4399,7 +4380,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4411,16 +4392,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4438,13 +4419,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4464,7 +4445,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4476,16 +4457,16 @@
         <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4501,13 +4482,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4527,7 +4508,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4537,16 +4518,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4562,10 +4543,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4577,18 +4558,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4598,16 +4579,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4623,13 +4604,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4639,7 +4620,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4649,16 +4630,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4674,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4690,7 +4671,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4702,7 +4683,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4726,7 +4707,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4743,7 +4724,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4755,16 +4736,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4782,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4808,7 +4789,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4820,16 +4801,16 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4845,13 +4826,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4866,12 +4847,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4883,16 +4864,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4910,13 +4891,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4936,7 +4917,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4948,16 +4929,16 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4975,13 +4956,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4996,12 +4977,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5013,16 +4994,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5040,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5066,7 +5047,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5078,16 +5059,16 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5105,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5126,12 +5107,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5143,7 +5124,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5167,7 +5148,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5184,7 +5165,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5196,16 +5177,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5223,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5249,7 +5230,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5261,16 +5242,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5288,13 +5269,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5304,7 +5285,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5316,16 +5297,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5343,13 +5324,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5359,7 +5340,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5371,16 +5352,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5398,13 +5379,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5424,7 +5405,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5436,16 +5417,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5463,13 +5444,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O65" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="O65" s="10" t="s">
-        <v>238</v>
-      </c>
       <c r="P65" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5479,7 +5460,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5491,16 +5472,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5518,13 +5499,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="O66" s="6" t="s">
-        <v>238</v>
-      </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5534,7 +5515,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5546,16 +5527,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5571,13 +5552,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5592,12 +5573,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5609,16 +5590,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5634,13 +5615,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5650,7 +5631,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5662,16 +5643,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5687,13 +5668,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5703,7 +5684,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5715,7 +5696,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5739,7 +5720,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5756,7 +5737,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5768,16 +5749,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5793,13 +5774,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5819,7 +5800,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5831,16 +5812,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5856,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5882,7 +5863,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5894,16 +5875,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5919,13 +5900,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5945,7 +5926,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5957,16 +5938,16 @@
         <v>46212.776568009256</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5982,13 +5963,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5997,7 +5978,7 @@
         <v>46218</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6008,7 +5989,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6018,7 +5999,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6042,7 +6023,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6055,7 +6036,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6067,17 +6048,15 @@
         <v>46218.171660567124</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="5">
         <v>46219</v>
       </c>
@@ -6094,13 +6073,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6109,18 +6088,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6132,17 +6111,15 @@
         <v>46212.77656100695</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="10"/>
       <c r="I77" s="9">
         <v>46219</v>
       </c>
@@ -6159,10 +6136,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="O77" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="O77" s="10" t="s">
-        <v>268</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6175,7 +6152,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6187,17 +6164,15 @@
         <v>46212.7765616088</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46219</v>
       </c>
@@ -6214,10 +6189,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O78" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6230,7 +6205,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6242,17 +6217,15 @@
         <v>46197.5890270949</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="10"/>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
         <v>46226</v>
@@ -6267,13 +6240,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6282,7 +6255,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6293,7 +6266,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6305,17 +6278,15 @@
         <v>46212.66404658565</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
         <v>46226</v>
@@ -6330,13 +6301,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6346,7 +6317,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6358,17 +6329,15 @@
         <v>46212.66404525463</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="10"/>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
         <v>46226</v>
@@ -6383,13 +6352,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6399,7 +6368,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6411,17 +6380,15 @@
         <v>46210.670105150464</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46227</v>
       </c>
@@ -6438,13 +6405,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6453,7 +6420,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6464,7 +6431,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6476,17 +6443,15 @@
         <v>46212.66405841435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
         <v>46227</v>
@@ -6501,13 +6466,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6517,7 +6482,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6529,17 +6494,15 @@
         <v>46212.664059675924</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
         <v>46227</v>
@@ -6554,13 +6517,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6570,7 +6533,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6582,17 +6545,15 @@
         <v>46210.67032010417</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="10"/>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
         <v>46230</v>
@@ -6607,13 +6568,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6622,7 +6583,7 @@
         <v>46230</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6633,7 +6594,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6645,17 +6606,15 @@
         <v>46212.664253379626</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
         <v>46230</v>
@@ -6670,13 +6629,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6686,7 +6645,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6698,17 +6657,15 @@
         <v>46212.6642540625</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46230</v>
@@ -6723,13 +6680,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6739,7 +6696,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6749,17 +6706,15 @@
         <v>46218.59600712963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
         <v>46231</v>
@@ -6774,13 +6729,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6789,18 +6744,18 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6810,17 +6765,15 @@
         <v>46212.77709833333</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
         <v>46231</v>
@@ -6835,13 +6788,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>291</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6851,7 +6804,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6861,17 +6814,15 @@
         <v>46212.777147280096</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46231</v>
@@ -6886,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>294</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6902,7 +6853,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6912,17 +6863,15 @@
         <v>46146.94197326389</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="10"/>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
         <v>46233</v>
@@ -6937,13 +6886,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6952,18 +6901,18 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6973,17 +6922,15 @@
         <v>46212.77733467593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46232</v>
@@ -6998,13 +6945,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7014,7 +6961,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -7024,17 +6971,15 @@
         <v>46212.77735347222</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46232</v>
@@ -7049,13 +6994,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7065,7 +7010,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7075,7 +7020,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7099,7 +7044,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7112,7 +7057,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7122,16 +7067,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7147,13 +7092,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7162,18 +7107,18 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7183,16 +7128,16 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7208,13 +7153,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7224,7 +7169,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7234,16 +7179,16 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7259,13 +7204,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7275,7 +7220,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7285,17 +7230,15 @@
         <v>46146.94289535879</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46237</v>
@@ -7310,13 +7253,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7325,18 +7268,18 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7346,17 +7289,15 @@
         <v>46212.777429884256</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="10"/>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
         <v>46237</v>
@@ -7371,13 +7312,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7387,7 +7328,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7397,17 +7338,15 @@
         <v>46212.77744148148</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46237</v>
@@ -7422,13 +7361,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7438,7 +7377,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7448,16 +7387,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7473,13 +7412,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7488,18 +7427,18 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7509,16 +7448,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7534,13 +7473,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7550,7 +7489,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7560,16 +7499,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7585,13 +7524,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7601,7 +7540,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7611,16 +7550,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7636,13 +7575,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7651,18 +7590,18 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7672,16 +7611,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7697,13 +7636,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7713,7 +7652,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7723,16 +7662,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7748,13 +7687,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7764,7 +7703,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7774,7 +7713,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7798,7 +7737,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7811,7 +7750,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7821,16 +7760,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7848,13 +7787,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7863,18 +7802,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7884,7 +7823,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7911,13 +7850,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7926,13 +7865,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -844,25 +844,25 @@
     <t>Revestimiento,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
   </si>
   <si>
+    <t>1214511155964046</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Rodete,Revestimiento,Pruebas FAT,Montaje Alabe,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214511155964056</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511155964046</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Rodete,Revestimiento,Pruebas FAT,Montaje Alabe,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214511155964056</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
   </si>
   <si>
     <t>1214511241123459</t>
@@ -5935,7 +5935,7 @@
         <v>46212.77655145833</v>
       </c>
       <c r="D74" s="5">
-        <v>46212.776568009256</v>
+        <v>46219.20182912037</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>255</v>
@@ -5977,8 +5977,8 @@
       <c r="R74" s="5">
         <v>46218</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>257</v>
+      <c r="S74" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -5989,7 +5989,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -5999,7 +5999,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6023,7 +6023,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6036,7 +6036,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6048,7 +6048,7 @@
         <v>46218.171660567124</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6073,13 +6073,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6088,7 +6088,7 @@
         <v>46225</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>265</v>
@@ -6189,7 +6189,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>265</v>
@@ -6214,7 +6214,7 @@
         <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46197.5890270949</v>
+        <v>46219.20799550926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>268</v>
@@ -6240,13 +6240,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>186</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6254,8 +6254,8 @@
       <c r="R79" s="9">
         <v>46226</v>
       </c>
-      <c r="S79" s="7" t="s">
-        <v>99</v>
+      <c r="S79" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6405,13 +6405,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>186</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6568,13 +6568,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>186</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6729,13 +6729,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>289</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6886,7 +6886,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>295</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -6377,7 +6377,7 @@
         <v>46210.670091631946</v>
       </c>
       <c r="D82" s="5">
-        <v>46210.670105150464</v>
+        <v>46220.206847511574</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>275</v>
@@ -6419,8 +6419,8 @@
       <c r="R82" s="5">
         <v>46227</v>
       </c>
-      <c r="S82" s="7" t="s">
-        <v>99</v>
+      <c r="S82" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete OT 4309</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4309</t>
@@ -2516,7 +2519,7 @@
         <v>46191.784087754626</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.907181365736</v>
+        <v>46223.59254012731</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -2525,9 +2528,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I17" s="9">
         <v>46149</v>
       </c>
@@ -2550,7 +2555,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2570,7 +2575,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46146.78705905093</v>
@@ -2579,18 +2584,20 @@
         <v>46204.90713112269</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.90714847222</v>
+        <v>46223.59253631944</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I18" s="5">
         <v>46177</v>
       </c>
@@ -2610,10 +2617,10 @@
         <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46146</v>
@@ -2633,7 +2640,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
@@ -2642,18 +2649,20 @@
         <v>46204.90751574074</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.9075317824</v>
+        <v>46223.59253284722</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I19" s="9">
         <v>46177</v>
       </c>
@@ -2673,10 +2682,10 @@
         <v>64</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2696,7 +2705,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
@@ -2705,18 +2714,20 @@
         <v>46204.90776649305</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.90778255787</v>
+        <v>46223.592529375004</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I20" s="5">
         <v>46177</v>
       </c>
@@ -2736,10 +2747,10 @@
         <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2759,7 +2770,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
@@ -2768,18 +2779,20 @@
         <v>46204.90798908565</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.90800618056</v>
+        <v>46223.592524085645</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I21" s="9">
         <v>46177</v>
       </c>
@@ -2799,10 +2812,10 @@
         <v>64</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2822,7 +2835,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2834,7 +2847,7 @@
         <v>46212.77676006945</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2858,7 +2871,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2875,7 +2888,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2887,16 +2900,16 @@
         <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2914,13 +2927,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2940,7 +2953,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2952,16 +2965,16 @@
         <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2979,29 +2992,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3013,16 +3026,16 @@
         <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3040,29 +3053,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3074,16 +3087,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3101,13 +3114,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3127,7 +3140,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3139,16 +3152,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3166,29 +3179,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3200,16 +3213,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3227,29 +3240,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3261,16 +3274,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3288,13 +3301,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3314,7 +3327,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3326,16 +3339,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3353,29 +3366,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3387,16 +3400,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3414,29 +3427,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3448,16 +3461,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3475,29 +3488,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3509,16 +3522,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3536,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3562,7 +3575,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3574,16 +3587,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3601,29 +3614,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3635,16 +3648,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3662,29 +3675,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3696,16 +3709,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3723,10 +3736,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3749,7 +3762,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3761,16 +3774,16 @@
         <v>46205.60679543982</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3788,13 +3801,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3804,7 +3817,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3816,16 +3829,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3843,13 +3856,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3859,7 +3872,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3871,16 +3884,16 @@
         <v>46218.17888028936</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3898,10 +3911,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3924,7 +3937,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3936,16 +3949,16 @@
         <v>46205.54751966435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3963,13 +3976,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3979,7 +3992,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -3991,16 +4004,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4018,13 +4031,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4034,7 +4047,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4046,16 +4059,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4071,10 +4084,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4087,7 +4100,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4099,16 +4112,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4126,10 +4139,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4152,7 +4165,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4164,16 +4177,16 @@
         <v>46205.607340787035</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4191,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4207,7 +4220,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4219,16 +4232,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4246,13 +4259,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4262,7 +4275,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4274,7 +4287,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4298,7 +4311,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4315,7 +4328,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4327,16 +4340,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4354,13 +4367,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4380,7 +4393,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4392,16 +4405,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4419,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4445,7 +4458,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4457,16 +4470,16 @@
         <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4482,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4508,7 +4521,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4518,16 +4531,16 @@
         <v>46146.93970905093</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4543,10 +4556,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4558,18 +4571,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4579,16 +4592,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4604,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4620,7 +4633,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4630,16 +4643,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4655,13 +4668,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4671,7 +4684,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4683,7 +4696,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4707,7 +4720,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4724,7 +4737,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4736,16 +4749,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4763,13 +4776,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4789,7 +4802,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4801,16 +4814,16 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4826,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4847,12 +4860,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4864,16 +4877,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4891,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4917,7 +4930,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4929,16 +4942,16 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4956,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4977,12 +4990,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -4994,16 +5007,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5021,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5047,7 +5060,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5059,16 +5072,16 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5086,13 +5099,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5107,12 +5120,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5124,7 +5137,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5148,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5165,7 +5178,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5177,16 +5190,16 @@
         <v>46198.89361756944</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5204,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5230,7 +5243,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5242,16 +5255,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5269,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5285,7 +5298,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5297,16 +5310,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5324,13 +5337,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5340,7 +5353,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5352,16 +5365,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5379,13 +5392,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5405,7 +5418,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5417,16 +5430,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5444,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5460,7 +5473,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5472,16 +5485,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5499,13 +5512,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5515,7 +5528,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5527,16 +5540,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5552,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5573,12 +5586,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5590,16 +5603,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5615,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5631,7 +5644,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5643,16 +5656,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5668,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5684,7 +5697,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5696,7 +5709,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5720,7 +5733,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5737,7 +5750,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5749,16 +5762,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5774,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5800,7 +5813,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5812,16 +5825,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5837,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5863,7 +5876,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5875,16 +5888,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5900,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5926,7 +5939,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5938,16 +5951,16 @@
         <v>46219.20182912037</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5963,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -5989,7 +6002,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -5999,7 +6012,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6023,7 +6036,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6036,7 +6049,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6045,18 +6058,20 @@
         <v>46210.669946180555</v>
       </c>
       <c r="D76" s="5">
-        <v>46218.171660567124</v>
+        <v>46223.59340103009</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I76" s="5">
         <v>46219</v>
       </c>
@@ -6073,13 +6088,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6088,18 +6103,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6108,18 +6123,20 @@
         <v>46210.66987290509</v>
       </c>
       <c r="D77" s="9">
-        <v>46212.77656100695</v>
+        <v>46223.592820370366</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I77" s="9">
         <v>46219</v>
       </c>
@@ -6136,10 +6153,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6152,7 +6169,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6161,18 +6178,20 @@
         <v>46210.66993070602</v>
       </c>
       <c r="D78" s="5">
-        <v>46212.7765616088</v>
+        <v>46223.592816550925</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I78" s="5">
         <v>46219</v>
       </c>
@@ -6189,10 +6208,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6205,7 +6224,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6214,18 +6233,20 @@
         <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46219.20799550926</v>
+        <v>46223.59339736111</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
         <v>46226</v>
@@ -6240,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6255,7 +6276,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6266,7 +6287,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6275,18 +6296,20 @@
         <v>46197.58893424769</v>
       </c>
       <c r="D80" s="5">
-        <v>46212.66404658565</v>
+        <v>46223.592917766204</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
         <v>46226</v>
@@ -6301,13 +6324,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6317,7 +6340,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6326,18 +6349,20 @@
         <v>46197.58900142361</v>
       </c>
       <c r="D81" s="9">
-        <v>46212.66404525463</v>
+        <v>46223.59291269676</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
         <v>46226</v>
@@ -6352,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6368,7 +6393,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6377,18 +6402,20 @@
         <v>46210.670091631946</v>
       </c>
       <c r="D82" s="5">
-        <v>46220.206847511574</v>
+        <v>46223.59339306713</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I82" s="5">
         <v>46227</v>
       </c>
@@ -6405,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6420,7 +6447,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6431,7 +6458,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6440,18 +6467,20 @@
         <v>46210.66999793981</v>
       </c>
       <c r="D83" s="9">
-        <v>46212.66405841435</v>
+        <v>46223.59301689814</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
         <v>46227</v>
@@ -6466,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6482,7 +6511,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6491,18 +6520,20 @@
         <v>46210.67007324074</v>
       </c>
       <c r="D84" s="5">
-        <v>46212.664059675924</v>
+        <v>46223.59301378472</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
         <v>46227</v>
@@ -6517,13 +6548,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6533,7 +6564,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6542,18 +6573,20 @@
         <v>46210.670307418986</v>
       </c>
       <c r="D85" s="9">
-        <v>46210.67032010417</v>
+        <v>46223.59338895833</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
         <v>46230</v>
@@ -6568,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6582,8 +6615,8 @@
       <c r="R85" s="9">
         <v>46230</v>
       </c>
-      <c r="S85" s="7" t="s">
-        <v>99</v>
+      <c r="S85" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6594,7 +6627,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6603,18 +6636,20 @@
         <v>46210.67028576389</v>
       </c>
       <c r="D86" s="5">
-        <v>46212.664253379626</v>
+        <v>46223.59310229166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
         <v>46230</v>
@@ -6629,13 +6664,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6645,7 +6680,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6654,18 +6689,20 @@
         <v>46210.67029284722</v>
       </c>
       <c r="D87" s="9">
-        <v>46212.6642540625</v>
+        <v>46223.5930984375</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46230</v>
@@ -6680,13 +6717,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6696,25 +6733,27 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46218.59600712963</v>
+        <v>46223.59337920139</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
         <v>46231</v>
@@ -6729,13 +6768,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6744,36 +6783,38 @@
         <v>46231</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46212.77709833333</v>
+        <v>46223.59318827547</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
         <v>46231</v>
@@ -6788,13 +6829,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6804,25 +6845,27 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46212.777147280096</v>
+        <v>46223.59318765046</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46231</v>
@@ -6837,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6853,25 +6896,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46146.94197326389</v>
+        <v>46223.59337854167</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
         <v>46233</v>
@@ -6886,13 +6931,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6901,36 +6946,38 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46212.77733467593</v>
+        <v>46223.59328414351</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46232</v>
@@ -6945,13 +6992,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6961,25 +7008,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46212.77735347222</v>
+        <v>46223.59328350694</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46232</v>
@@ -6994,13 +7043,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7010,7 +7059,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7020,7 +7069,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7044,7 +7093,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7057,7 +7106,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7067,16 +7116,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7092,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7107,18 +7156,18 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7128,16 +7177,16 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7153,13 +7202,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7169,7 +7218,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7179,16 +7228,16 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7204,13 +7253,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7220,25 +7269,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46146.94289535879</v>
+        <v>46223.5935097801</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46237</v>
@@ -7253,13 +7304,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7268,36 +7319,38 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46212.777429884256</v>
+        <v>46223.593458159725</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
         <v>46237</v>
@@ -7312,13 +7365,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7328,25 +7381,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46212.77744148148</v>
+        <v>46223.59345743056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46237</v>
@@ -7361,13 +7416,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7377,7 +7432,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7387,16 +7442,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7412,13 +7467,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7427,18 +7482,18 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7448,16 +7503,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7473,13 +7528,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7489,7 +7544,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7499,16 +7554,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7524,13 +7579,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7540,7 +7595,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7550,16 +7605,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7575,13 +7630,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7590,18 +7645,18 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7611,16 +7666,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7636,13 +7691,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7652,7 +7707,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7662,16 +7717,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7687,13 +7742,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7703,7 +7758,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7713,7 +7768,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7737,7 +7792,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7750,7 +7805,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7760,16 +7815,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7787,13 +7842,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7802,18 +7857,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7823,7 +7878,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7850,13 +7905,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7865,13 +7920,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -6740,7 +6740,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46223.59337920139</v>
+        <v>46224.19668494213</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6782,8 +6782,8 @@
       <c r="R88" s="5">
         <v>46231</v>
       </c>
-      <c r="S88" s="7" t="s">
-        <v>100</v>
+      <c r="S88" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -745,7 +745,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5187,7 +5187,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46198.89361756944</v>
+        <v>46224.87838483797</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>221</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -637,6 +637,9 @@
     <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214511155901586</t>
   </si>
   <si>
@@ -745,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -863,9 +866,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214511241123459</t>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46146.93970905093</v>
+        <v>46225.200143055554</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4570,8 +4570,8 @@
       <c r="R50" s="5">
         <v>46232</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>100</v>
+      <c r="S50" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4592,7 +4592,7 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4620,10 +4620,10 @@
         <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4643,7 +4643,7 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4671,10 +4671,10 @@
         <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4696,7 +4696,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4720,7 +4720,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4749,16 +4749,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4776,13 +4776,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4814,7 +4814,7 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4839,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4860,12 +4860,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4877,16 +4877,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4904,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4942,7 +4942,7 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4969,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4990,12 +4990,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5007,16 +5007,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5034,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5072,7 +5072,7 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5099,13 +5099,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5120,12 +5120,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5137,7 +5137,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5161,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5187,19 +5187,19 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46224.87838483797</v>
+        <v>46225.00960046296</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5217,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5255,16 +5255,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5282,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5310,16 +5310,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5337,13 +5337,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5365,16 +5365,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5392,13 +5392,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5430,16 +5430,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5457,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5485,16 +5485,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5512,13 +5512,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5528,7 +5528,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5540,7 +5540,7 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5565,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5586,12 +5586,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5603,7 +5603,7 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5628,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5656,7 +5656,7 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5681,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5709,7 +5709,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5733,7 +5733,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5762,16 +5762,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5787,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5813,7 +5813,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5825,16 +5825,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5850,13 +5850,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5888,16 +5888,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5913,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>121</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5951,16 +5951,16 @@
         <v>46219.20182912037</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5976,13 +5976,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6012,7 +6012,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6036,7 +6036,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6061,7 +6061,7 @@
         <v>46223.59340103009</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6088,13 +6088,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6103,13 +6103,13 @@
         <v>46225</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6126,7 +6126,7 @@
         <v>46223.592820370366</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6153,7 +6153,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>266</v>
@@ -6181,7 +6181,7 @@
         <v>46223.592816550925</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6208,7 +6208,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>266</v>
@@ -6261,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>187</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6276,7 +6276,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6299,7 +6299,7 @@
         <v>46223.592917766204</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6352,7 +6352,7 @@
         <v>46223.59291269676</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6432,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>187</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6447,7 +6447,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6470,7 +6470,7 @@
         <v>46223.59301689814</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6523,7 +6523,7 @@
         <v>46223.59301378472</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6601,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>187</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6616,7 +6616,7 @@
         <v>46230</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6639,7 +6639,7 @@
         <v>46223.59310229166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6692,7 +6692,7 @@
         <v>46223.5930984375</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6768,13 +6768,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>290</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6783,7 +6783,7 @@
         <v>46231</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6804,7 +6804,7 @@
         <v>46223.59318827547</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6832,7 +6832,7 @@
         <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>292</v>
@@ -6855,7 +6855,7 @@
         <v>46223.59318765046</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6883,7 +6883,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>292</v>
@@ -6931,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>296</v>
@@ -6967,7 +6967,7 @@
         <v>46223.59328414351</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6995,7 +6995,7 @@
         <v>295</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>299</v>
@@ -7018,7 +7018,7 @@
         <v>46223.59328350694</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7046,7 +7046,7 @@
         <v>295</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>299</v>
@@ -7177,7 +7177,7 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7205,7 +7205,7 @@
         <v>305</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>310</v>
@@ -7228,7 +7228,7 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7256,7 +7256,7 @@
         <v>305</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>312</v>
@@ -7340,7 +7340,7 @@
         <v>46223.593458159725</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7368,7 +7368,7 @@
         <v>314</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>316</v>
@@ -7391,7 +7391,7 @@
         <v>46223.59345743056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7419,7 +7419,7 @@
         <v>314</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>318</v>
@@ -7448,10 +7448,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7503,16 +7503,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7531,7 +7531,7 @@
         <v>320</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>322</v>
@@ -7554,16 +7554,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7582,7 +7582,7 @@
         <v>320</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>324</v>
@@ -7611,10 +7611,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7666,16 +7666,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7694,7 +7694,7 @@
         <v>326</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>326</v>
@@ -7717,16 +7717,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7745,7 +7745,7 @@
         <v>326</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>326</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5187,7 +5187,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46225.00960046296</v>
+        <v>46225.58945297454</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="340">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -295,6 +295,9 @@
     <t>propuesta nucleo rodete OT 4309</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -748,7 +751,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -2531,7 +2534,7 @@
         <v>74</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I17" s="9">
         <v>46149</v>
@@ -2555,7 +2558,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46149</v>
@@ -2575,7 +2578,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46146.78705905093</v>
@@ -2587,7 +2590,7 @@
         <v>46223.59253631944</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2596,7 +2599,7 @@
         <v>74</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5">
         <v>46177</v>
@@ -2617,10 +2620,10 @@
         <v>64</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46146</v>
@@ -2640,7 +2643,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46146.78706952547</v>
@@ -2652,7 +2655,7 @@
         <v>46223.59253284722</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2661,7 +2664,7 @@
         <v>74</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="9">
         <v>46177</v>
@@ -2682,10 +2685,10 @@
         <v>64</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46177</v>
@@ -2705,7 +2708,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46146.78707340278</v>
@@ -2717,7 +2720,7 @@
         <v>46223.592529375004</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2726,7 +2729,7 @@
         <v>74</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I20" s="5">
         <v>46177</v>
@@ -2747,10 +2750,10 @@
         <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46177</v>
@@ -2770,7 +2773,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46146.78707737269</v>
@@ -2782,7 +2785,7 @@
         <v>46223.592524085645</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2791,7 +2794,7 @@
         <v>74</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I21" s="9">
         <v>46177</v>
@@ -2812,10 +2815,10 @@
         <v>64</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46177</v>
@@ -2835,7 +2838,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46146.786881064814</v>
@@ -2847,7 +2850,7 @@
         <v>46212.77676006945</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2871,7 +2874,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2888,7 +2891,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46146.78708193287</v>
@@ -2900,16 +2903,16 @@
         <v>46212.66397574074</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46153</v>
@@ -2927,13 +2930,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9">
         <v>46153</v>
@@ -2953,7 +2956,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46146.78708679398</v>
@@ -2965,16 +2968,16 @@
         <v>46212.663913888886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46153</v>
@@ -2992,29 +2995,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46146.78709203703</v>
@@ -3026,16 +3029,16 @@
         <v>46212.66394828704</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3053,29 +3056,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46146.78709759259</v>
@@ -3087,16 +3090,16 @@
         <v>46195.92635861111</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46153</v>
@@ -3114,13 +3117,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46153</v>
@@ -3140,7 +3143,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46146.78710313658</v>
@@ -3152,16 +3155,16 @@
         <v>46195.92632960648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46153</v>
@@ -3179,29 +3182,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46146.787108969904</v>
@@ -3213,16 +3216,16 @@
         <v>46195.9263380787</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3240,29 +3243,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46146.78711427083</v>
@@ -3274,16 +3277,16 @@
         <v>46203.71001635416</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46153</v>
@@ -3301,13 +3304,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="9">
         <v>46153</v>
@@ -3327,7 +3330,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46146.78711935185</v>
@@ -3339,16 +3342,16 @@
         <v>46203.70991413195</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46153</v>
@@ -3366,29 +3369,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46146.78712466435</v>
@@ -3400,16 +3403,16 @@
         <v>46203.70997798612</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46162</v>
@@ -3427,29 +3430,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46146.78712987268</v>
@@ -3461,16 +3464,16 @@
         <v>46203.709962685185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46161</v>
@@ -3488,29 +3491,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46146.78718802083</v>
@@ -3522,16 +3525,16 @@
         <v>46205.606630173614</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46181</v>
@@ -3549,13 +3552,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="9">
         <v>46150</v>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46146.78719326389</v>
@@ -3587,16 +3590,16 @@
         <v>46205.60655203703</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46181</v>
@@ -3614,29 +3617,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46146.78719805555</v>
@@ -3648,16 +3651,16 @@
         <v>46205.60660486111</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46183</v>
@@ -3675,29 +3678,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46146.78721570602</v>
@@ -3709,16 +3712,16 @@
         <v>46205.60686332176</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46181</v>
@@ -3736,10 +3739,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3762,7 +3765,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46146.787218854166</v>
@@ -3774,16 +3777,16 @@
         <v>46205.60679543982</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46181</v>
@@ -3801,13 +3804,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3817,7 +3820,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46146.78722290509</v>
@@ -3829,16 +3832,16 @@
         <v>46205.60683582176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46183</v>
@@ -3856,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46146.78722673611</v>
@@ -3884,16 +3887,16 @@
         <v>46218.17888028936</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46181</v>
@@ -3911,10 +3914,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46146.787229884256</v>
@@ -3949,16 +3952,16 @@
         <v>46205.54751966435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46181</v>
@@ -3976,13 +3979,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3992,7 +3995,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46146.787233807874</v>
@@ -4004,16 +4007,16 @@
         <v>46205.5916524537</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46188</v>
@@ -4031,13 +4034,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4047,7 +4050,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46146.92145594908</v>
@@ -4059,16 +4062,16 @@
         <v>46205.59169479167</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -4084,10 +4087,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4100,7 +4103,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46146.78723741898</v>
@@ -4112,16 +4115,16 @@
         <v>46205.60740758102</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46181</v>
@@ -4139,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4165,7 +4168,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46146.78724063658</v>
@@ -4177,16 +4180,16 @@
         <v>46205.607340787035</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46181</v>
@@ -4204,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46146.78724467593</v>
@@ -4232,16 +4235,16 @@
         <v>46205.607379733796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46183</v>
@@ -4259,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46146.78688576389</v>
@@ -4287,7 +4290,7 @@
         <v>46210.52859619213</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4311,7 +4314,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4328,7 +4331,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46146.78724949074</v>
@@ -4340,16 +4343,16 @@
         <v>46197.711020393515</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46156</v>
@@ -4367,13 +4370,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46156</v>
@@ -4393,7 +4396,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46146.7872546412</v>
@@ -4405,16 +4408,16 @@
         <v>46203.71488673611</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46169</v>
@@ -4432,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46169</v>
@@ -4458,7 +4461,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46146.787260625</v>
@@ -4470,16 +4473,16 @@
         <v>46203.71493509259</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4495,13 +4498,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4521,7 +4524,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46146.78727884259</v>
@@ -4531,16 +4534,16 @@
         <v>46225.200143055554</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4556,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4571,18 +4574,18 @@
         <v>46232</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4592,16 +4595,16 @@
         <v>46146.939574814816</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4617,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4633,7 +4636,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4643,16 +4646,16 @@
         <v>46146.939575474535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4668,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4684,7 +4687,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4696,7 +4699,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4720,7 +4723,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4737,7 +4740,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4749,16 +4752,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4776,13 +4779,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4802,7 +4805,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4814,16 +4817,16 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -4839,13 +4842,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4860,12 +4863,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4877,16 +4880,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4904,13 +4907,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4930,7 +4933,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4942,16 +4945,16 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="9">
         <v>46192</v>
@@ -4969,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4990,12 +4993,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5007,16 +5010,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5034,13 +5037,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5060,7 +5063,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5072,16 +5075,16 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="9">
         <v>46192</v>
@@ -5099,13 +5102,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5120,12 +5123,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5137,7 +5140,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5161,7 +5164,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5178,7 +5181,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5187,19 +5190,19 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46225.58945297454</v>
+        <v>46225.861886875005</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5217,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5243,7 +5246,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5255,16 +5258,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5282,13 +5285,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5298,7 +5301,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5310,16 +5313,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5337,13 +5340,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5353,7 +5356,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5365,16 +5368,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5392,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5418,7 +5421,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5430,16 +5433,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5457,13 +5460,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5473,7 +5476,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5485,16 +5488,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5512,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5528,7 +5531,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5540,16 +5543,16 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5565,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5586,12 +5589,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5603,16 +5606,16 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5628,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5656,16 +5659,16 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="9">
@@ -5681,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5709,7 +5712,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5733,7 +5736,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5750,7 +5753,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5762,16 +5765,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5787,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5813,7 +5816,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5825,16 +5828,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5850,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5876,7 +5879,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5888,16 +5891,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5913,13 +5916,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5939,7 +5942,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5951,16 +5954,16 @@
         <v>46219.20182912037</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5976,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -6002,7 +6005,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6012,7 +6015,7 @@
         <v>46210.67031722222</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6036,7 +6039,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6061,7 +6064,7 @@
         <v>46223.59340103009</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6070,7 +6073,7 @@
         <v>74</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I76" s="5">
         <v>46219</v>
@@ -6088,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6103,18 +6106,18 @@
         <v>46225</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6126,7 +6129,7 @@
         <v>46223.592820370366</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6135,7 +6138,7 @@
         <v>74</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I77" s="9">
         <v>46219</v>
@@ -6153,10 +6156,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6169,7 +6172,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6181,7 +6184,7 @@
         <v>46223.592816550925</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6190,7 +6193,7 @@
         <v>74</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78" s="5">
         <v>46219</v>
@@ -6208,10 +6211,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6224,7 +6227,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6236,7 +6239,7 @@
         <v>46223.59339736111</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6245,7 +6248,7 @@
         <v>74</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6261,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6276,7 +6279,7 @@
         <v>46226</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6287,7 +6290,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6299,7 +6302,7 @@
         <v>46223.592917766204</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6308,7 +6311,7 @@
         <v>74</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6324,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6340,7 +6343,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6352,7 +6355,7 @@
         <v>46223.59291269676</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6361,7 +6364,7 @@
         <v>74</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="9">
@@ -6377,13 +6380,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6393,7 +6396,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6405,7 +6408,7 @@
         <v>46223.59339306713</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6414,7 +6417,7 @@
         <v>74</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I82" s="5">
         <v>46227</v>
@@ -6432,13 +6435,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6447,7 +6450,7 @@
         <v>46227</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6458,7 +6461,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6470,7 +6473,7 @@
         <v>46223.59301689814</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6479,7 +6482,7 @@
         <v>74</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6495,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6511,7 +6514,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6523,7 +6526,7 @@
         <v>46223.59301378472</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6532,7 +6535,7 @@
         <v>74</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6548,13 +6551,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6564,7 +6567,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6576,7 +6579,7 @@
         <v>46223.59338895833</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6585,7 +6588,7 @@
         <v>74</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6601,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6616,7 +6619,7 @@
         <v>46230</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -6627,7 +6630,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6639,7 +6642,7 @@
         <v>46223.59310229166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6648,7 +6651,7 @@
         <v>74</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6664,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6692,7 +6695,7 @@
         <v>46223.5930984375</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6701,7 +6704,7 @@
         <v>74</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6717,13 +6720,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6733,7 +6736,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6743,7 +6746,7 @@
         <v>46224.19668494213</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6752,7 +6755,7 @@
         <v>74</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6768,13 +6771,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6783,18 +6786,18 @@
         <v>46231</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6804,7 +6807,7 @@
         <v>46223.59318827547</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6813,7 +6816,7 @@
         <v>74</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6829,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6845,7 +6848,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6855,7 +6858,7 @@
         <v>46223.59318765046</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6864,7 +6867,7 @@
         <v>74</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6880,13 +6883,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6896,7 +6899,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
@@ -6906,7 +6909,7 @@
         <v>46223.59337854167</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6915,7 +6918,7 @@
         <v>74</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6931,13 +6934,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6946,18 +6949,18 @@
         <v>46233</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -6967,7 +6970,7 @@
         <v>46223.59328414351</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6976,7 +6979,7 @@
         <v>74</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6992,13 +6995,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7008,7 +7011,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -7018,7 +7021,7 @@
         <v>46223.59328350694</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7027,7 +7030,7 @@
         <v>74</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -7043,13 +7046,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7059,7 +7062,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7069,7 +7072,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7093,7 +7096,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7106,7 +7109,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
@@ -7116,16 +7119,16 @@
         <v>46146.9429809375</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7141,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7156,18 +7159,18 @@
         <v>46234</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7177,16 +7180,16 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7202,13 +7205,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7228,16 +7231,16 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7253,13 +7256,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7269,7 +7272,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7279,7 +7282,7 @@
         <v>46223.5935097801</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7288,7 +7291,7 @@
         <v>74</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7304,13 +7307,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7319,18 +7322,18 @@
         <v>46237</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7340,7 +7343,7 @@
         <v>46223.593458159725</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7349,7 +7352,7 @@
         <v>74</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7365,13 +7368,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7381,7 +7384,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7391,7 +7394,7 @@
         <v>46223.59345743056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7400,7 +7403,7 @@
         <v>74</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7416,13 +7419,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7432,7 +7435,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
@@ -7442,16 +7445,16 @@
         <v>46146.9431597338</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7467,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7482,18 +7485,18 @@
         <v>46238</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7503,16 +7506,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7528,13 +7531,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7544,7 +7547,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7554,16 +7557,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7579,13 +7582,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7595,7 +7598,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
@@ -7605,16 +7608,16 @@
         <v>46146.94327527778</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7630,13 +7633,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7645,18 +7648,18 @@
         <v>46239</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7666,16 +7669,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7691,13 +7694,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7707,7 +7710,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7717,16 +7720,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7742,13 +7745,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7758,7 +7761,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7768,7 +7771,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7792,7 +7795,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7805,7 +7808,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7815,16 +7818,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7842,13 +7845,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7857,18 +7860,18 @@
         <v>46248</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7878,7 +7881,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7905,13 +7908,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>
@@ -7920,13 +7923,13 @@
         <v>46248</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -6061,7 +6061,7 @@
         <v>46210.669946180555</v>
       </c>
       <c r="D76" s="5">
-        <v>46223.59340103009</v>
+        <v>46226.20641083333</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>264</v>
@@ -6105,8 +6105,8 @@
       <c r="R76" s="5">
         <v>46225</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>189</v>
+      <c r="S76" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46223.59337854167</v>
+        <v>46226.19054920139</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>296</v>
@@ -6948,8 +6948,8 @@
       <c r="R91" s="9">
         <v>46233</v>
       </c>
-      <c r="S91" s="7" t="s">
-        <v>101</v>
+      <c r="S91" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46225.200143055554</v>
+        <v>46230.57274482639</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46146.939574814816</v>
+        <v>46230.57243269676</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46146.939575474535</v>
+        <v>46230.57244231481</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46210.67031722222</v>
+        <v>46230.572455416666</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>261</v>
@@ -6236,7 +6236,7 @@
         <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46223.59339736111</v>
+        <v>46227.201945636574</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>270</v>
@@ -6278,8 +6278,8 @@
       <c r="R79" s="9">
         <v>46226</v>
       </c>
-      <c r="S79" s="12" t="s">
-        <v>189</v>
+      <c r="S79" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6405,7 +6405,7 @@
         <v>46210.670091631946</v>
       </c>
       <c r="D82" s="5">
-        <v>46223.59339306713</v>
+        <v>46228.18810619213</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>277</v>
@@ -6449,8 +6449,8 @@
       <c r="R82" s="5">
         <v>46227</v>
       </c>
-      <c r="S82" s="12" t="s">
-        <v>189</v>
+      <c r="S82" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6741,9 +6741,11 @@
       <c r="B88" s="5">
         <v>46146.78773052084</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46230.57244761574</v>
+      </c>
       <c r="D88" s="5">
-        <v>46224.19668494213</v>
+        <v>46230.572459166666</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>290</v>
@@ -6789,10 +6791,10 @@
         <v>189</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U88" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6802,9 +6804,11 @@
       <c r="B89" s="9">
         <v>46146.78773511574</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46230.57242506945</v>
+      </c>
       <c r="D89" s="9">
-        <v>46223.59318827547</v>
+        <v>46230.57242677083</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>192</v>
@@ -6853,9 +6857,11 @@
       <c r="B90" s="5">
         <v>46146.78774035879</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46230.57243163194</v>
+      </c>
       <c r="D90" s="5">
-        <v>46223.59318765046</v>
+        <v>46230.57243314815</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -7116,7 +7122,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46146.9429809375</v>
+        <v>46227.20191582176</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>306</v>
@@ -7158,8 +7164,8 @@
       <c r="R95" s="9">
         <v>46234</v>
       </c>
-      <c r="S95" s="7" t="s">
-        <v>101</v>
+      <c r="S95" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
@@ -7279,7 +7285,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46223.5935097801</v>
+        <v>46230.17393229167</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>315</v>
@@ -7321,8 +7327,8 @@
       <c r="R98" s="5">
         <v>46237</v>
       </c>
-      <c r="S98" s="7" t="s">
-        <v>101</v>
+      <c r="S98" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -751,7 +751,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46230.57274482639</v>
+        <v>46231.582990428244</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46225.861886875005</v>
+        <v>46231.560368356484</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>223</v>
@@ -6576,7 +6576,7 @@
         <v>46210.670307418986</v>
       </c>
       <c r="D85" s="9">
-        <v>46223.59338895833</v>
+        <v>46231.20319630787</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>282</v>
@@ -6618,8 +6618,8 @@
       <c r="R85" s="9">
         <v>46230</v>
       </c>
-      <c r="S85" s="12" t="s">
-        <v>189</v>
+      <c r="S85" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T85" s="10">
         <v>1</v>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46146.9431597338</v>
+        <v>46231.18550335648</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>321</v>
@@ -7490,8 +7490,8 @@
       <c r="R101" s="9">
         <v>46238</v>
       </c>
-      <c r="S101" s="7" t="s">
-        <v>101</v>
+      <c r="S101" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46231.560368356484</v>
+        <v>46231.6530978588</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>223</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46231.582990428244</v>
+        <v>46232.16793053241</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46230.57243269676</v>
+        <v>46232.16793350695</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46230.57244231481</v>
+        <v>46232.1679349537</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -6745,7 +6745,7 @@
         <v>46230.57244761574</v>
       </c>
       <c r="D88" s="5">
-        <v>46230.572459166666</v>
+        <v>46232.19402519676</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>290</v>
@@ -6787,8 +6787,8 @@
       <c r="R88" s="5">
         <v>46231</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>189</v>
+      <c r="S88" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.59328414351</v>
+        <v>46232.16793638889</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>192</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46223.59328350694</v>
+        <v>46232.16793821759</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>192</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46146.94327527778</v>
+        <v>46232.17183269676</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7653,8 +7653,8 @@
       <c r="R104" s="5">
         <v>46239</v>
       </c>
-      <c r="S104" s="7" t="s">
-        <v>101</v>
+      <c r="S104" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -751,7 +751,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46231.6530978588</v>
+        <v>46232.835987314815</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>223</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -640,334 +640,334 @@
     <t>ZVN 1-9-75/2,ZVN 1-9-75/2</t>
   </si>
   <si>
+    <t>1214511155901586</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155901596</t>
+  </si>
+  <si>
+    <t>ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155796713</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511155796723</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214511245146577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214511155961778</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214508463084772</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155961793</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214508463084773</t>
+  </si>
+  <si>
+    <t>1214511241037947</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214511241037957</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+  </si>
+  <si>
+    <t>1214508463084766</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214508463084767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245155134</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245155149</t>
+  </si>
+  <si>
+    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142568769</t>
+  </si>
+  <si>
+    <t>1214511245167372</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214511245167387</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142578821</t>
+  </si>
+  <si>
+    <t>OT  4309- ZVN 1-9-75/2,check planos</t>
+  </si>
+  <si>
+    <t>1214511241084950</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214511241084960</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245195202</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,Bodega:,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245195222</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214511241089613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511155964046</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Rodete,Revestimiento,Pruebas FAT,Montaje Alabe,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214511155964056</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214511241123459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214511241123474</t>
+  </si>
+  <si>
+    <t>1214511199208690</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214511245285094</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214511241152873</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511199219177</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214511199219192</t>
+  </si>
+  <si>
+    <t>ZVN 1-9-75/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214527136078590</t>
+  </si>
+  <si>
+    <t>1214511142768640</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214511241215767</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511241215787</t>
+  </si>
+  <si>
+    <t>check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>Montaje motor,ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511241247725</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2,ot 4309 - ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511241247740</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245377310</t>
+  </si>
+  <si>
+    <t>1214511156146755</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511155901586</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155901596</t>
-  </si>
-  <si>
-    <t>ot 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155796713</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511155796723</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser ,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214511245146577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Bodega:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214511155961778</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214508463084772</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155961793</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214508463084773</t>
-  </si>
-  <si>
-    <t>1214511241037947</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214511241037957</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1214508463084766</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214508463084767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT  4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245155134</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT  4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245155149</t>
-  </si>
-  <si>
-    <t>OT 4309 - ZVN 1-9-75/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142568769</t>
-  </si>
-  <si>
-    <t>1214511245167372</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214511245167387</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142578821</t>
-  </si>
-  <si>
-    <t>OT  4309- ZVN 1-9-75/2,check planos</t>
-  </si>
-  <si>
-    <t>1214511241084950</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214511241084960</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245195202</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,Bodega:,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245195222</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214511241089613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,ZVN 1-9-75/2,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511155964046</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Rodete,Revestimiento,Pruebas FAT,Montaje Alabe,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214511155964056</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214511241123459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214511241123474</t>
-  </si>
-  <si>
-    <t>1214511199208690</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214511245285094</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214511241152873</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511199219177</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214511199219192</t>
-  </si>
-  <si>
-    <t>ZVN 1-9-75/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214527136078590</t>
-  </si>
-  <si>
-    <t>1214511142768640</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214511241215767</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511241215787</t>
-  </si>
-  <si>
-    <t>check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>Montaje motor,ot 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511241247725</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2,ot 4309 - ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511241247740</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245377310</t>
-  </si>
-  <si>
-    <t>1214511156146755</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1214511245386084</t>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46232.16793053241</v>
+        <v>46233.19362954861</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4573,8 +4573,8 @@
       <c r="R50" s="5">
         <v>46232</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>189</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46146.78728261574</v>
@@ -4595,7 +4595,7 @@
         <v>46232.16793350695</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4623,10 +4623,10 @@
         <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46146.787286527775</v>
@@ -4646,7 +4646,7 @@
         <v>46232.1679349537</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4674,10 +4674,10 @@
         <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46146.787341759264</v>
@@ -4699,7 +4699,7 @@
         <v>46212.77634790509</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4723,7 +4723,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46146.787345254634</v>
@@ -4752,16 +4752,16 @@
         <v>46216.60292806713</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46190</v>
@@ -4779,13 +4779,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46190</v>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9">
         <v>46146.787358877315</v>
@@ -4817,7 +4817,7 @@
         <v>46212.776321666664</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4842,13 +4842,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>206</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46192</v>
@@ -4863,12 +4863,12 @@
         <v>1</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46146.78735064815</v>
@@ -4880,16 +4880,16 @@
         <v>46212.77631554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46190</v>
@@ -4907,13 +4907,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46190</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46146.79730351851</v>
@@ -4945,7 +4945,7 @@
         <v>46212.776320439814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4972,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="9">
         <v>46192</v>
@@ -4993,12 +4993,12 @@
         <v>1</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46146.78735449074</v>
@@ -5010,16 +5010,16 @@
         <v>46212.77632949074</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46190</v>
@@ -5037,13 +5037,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>166</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46190</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
         <v>46146.79750996528</v>
@@ -5075,7 +5075,7 @@
         <v>46212.77632611111</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5102,13 +5102,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46192</v>
@@ -5123,12 +5123,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46146.787364398144</v>
@@ -5140,7 +5140,7 @@
         <v>46200.68337925926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5164,7 +5164,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46146.78736695602</v>
@@ -5193,16 +5193,16 @@
         <v>46232.835987314815</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I61" s="9">
         <v>46195</v>
@@ -5220,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="9">
         <v>46195</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46146.79438380787</v>
@@ -5258,16 +5258,16 @@
         <v>46200.6839671412</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46195</v>
@@ -5285,13 +5285,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="9">
         <v>46146.79440119213</v>
@@ -5313,16 +5313,16 @@
         <v>46200.683967916666</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46195</v>
@@ -5340,13 +5340,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46146.78737179398</v>
@@ -5368,16 +5368,16 @@
         <v>46205.203211134256</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46198</v>
@@ -5395,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="5">
         <v>46198</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B65" s="9">
         <v>46146.78737561342</v>
@@ -5433,16 +5433,16 @@
         <v>46203.71492597222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46198</v>
@@ -5460,13 +5460,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46146.78738193287</v>
@@ -5488,16 +5488,16 @@
         <v>46203.714927361114</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46198</v>
@@ -5515,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B67" s="9">
         <v>46146.78740461805</v>
@@ -5543,7 +5543,7 @@
         <v>46206.20677265046</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5568,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5589,12 +5589,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46146.787408564815</v>
@@ -5606,7 +5606,7 @@
         <v>46203.7149283912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5631,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B69" s="9">
         <v>46146.78741372685</v>
@@ -5659,7 +5659,7 @@
         <v>46203.714929317124</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5684,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46146.78743457176</v>
@@ -5712,7 +5712,7 @@
         <v>46212.776581342594</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5736,7 +5736,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B71" s="9">
         <v>46146.787437465275</v>
@@ -5765,16 +5765,16 @@
         <v>46212.66406818287</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -5790,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q71" s="9">
         <v>46175</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46146.78744341435</v>
@@ -5828,16 +5828,16 @@
         <v>46212.66405451389</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5853,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q72" s="5">
         <v>46156</v>
@@ -5879,7 +5879,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B73" s="9">
         <v>46146.7874489699</v>
@@ -5891,16 +5891,16 @@
         <v>46212.664260694444</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -5916,13 +5916,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="9">
         <v>46191</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46146.78746039352</v>
@@ -5954,16 +5954,16 @@
         <v>46219.20182912037</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5979,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46218</v>
@@ -6005,7 +6005,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B75" s="9">
         <v>46146.78750452546</v>
@@ -6015,7 +6015,7 @@
         <v>46230.572455416666</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>25</v>
@@ -6039,7 +6039,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46146.787508912035</v>
@@ -6064,7 +6064,7 @@
         <v>46226.20641083333</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6091,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46219</v>
@@ -6112,12 +6112,12 @@
         <v>1</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B77" s="9">
         <v>46146.78752016203</v>
@@ -6129,7 +6129,7 @@
         <v>46223.592820370366</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6156,10 +6156,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B78" s="5">
         <v>46146.78752439815</v>
@@ -6184,7 +6184,7 @@
         <v>46223.592816550925</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6211,10 +6211,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" s="9">
         <v>46146.78758131944</v>
@@ -6239,7 +6239,7 @@
         <v>46227.201945636574</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6264,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q79" s="9">
         <v>46226</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46146.78758657408</v>
@@ -6302,7 +6302,7 @@
         <v>46223.592917766204</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6327,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6343,7 +6343,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="9">
         <v>46146.787592939814</v>
@@ -6355,7 +6355,7 @@
         <v>46223.59291269676</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6380,13 +6380,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B82" s="5">
         <v>46146.78761755787</v>
@@ -6408,7 +6408,7 @@
         <v>46228.18810619213</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6435,13 +6435,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="5">
         <v>46227</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B83" s="9">
         <v>46146.78762708334</v>
@@ -6473,7 +6473,7 @@
         <v>46223.59301689814</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6498,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6514,7 +6514,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B84" s="5">
         <v>46146.78763331019</v>
@@ -6526,7 +6526,7 @@
         <v>46223.59301378472</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6551,13 +6551,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B85" s="9">
         <v>46146.78769865741</v>
@@ -6579,7 +6579,7 @@
         <v>46231.20319630787</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6604,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="9">
         <v>46230</v>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46146.787703553244</v>
@@ -6642,7 +6642,7 @@
         <v>46223.59310229166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6667,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
         <v>46146.78770892361</v>
@@ -6695,7 +6695,7 @@
         <v>46223.5930984375</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6720,13 +6720,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O87" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="P87" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="P87" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B88" s="5">
         <v>46146.78773052084</v>
@@ -6748,7 +6748,7 @@
         <v>46232.19402519676</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6773,13 +6773,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q88" s="5">
         <v>46231</v>
@@ -6799,7 +6799,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B89" s="9">
         <v>46146.78773511574</v>
@@ -6811,7 +6811,7 @@
         <v>46230.57242677083</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6836,13 +6836,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B90" s="5">
         <v>46146.78774035879</v>
@@ -6864,7 +6864,7 @@
         <v>46230.57243314815</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6889,13 +6889,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6905,17 +6905,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B91" s="9">
         <v>46146.787759479164</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46226.19054920139</v>
+        <v>46233.16790422454</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6940,13 +6940,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q91" s="9">
         <v>46233</v>
@@ -6955,7 +6955,7 @@
         <v>46233</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6976,7 +6976,7 @@
         <v>46232.16793638889</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7001,10 +7001,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>300</v>
@@ -7027,7 +7027,7 @@
         <v>46232.16793821759</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7052,10 +7052,10 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>300</v>
@@ -7165,7 +7165,7 @@
         <v>46234</v>
       </c>
       <c r="S95" s="12" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>46212.77737873842</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7214,7 +7214,7 @@
         <v>306</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>311</v>
@@ -7237,7 +7237,7 @@
         <v>46212.777400127314</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7265,7 +7265,7 @@
         <v>306</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>313</v>
@@ -7316,7 +7316,7 @@
         <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>303</v>
@@ -7328,7 +7328,7 @@
         <v>46237</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7349,7 +7349,7 @@
         <v>46223.593458159725</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7377,7 +7377,7 @@
         <v>315</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>317</v>
@@ -7400,7 +7400,7 @@
         <v>46223.59345743056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7428,7 +7428,7 @@
         <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>319</v>
@@ -7457,10 +7457,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7479,7 +7479,7 @@
         <v>303</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>303</v>
@@ -7491,7 +7491,7 @@
         <v>46238</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7512,16 +7512,16 @@
         <v>46212.77746881945</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7540,7 +7540,7 @@
         <v>321</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>323</v>
@@ -7563,16 +7563,16 @@
         <v>46212.77748577546</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7591,7 +7591,7 @@
         <v>321</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>325</v>
@@ -7620,10 +7620,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7642,7 +7642,7 @@
         <v>303</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>328</v>
@@ -7654,7 +7654,7 @@
         <v>46239</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7675,16 +7675,16 @@
         <v>46212.77751017361</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7703,7 +7703,7 @@
         <v>327</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>327</v>
@@ -7726,16 +7726,16 @@
         <v>46212.777535706016</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7754,7 +7754,7 @@
         <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>327</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46232.835987314815</v>
+        <v>46233.64826086805</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -967,40 +967,40 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1214511245386084</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511245386099</t>
+  </si>
+  <si>
+    <t>1214511156162478</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Despacho,Coordinacion Entrega con Cliente,Embalaje</t>
+  </si>
+  <si>
+    <t>1214511245412261</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2,RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511245386084</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511245386099</t>
-  </si>
-  <si>
-    <t>1214511156162478</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Despacho,Coordinacion Entrega con Cliente,Embalaje</t>
-  </si>
-  <si>
-    <t>1214511245412261</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2,RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
     <t>1214511245412281</t>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46233.16790422454</v>
+        <v>46234.16923135417</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>295</v>
@@ -6954,8 +6954,8 @@
       <c r="R91" s="9">
         <v>46233</v>
       </c>
-      <c r="S91" s="12" t="s">
-        <v>298</v>
+      <c r="S91" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B92" s="5">
         <v>46146.78776425926</v>
@@ -7007,7 +7007,7 @@
         <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7017,7 +7017,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B93" s="9">
         <v>46146.787768587965</v>
@@ -7058,7 +7058,7 @@
         <v>190</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7068,7 +7068,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B94" s="5">
         <v>46146.78778571759</v>
@@ -7078,7 +7078,7 @@
         <v>46146.9405634838</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7102,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7115,26 +7115,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B95" s="9">
         <v>46146.78778912037</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46227.20191582176</v>
+        <v>46234.16929877315</v>
       </c>
       <c r="E95" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="H95" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7150,13 +7150,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q95" s="9">
         <v>46234</v>
@@ -7165,7 +7165,7 @@
         <v>46234</v>
       </c>
       <c r="S95" s="12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46212.77737873842</v>
+        <v>46234.16930011574</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7192,10 +7192,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7211,7 +7211,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>191</v>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46212.777400127314</v>
+        <v>46234.169297361106</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7243,10 +7243,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7262,7 +7262,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>191</v>
@@ -7313,13 +7313,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46237</v>
@@ -7328,7 +7328,7 @@
         <v>46237</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7476,13 +7476,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>296</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="9">
         <v>46238</v>
@@ -7491,7 +7491,7 @@
         <v>46238</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7639,7 +7639,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>296</v>
@@ -7654,7 +7654,7 @@
         <v>46239</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1000,25 +1000,25 @@
     <t>ot 4309- ZVN 1-9-75/2,RE-PINTADO,ot 4309- ZVN 1-9-75/2</t>
   </si>
   <si>
+    <t>1214511245412281</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511241300240</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214511245415624</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511245412281</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511241300240</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214511245415624</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
   </si>
   <si>
     <t>1214511245415639</t>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46234.16929877315</v>
+        <v>46235.205738668985</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7164,8 +7164,8 @@
       <c r="R95" s="9">
         <v>46234</v>
       </c>
-      <c r="S95" s="12" t="s">
-        <v>309</v>
+      <c r="S95" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B96" s="5">
         <v>46146.78779429398</v>
@@ -7217,7 +7217,7 @@
         <v>191</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7227,7 +7227,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B97" s="9">
         <v>46146.787798414356</v>
@@ -7268,7 +7268,7 @@
         <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7278,7 +7278,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
         <v>46146.787814745374</v>
@@ -7288,7 +7288,7 @@
         <v>46230.17393229167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7328,7 +7328,7 @@
         <v>46237</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>191</v>
@@ -7425,7 +7425,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>191</v>
@@ -7491,7 +7491,7 @@
         <v>46238</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7654,7 +7654,7 @@
         <v>46239</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2091,7 +2091,7 @@
         <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.6494803588</v>
+        <v>46237.42832782408</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2339,7 +2339,7 @@
         <v>46204.90800548611</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.908018587965</v>
+        <v>46237.42828950231</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2847,7 +2847,7 @@
         <v>46212.77674577547</v>
       </c>
       <c r="D22" s="5">
-        <v>46212.77676006945</v>
+        <v>46237.4282659375</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46233.19362954861</v>
+        <v>46237.41577957176</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4696,7 +4696,7 @@
         <v>46212.77632917824</v>
       </c>
       <c r="D53" s="9">
-        <v>46212.77634790509</v>
+        <v>46237.4182359838</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>196</v>
@@ -5365,7 +5365,7 @@
         <v>46198.8940372338</v>
       </c>
       <c r="D64" s="5">
-        <v>46205.203211134256</v>
+        <v>46237.41432614584</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5540,7 +5540,7 @@
         <v>46200.68334386574</v>
       </c>
       <c r="D67" s="9">
-        <v>46206.20677265046</v>
+        <v>46237.53703127315</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>241</v>
@@ -5588,8 +5588,8 @@
       <c r="T67" s="10">
         <v>1</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>207</v>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5709,7 +5709,7 @@
         <v>46212.77656946759</v>
       </c>
       <c r="D70" s="5">
-        <v>46212.776581342594</v>
+        <v>46237.44790144676</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>196</v>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46230.572455416666</v>
+        <v>46237.454968252314</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>260</v>
@@ -6061,7 +6061,7 @@
         <v>46210.669946180555</v>
       </c>
       <c r="D76" s="5">
-        <v>46226.20641083333</v>
+        <v>46237.537073287036</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>263</v>
@@ -6111,8 +6111,8 @@
       <c r="T76" s="6">
         <v>1</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>207</v>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6236,7 +6236,7 @@
         <v>46197.58901480324</v>
       </c>
       <c r="D79" s="9">
-        <v>46227.201945636574</v>
+        <v>46237.416011134264</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>269</v>
@@ -6405,7 +6405,7 @@
         <v>46210.670091631946</v>
       </c>
       <c r="D82" s="5">
-        <v>46228.18810619213</v>
+        <v>46237.41610037037</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>276</v>
@@ -6576,7 +6576,7 @@
         <v>46210.670307418986</v>
       </c>
       <c r="D85" s="9">
-        <v>46231.20319630787</v>
+        <v>46237.41616101852</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>281</v>
@@ -6745,7 +6745,7 @@
         <v>46230.57244761574</v>
       </c>
       <c r="D88" s="5">
-        <v>46232.19402519676</v>
+        <v>46237.416258136574</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46234.16923135417</v>
+        <v>46237.537099340276</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>295</v>
@@ -6960,8 +6960,8 @@
       <c r="T91" s="10">
         <v>0</v>
       </c>
-      <c r="U91" s="11" t="s">
-        <v>102</v>
+      <c r="U91" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46235.205738668985</v>
+        <v>46237.41653664352</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46230.17393229167</v>
+        <v>46237.53713827547</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>314</v>
@@ -7333,8 +7333,8 @@
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="11" t="s">
-        <v>102</v>
+      <c r="U98" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46223.593458159725</v>
+        <v>46237.16882690972</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>191</v>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46223.59345743056</v>
+        <v>46237.16882849537</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46231.18550335648</v>
+        <v>46237.416664097225</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>321</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46232.17183269676</v>
+        <v>46237.41690960648</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46233.64826086805</v>
+        <v>46237.57049788194</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -5190,7 +5190,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46237.57049788194</v>
+        <v>46237.8101593287</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -1018,25 +1018,25 @@
     <t>Embalaje</t>
   </si>
   <si>
+    <t>1214511245415639</t>
+  </si>
+  <si>
+    <t>ot 4309- ZVN 1-9-75/2,Embalaje</t>
+  </si>
+  <si>
+    <t>1214511245415654</t>
+  </si>
+  <si>
+    <t>Embalaje,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511156219005</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511245415639</t>
-  </si>
-  <si>
-    <t>ot 4309- ZVN 1-9-75/2,Embalaje</t>
-  </si>
-  <si>
-    <t>1214511245415654</t>
-  </si>
-  <si>
-    <t>Embalaje,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511156219005</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>1214511241390749</t>
@@ -4529,9 +4529,11 @@
       <c r="B50" s="5">
         <v>46146.78727884259</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46238.512052129634</v>
+      </c>
       <c r="D50" s="5">
-        <v>46237.41577957176</v>
+        <v>46238.5120678588</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4577,10 +4579,10 @@
         <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4590,9 +4592,11 @@
       <c r="B51" s="9">
         <v>46146.78728261574</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46238.512004027776</v>
+      </c>
       <c r="D51" s="9">
-        <v>46232.16793350695</v>
+        <v>46238.51200577546</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4641,9 +4645,11 @@
       <c r="B52" s="5">
         <v>46146.787286527775</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46238.51203953703</v>
+      </c>
       <c r="D52" s="5">
-        <v>46232.1679349537</v>
+        <v>46238.512041064816</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -6973,7 +6979,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46232.16793638889</v>
+        <v>46238.51200935185</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -7024,7 +7030,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46232.16793821759</v>
+        <v>46238.512046909724</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7285,7 +7291,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46237.53713827547</v>
+        <v>46238.19551771991</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>314</v>
@@ -7327,8 +7333,8 @@
       <c r="R98" s="5">
         <v>46237</v>
       </c>
-      <c r="S98" s="12" t="s">
-        <v>315</v>
+      <c r="S98" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7339,7 +7345,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B99" s="9">
         <v>46146.78781900463</v>
@@ -7380,7 +7386,7 @@
         <v>191</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7390,7 +7396,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
         <v>46146.787823148145</v>
@@ -7431,7 +7437,7 @@
         <v>191</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7441,17 +7447,17 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B101" s="9">
         <v>46146.787891527776</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46237.416664097225</v>
+        <v>46238.16801050926</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7491,7 +7497,7 @@
         <v>46238</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7509,7 +7515,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46212.77746881945</v>
+        <v>46238.1680128588</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7537,7 +7543,7 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>191</v>
@@ -7560,7 +7566,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46212.77748577546</v>
+        <v>46238.1680141088</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7588,7 +7594,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>191</v>
@@ -7654,7 +7660,7 @@
         <v>46239</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -1036,28 +1036,28 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1214511241390749</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Planos Preliminar,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511241390769</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,PACKING LIST,ot 4309- ZVN 1-9-75/2</t>
+  </si>
+  <si>
+    <t>1214511142894089</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214511241390749</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Planos Preliminar,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511241390769</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,PACKING LIST,ot 4309- ZVN 1-9-75/2</t>
-  </si>
-  <si>
-    <t>1214511142894089</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1214511241404562</t>
@@ -5196,7 +5196,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46237.8101593287</v>
+        <v>46239.57424165509</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46238.16801050926</v>
+        <v>46239.17831525463</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>320</v>
@@ -7496,8 +7496,8 @@
       <c r="R101" s="9">
         <v>46238</v>
       </c>
-      <c r="S101" s="12" t="s">
-        <v>321</v>
+      <c r="S101" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T101" s="10">
         <v>0</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B102" s="5">
         <v>46146.78789762731</v>
@@ -7549,7 +7549,7 @@
         <v>191</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7559,7 +7559,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B103" s="9">
         <v>46146.78790538195</v>
@@ -7600,7 +7600,7 @@
         <v>191</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7610,17 +7610,17 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B104" s="5">
         <v>46146.787928171296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46237.41690960648</v>
+        <v>46239.16792815972</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7651,7 +7651,7 @@
         <v>296</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q104" s="5">
         <v>46239</v>
@@ -7660,7 +7660,7 @@
         <v>46239</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46212.77751017361</v>
+        <v>46239.167930972224</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7706,13 +7706,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46212.777535706016</v>
+        <v>46239.167932233795</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7757,13 +7757,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7860,7 +7860,7 @@
         <v>332</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>332</v>
@@ -7923,7 +7923,7 @@
         <v>332</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>332</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214508463084766</t>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -1055,9 +1055,6 @@
   </si>
   <si>
     <t>Logistica:,Gestion,Costos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214511241404562</t>
@@ -5196,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46239.57424165509</v>
+        <v>46240.58270290509</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -7617,7 +7614,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46239.16792815972</v>
+        <v>46240.19482599537</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>326</v>
@@ -7659,8 +7656,8 @@
       <c r="R104" s="5">
         <v>46239</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>328</v>
+      <c r="S104" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7671,7 +7668,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B105" s="9">
         <v>46146.787934409724</v>
@@ -7722,7 +7719,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B106" s="5">
         <v>46146.787939131944</v>
@@ -7773,7 +7770,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B107" s="9">
         <v>46146.787957974535</v>
@@ -7783,7 +7780,7 @@
         <v>46146.94056351852</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>25</v>
@@ -7807,7 +7804,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -7820,7 +7817,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B108" s="5">
         <v>46146.78796153935</v>
@@ -7830,16 +7827,16 @@
         <v>46146.94352958333</v>
       </c>
       <c r="E108" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7857,13 +7854,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>326</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q108" s="5">
         <v>46240</v>
@@ -7883,7 +7880,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
@@ -7893,7 +7890,7 @@
         <v>46196.86770128472</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7920,13 +7917,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>326</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q109" s="9">
         <v>46240</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="340">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -1082,6 +1082,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214511241432568</t>
@@ -7824,7 +7827,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46146.94352958333</v>
+        <v>46241.1826499537</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>334</v>
@@ -7868,8 +7871,8 @@
       <c r="R108" s="5">
         <v>46248</v>
       </c>
-      <c r="S108" s="7" t="s">
-        <v>101</v>
+      <c r="S108" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
@@ -7880,17 +7883,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46196.86770128472</v>
+        <v>46241.18265023148</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7931,8 +7934,8 @@
       <c r="R109" s="9">
         <v>46248</v>
       </c>
-      <c r="S109" s="7" t="s">
-        <v>101</v>
+      <c r="S109" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5196,7 +5196,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46240.58270290509</v>
+        <v>46244.58203480324</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5196,7 +5196,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46244.58203480324</v>
+        <v>46244.81647160879</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5196,7 +5196,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46244.81647160879</v>
+        <v>46244.91622329861</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46241.1826499537</v>
+        <v>46248.168381041665</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>334</v>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46241.18265023148</v>
+        <v>46248.168384108794</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>339</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -1082,9 +1082,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214511241432568</t>
@@ -7827,7 +7824,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46248.168381041665</v>
+        <v>46249.181991273144</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>334</v>
@@ -7871,8 +7868,8 @@
       <c r="R108" s="5">
         <v>46248</v>
       </c>
-      <c r="S108" s="12" t="s">
-        <v>337</v>
+      <c r="S108" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
@@ -7883,17 +7880,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B109" s="9">
         <v>46146.78796724537</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46248.168384108794</v>
+        <v>46249.181991273144</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7934,8 +7931,8 @@
       <c r="R109" s="9">
         <v>46248</v>
       </c>
-      <c r="S109" s="12" t="s">
-        <v>337</v>
+      <c r="S109" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5193,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46244.91622329861</v>
+        <v>46252.55708864583</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5193,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46252.55708864583</v>
+        <v>46252.69802989584</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5193,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46252.69802989584</v>
+        <v>46258.649322060184</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46239.17831525463</v>
+        <v>46260.575125601856</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>320</v>
@@ -7499,8 +7499,8 @@
       <c r="T101" s="10">
         <v>0</v>
       </c>
-      <c r="U101" s="11" t="s">
-        <v>102</v>
+      <c r="U101" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46240.19482599537</v>
+        <v>46260.57514836805</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>326</v>
@@ -7662,8 +7662,8 @@
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="11" t="s">
-        <v>102</v>
+      <c r="U104" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="339">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5193,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46258.649322060184</v>
+        <v>46260.679553298614</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46237.454968252314</v>
+        <v>46260.83940523148</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>260</v>
@@ -6051,7 +6051,9 @@
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
       <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+      <c r="U75" s="12" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -6913,9 +6915,11 @@
       <c r="B91" s="9">
         <v>46146.787759479164</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46260.83938579861</v>
+      </c>
       <c r="D91" s="9">
-        <v>46237.537099340276</v>
+        <v>46260.83939934028</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>295</v>
@@ -6961,7 +6965,7 @@
         <v>33</v>
       </c>
       <c r="T91" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U91" s="7" t="s">
         <v>27</v>
@@ -6974,9 +6978,11 @@
       <c r="B92" s="5">
         <v>46146.78776425926</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46260.83918481482</v>
+      </c>
       <c r="D92" s="5">
-        <v>46238.51200935185</v>
+        <v>46260.839187210644</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -7025,9 +7031,11 @@
       <c r="B93" s="9">
         <v>46146.787768587965</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46260.83937011574</v>
+      </c>
       <c r="D93" s="9">
-        <v>46238.512046909724</v>
+        <v>46260.839371504626</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7078,7 +7086,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46146.9405634838</v>
+        <v>46260.83942512731</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>302</v>
@@ -7125,7 +7133,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46237.41653664352</v>
+        <v>46260.83939849537</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7186,7 +7194,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46234.16930011574</v>
+        <v>46260.839191493054</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7237,7 +7245,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46234.169297361106</v>
+        <v>46260.839378668985</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7286,9 +7294,11 @@
       <c r="B98" s="5">
         <v>46146.787814745374</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46260.83923814815</v>
+      </c>
       <c r="D98" s="5">
-        <v>46238.19551771991</v>
+        <v>46260.83925326389</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>314</v>
@@ -7334,7 +7344,7 @@
         <v>33</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U98" s="7" t="s">
         <v>27</v>
@@ -7449,9 +7459,11 @@
       <c r="B101" s="9">
         <v>46146.787891527776</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9">
+        <v>46260.83941804398</v>
+      </c>
       <c r="D101" s="9">
-        <v>46260.575125601856</v>
+        <v>46260.83943501157</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>320</v>
@@ -7497,7 +7509,7 @@
         <v>33</v>
       </c>
       <c r="T101" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" s="7" t="s">
         <v>27</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="339">
   <si>
     <t>50001543 - ZITRON COLOMBIA EGM</t>
   </si>
@@ -6013,9 +6013,11 @@
       <c r="B75" s="9">
         <v>46146.78750452546</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46260.84442424768</v>
+      </c>
       <c r="D75" s="9">
-        <v>46260.83940523148</v>
+        <v>46260.84444311343</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>260</v>
@@ -6050,9 +6052,11 @@
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="12" t="s">
-        <v>207</v>
+      <c r="T75" s="10">
+        <v>1</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -7086,7 +7090,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46260.83942512731</v>
+        <v>46260.84455974537</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>302</v>
@@ -7122,7 +7126,9 @@
       <c r="R94" s="6"/>
       <c r="S94" s="6"/>
       <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="12" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
@@ -7131,9 +7137,11 @@
       <c r="B95" s="9">
         <v>46146.78778912037</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9">
+        <v>46260.84449711806</v>
+      </c>
       <c r="D95" s="9">
-        <v>46260.83939849537</v>
+        <v>46260.84451005787</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7179,10 +7187,10 @@
         <v>33</v>
       </c>
       <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U95" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7192,9 +7200,11 @@
       <c r="B96" s="5">
         <v>46146.78779429398</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46260.84448118055</v>
+      </c>
       <c r="D96" s="5">
-        <v>46260.839191493054</v>
+        <v>46260.844482615736</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7243,9 +7253,11 @@
       <c r="B97" s="9">
         <v>46146.787798414356</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9">
+        <v>46260.844485787035</v>
+      </c>
       <c r="D97" s="9">
-        <v>46260.839378668985</v>
+        <v>46260.84448701389</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7359,7 +7371,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46237.16882690972</v>
+        <v>46260.844491724536</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>191</v>
@@ -7410,7 +7422,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46237.16882849537</v>
+        <v>46260.84449135417</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7463,7 +7475,7 @@
         <v>46260.83941804398</v>
       </c>
       <c r="D101" s="9">
-        <v>46260.83943501157</v>
+        <v>46260.83958581019</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>320</v>
@@ -7511,8 +7523,8 @@
       <c r="T101" s="10">
         <v>1</v>
       </c>
-      <c r="U101" s="7" t="s">
-        <v>27</v>
+      <c r="U101" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7522,9 +7534,11 @@
       <c r="B102" s="5">
         <v>46146.78789762731</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46260.83956966436</v>
+      </c>
       <c r="D102" s="5">
-        <v>46238.1680128588</v>
+        <v>46260.839570972224</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7573,9 +7587,11 @@
       <c r="B103" s="9">
         <v>46146.78790538195</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46260.83951644676</v>
+      </c>
       <c r="D103" s="9">
-        <v>46238.1680141088</v>
+        <v>46260.83951788195</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7624,9 +7640,11 @@
       <c r="B104" s="5">
         <v>46146.787928171296</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46260.844537638885</v>
+      </c>
       <c r="D104" s="5">
-        <v>46260.57514836805</v>
+        <v>46260.8445503588</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>326</v>
@@ -7672,10 +7690,10 @@
         <v>33</v>
       </c>
       <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="7" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="U104" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7685,9 +7703,11 @@
       <c r="B105" s="9">
         <v>46146.787934409724</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="9">
+        <v>46260.84451734954</v>
+      </c>
       <c r="D105" s="9">
-        <v>46239.167930972224</v>
+        <v>46260.84451940972</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7736,9 +7756,11 @@
       <c r="B106" s="5">
         <v>46146.787939131944</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46260.84452320602</v>
+      </c>
       <c r="D106" s="5">
-        <v>46239.167932233795</v>
+        <v>46260.84452525463</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7836,7 +7858,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46249.181991273144</v>
+        <v>46260.84456067129</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>334</v>
@@ -7886,8 +7908,8 @@
       <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="U108" s="11" t="s">
-        <v>102</v>
+      <c r="U108" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7899,7 +7921,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46249.181991273144</v>
+        <v>46260.8445634838</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>338</v>
@@ -7949,8 +7971,8 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="11" t="s">
-        <v>102</v>
+      <c r="U109" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -748,7 +748,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT 4309 - ZVN 1-9-75/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1214508463084766</t>
@@ -5193,7 +5193,7 @@
         <v>46198.893461747684</v>
       </c>
       <c r="D61" s="9">
-        <v>46260.679553298614</v>
+        <v>46261.60081914352</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>

--- a/data/50001543 - ZITRON COLOMBIA EGM.xlsx
+++ b/data/50001543 - ZITRON COLOMBIA EGM.xlsx
@@ -2088,7 +2088,7 @@
         <v>46197.64946785879</v>
       </c>
       <c r="D10" s="5">
-        <v>46237.42832782408</v>
+        <v>46264.11015918982</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
